--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1319207930213133</v>
+        <v>0.1319207930213132</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13192.07930213133</v>
+        <v>13192.07930213132</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0437413188564415</v>
+        <v>0.0437413188564412</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>577.0389471339888</v>
+        <v>577.0389471339845</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>234.1111810047456</v>
+        <v>234.1111810047455</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>213.0850028991699</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8748263771288307</v>
+        <v>0.8748263771288256</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09914425429287414</v>
+        <v>0.09914425429287406</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9914.425429287414</v>
+        <v>9914.425429287407</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0171674480247481</v>
+        <v>0.0171674480247476</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>170.2053832525326</v>
+        <v>170.2053832525275</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>96.42747717689483</v>
+        <v>96.42747717689477</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>87.26794819863983</v>
+        <v>87.2679481986398</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2160730580000092</v>
+        <v>0.2160730580000031</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09732031456006449</v>
+        <v>0.09732031456006451</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9732.031456006449</v>
+        <v>9732.031456006451</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0695500946938858</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>676.8637093291238</v>
+        <v>676.8637093291239</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>426.2157127355135</v>
@@ -1103,7 +1103,7 @@
         <v>36.23975304114958</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.594290083864031</v>
+        <v>0.5942900838640295</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08114172203589044</v>
+        <v>0.08114172203589055</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8114.172203589044</v>
+        <v>8114.172203589055</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>189.1561894716127</v>
+        <v>189.1561894716146</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>136.5097916537755</v>
+        <v>136.5097916537756</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>126.7299942016601</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4662365666529613</v>
+        <v>0.4662365666529656</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1443,7 +1443,7 @@
         <v>0.0371203025212296</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0437413188564415</v>
+        <v>0.0437413188564412</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.120622641333925</v>
@@ -1452,7 +1452,7 @@
         <v>232.6260870205518</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>234.1111810047456</v>
+        <v>234.1111810047455</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>251.3556618710683</v>
@@ -1554,7 +1554,7 @@
         <v>24.97999954223633</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.07844690697526251</v>
+        <v>-0.0784469069752626</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>-0.0190929272018391</v>
@@ -1563,7 +1563,7 @@
         <v>0.09315584596891301</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>23.02039584190442</v>
+        <v>23.02039584190441</v>
       </c>
       <c r="I10" s="18" t="n">
         <v>24.50305822947444</v>
@@ -1572,7 +1572,7 @@
         <v>27.30703253189641</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>23.02039584190442</v>
+        <v>23.02039584190441</v>
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
@@ -1608,28 +1608,28 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>94.80000305175781</v>
+        <v>94.8000030517578</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0794520528549532</v>
+        <v>-0.0794520528549533</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0171674480247481</v>
+        <v>0.0171674480247476</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>0.0870869998031074</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>87.26794819863983</v>
+        <v>87.2679481986398</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>96.42747717689483</v>
+        <v>96.42747717689477</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>103.0558508988608</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>87.26794819863983</v>
+        <v>87.2679481986398</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         <v>44.06000137329102</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.084296702806661</v>
+        <v>-0.08429670280666079</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0004088702928312</v>
+        <v>0.0004088702928311</v>
       </c>
       <c r="G12" s="22" t="n">
         <v>0.1101031122376878</v>
@@ -1731,7 +1731,7 @@
         <v>-0.0036968005684216</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.1486665754350491</v>
+        <v>0.1486665754350493</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>424.0458804389618</v>
@@ -1740,7 +1740,7 @@
         <v>428.4103757555787</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>493.9266274370711</v>
+        <v>493.9266274370712</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>408.5</v>
@@ -1782,7 +1782,7 @@
         <v>72.09999847412109</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>-0.1073109919236646</v>
+        <v>-0.1073109919236645</v>
       </c>
       <c r="F14" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -1839,7 +1839,7 @@
         <v>38.97999954223633</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-0.0702987822798095</v>
+        <v>-0.0702987822798096</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>0.0417778692166073</v>
@@ -1956,19 +1956,19 @@
         <v>-0.0353227048870178</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.1081830165120092</v>
+        <v>0.108183016512009</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>128.6879452801489</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>136.5097916537755</v>
+        <v>136.5097916537756</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>147.8316076388897</v>
+        <v>147.8316076388896</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>126.7299942016601</v>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
         <v>0.0195327504943525</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0437413188564415</v>
+        <v>0.0437413188564412</v>
       </c>
     </row>
     <row r="5">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0821918345097203</v>
+        <v>0.0821918345097201</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.0349345483727359</v>
+        <v>0.0349345483727356</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>0.0065102745953808</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0175239369224565</v>
+        <v>0.0175239369224564</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0171674480247481</v>
+        <v>0.0171674480247476</v>
       </c>
     </row>
     <row r="8">
@@ -2323,7 +2323,7 @@
         <v>0.0291195183035908</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0.0004088702928312</v>
+        <v>0.0004088702928311</v>
       </c>
     </row>
     <row r="9">
@@ -2352,7 +2352,7 @@
         <v>0.1359779535346976</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.2201541438032379</v>
+        <v>0.2201541438032381</v>
       </c>
       <c r="H9" s="19" t="n">
         <v>0.0096886004836262</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="J10" s="19" t="n">
-        <v>0.0242987733054774</v>
+        <v>0.0242987733054775</v>
       </c>
       <c r="K10" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="J11" s="16" t="n">
-        <v>0.0244714614971411</v>
+        <v>0.0244714614971412</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>0.0417778692166073</v>
@@ -2538,7 +2538,7 @@
         <v>0.0171812701253963</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
     </row>
     <row r="14">
@@ -2739,7 +2739,7 @@
         <v>-0.0537261855796603</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>-0.244328041464684</v>
+        <v>-0.2443280414646841</v>
       </c>
       <c r="H18" s="24" t="n">
         <v>-0.0419382538842088</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.018326546308491</v>
+        <v>0.0183265463084909</v>
       </c>
       <c r="K18" s="24" t="n">
         <v>0.0999999076690971</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.0139213599674617</v>
+        <v>0.0139213599674618</v>
       </c>
       <c r="K19" s="24" t="n">
         <v>0.0999999076690971</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.0188455307128114</v>
+        <v>0.0188455307128113</v>
       </c>
       <c r="K20" s="24" t="n">
         <v>0.0294396733991557</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3444,7 +3444,7 @@
         <v>-1763.40361076151</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3474,7 +3474,7 @@
         <v>402757.4632715508</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3504,7 +3504,7 @@
         <v>-56270.17347722268</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3525,16 +3525,16 @@
         <v>96.5</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>94.80000305175781</v>
+        <v>94.8000030517578</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>-0.01761654868644758</v>
+        <v>-0.01761654868644769</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>-1546.988053709545</v>
+        <v>-1546.98805370956</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3564,7 +3564,7 @@
         <v>-2067.772894119626</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H9" s="26" t="n">
         <v>0.0503429940619526</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3444,7 +3444,7 @@
         <v>-1763.40361076151</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3474,7 +3474,7 @@
         <v>402757.4632715508</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3504,7 +3504,7 @@
         <v>-56270.17347722268</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3534,7 +3534,7 @@
         <v>-1546.98805370956</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3564,7 +3564,7 @@
         <v>-2067.772894119626</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H9" s="26" t="n">
         <v>0.0503429940619526</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,6 +164,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -171,15 +180,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,13 +191,16 @@
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -577,13 +580,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -630,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -647,7 +650,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Piyasa Rejimi: Risk ON</t>
+          <t>Piyasa Rejimi: Risk OFF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -664,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Aktif Model: volume_heavy</t>
+          <t>Aktif Model: low_volatility</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -681,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 51.86/100</t>
+          <t>Güven Puanı: 64.21/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -741,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, BIMAS.IS, GARAN.IS, SAHOL.IS, EREGL.IS</t>
+          <t>AL: KCHOL.IS, GARAN.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -758,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>AZALT: BIMAS.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -775,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
+          <t>ÇIK: THYAO.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -792,7 +795,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %50</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -890,7 +893,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 5</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -947,7 +950,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 5</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -961,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.12307111833361</v>
+        <v>0.2118012179582496</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12307.111833361</v>
+        <v>21180.12179582496</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>467.5182290732529</v>
+        <v>492.8207489184861</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>214.3444492591615</v>
+        <v>211.3048583304997</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>196.175</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.759752954882472</v>
+        <v>0.3518217892616204</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -990,12 +993,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %50</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1004,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1083549289094442</v>
+        <v>0.2046838490225011</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10835.49289094442</v>
+        <v>20468.38490225011</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0485933057984229</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>526.5324195262998</v>
+        <v>677.8604291940321</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>425.2045855012605</v>
+        <v>124.9038996016319</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>385.225</v>
+        <v>114.855001449585</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9718661159684575</v>
+        <v>0.662348722120733</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1036,7 +1039,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1045,25 +1048,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09211535586320244</v>
+        <v>0.1835149330192493</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9211.535586320244</v>
+        <v>18351.49330192493</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0296792745067082</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>305.0624412184431</v>
+        <v>544.659007315847</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>124.9038996016319</v>
+        <v>89.42764341974173</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>114.855001449585</v>
+        <v>82.50749855041504</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.662348722120733</v>
+        <v>0.5935854901341648</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1072,124 +1075,42 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>0.08923779370436544</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>8923.779370436543</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0.061538473957351</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>549.1557643887553</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>89.48769659416303</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>80.08500289916992</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>1.230769479147021</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0.08722080318937789</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>8722.080318937789</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>364.3891427389418</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>36.23302987695052</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.5942894806665029</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K25"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1200,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1244,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1286,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 12</t>
+          <t>Toplam önerilen/satılacak satır: 7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1429,37 +1350,37 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>206.5</v>
+        <v>405.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.039087920591243</v>
+        <v>-0.0339316179450966</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.1206226545342643</v>
+        <v>0.0770489383118369</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>198.4283443979083</v>
+        <v>391.7407289232634</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>214.3444492591615</v>
+        <v>413.2162352085374</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>231.4085781613256</v>
+        <v>436.7433444854499</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>196.175</v>
+        <v>385.225</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1467,7 +1388,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1486,45 +1407,45 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>401.75</v>
+        <v>206.5</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.0985715365910573</v>
+        <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>-0.003584755659184</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>0.1274261934904716</v>
+        <v>0.0690438632887718</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>362.1488851745427</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>400.3098244139228</v>
+        <v>211.3048583304997</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>452.943473234797</v>
+        <v>220.7575577691314</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>362.1488851745427</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="L9" s="16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M9" s="16" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="N9" s="16" t="inlineStr">
         <is>
@@ -1533,64 +1454,64 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>20.97999954223633</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>-0.0954999923706054</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>0.09315584596891301</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>18.97640974601746</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>20.97999954223633</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>22.93440914802076</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>18.97640974601746</v>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N10" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="19" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>120.9000015258789</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0446735791747727</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1240418332017574</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>115.4989657354824</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>124.9038996016319</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>135.8966593492442</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>114.855001449585</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1600,515 +1521,230 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0855565177750571</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0171415659369608</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.1267042006856777</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>367.3776689838708</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>408.636624115174</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>452.653412625471</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>367.3776689838708</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0082994402169681</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0485933057984229</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.1486667759327886</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>402.1345769920194</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>425.2045855012605</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>465.7843776407458</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>385.225</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="D12" s="17" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0450302501162372</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.0296792745067082</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.0884521142598899</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>82.93912132023661</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>89.42764341974173</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>94.53206446262533</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>82.50749855041504</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>38.22000122070312</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0842967976871922</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.000408918900135</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.1015857338863732</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>34.99817751019727</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>38.23563010156546</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>42.10260809384634</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>34.99817751019727</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="M12" s="16" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>273</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0762004294665497</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.0438597808507175</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.0475785896346643</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>252.1972827556319</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>261.0262798277541</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>285.9889549702634</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>252.1972827556319</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>120.9000015258789</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.0371959299442395</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>0.1272217020935506</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>116.4030135388639</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>124.9038996016319</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>136.2811055031141</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <v>114.855001449585</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N13" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="M13" s="19" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="A14" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
-        <v>95.75</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.06865539483568921</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.0285467446983213</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.0289374356535263</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>89.17624594448276</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>93.01664919513574</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>98.52075946382514</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>89.17624594448276</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="D14" s="20" t="n">
+        <v>272.25</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.082926169656068</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.000450260009301</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.1059737014525552</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>249.6733503111355</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>272.1274167124678</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>301.1013402204582</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>249.6733503111355</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="16" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>65.19999694824219</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.0621387669809665</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>0.0306241627672483</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.1086638342048738</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>61.14854953071563</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>67.19669226720924</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>72.28487860678426</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>61.14854953071563</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>34.77999877929688</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-0.0702987015861401</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>0.0831932668372119</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>36.23302987695052</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>37.67346049834082</v>
-      </c>
-      <c r="K16" s="14" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N16" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>84.30000305175781</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.0181378772961786</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>0.061538473957351</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>0.1293435773389155</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>82.77097994033755</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>89.48769659416303</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>95.20366701615366</v>
-      </c>
-      <c r="K17" s="14" t="n">
-        <v>80.08500289916992</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N17" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O17" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>145.1999969482422</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0392156862745097</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0007077205736818</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.1293359288901121</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>139.5058794208602</v>
-      </c>
-      <c r="I18" s="23" t="n">
-        <v>145.0972359231034</v>
-      </c>
-      <c r="J18" s="23" t="n">
-        <v>163.9795734283845</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>137.9399971008301</v>
-      </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="n">
-        <v>32.11999893188477</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0532446188809735</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.0190620607116771</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.0428598924856524</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>30.40978183029928</v>
-      </c>
-      <c r="I19" s="23" t="n">
-        <v>31.50772556218617</v>
-      </c>
-      <c r="J19" s="23" t="n">
-        <v>33.49665863274462</v>
-      </c>
-      <c r="K19" s="23" t="n">
-        <v>30.40978183029928</v>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M19" s="22" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N19" s="22" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O19" s="22" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M14" s="19" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O19"/>
+  <autoFilter ref="A7:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2155,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2232,7 +1868,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -2242,20 +1878,20 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0043774020903055</v>
+        <v>0.0072916582962114</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0551865264188744</v>
+        <v>0.0413608561912206</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.1088043175022459</v>
+        <v>0.1851961795211201</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>0.2057032864944392</v>
+        <v>-0.0623598620860903</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -2263,10 +1899,10 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0200019040925806</v>
+        <v>0.0188637341167536</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0190289400950367</v>
       </c>
     </row>
     <row r="5">
@@ -2275,84 +1911,84 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>-0.0067339775737629</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.034051092416993</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.0985692087568079</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.2031171068964992</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0194217173689601</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>0.08949152542372869</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.772165881818355</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.5754901960784313</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.09061475678536079</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0266079182148352</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>-0.003584755659184</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>0.0955613556219225</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>0.044820698304274</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>0.0595959773052476</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>0.1643757802273222</v>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>0.0406349141733305</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>0</v>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>-0.064965207483533</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>-0.1604166560702853</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-0.0918000573807312</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.1338440657530808</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0.0168100770079203</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0.0331174361060366</v>
       </c>
     </row>
     <row r="7">
@@ -2361,600 +1997,600 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.07419786096256679</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.7927264125750395</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.5974155069582505</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.0866514907563507</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0.0264956263736686</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0171415659369608</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0679401059595536</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.0665440612239525</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.2150456013908888</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.0056807080181966</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="E8" s="18" t="n">
+        <v>-0.0666308906426155</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>-0.16329483698748</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>-0.2434669323574443</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.0447946090151196</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.0144115919578272</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0.0296792745067082</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>-0.0522764930412542</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.1775609458365091</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>-0.1068369587850867</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0.0974086401731955</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>0.0172418278494896</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0125688346543615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>-0.0915141430948419</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>-0.1689497716894977</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>-0.0737913486005089</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>-0.0009174564930963</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>0.0173415165449425</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>-0.0438597808507175</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>-0.0274615272586047</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.2138603175563069</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1928849256560219</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0.0526434538225228</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>0.0170949295625193</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.006131117760765</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>0.0585267338684687</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0.0274240677693482</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.031465063168498</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>0.1705560918196227</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0191191082032721</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0485933057984229</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="J12" s="23" t="n">
+        <v>0.0355156641914875</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0.002557432846991</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>-0.0774536319509322</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-0.130500030517578</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>0.228324143503479</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0.0673904056469028</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.0257858693771773</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.019070255160478</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.0254237288135592</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1799698795180723</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.0768923210325955</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0341755137155445</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0228770438599459</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>-0.000450260009301</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>-0.0538656516832387</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.1872618098419274</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.3081556953641494</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.0216399265741287</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0175418542292546</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>0.0006695213718759</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>-0.0748792270531401</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>-0.1745689655172413</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>-0.1358303487115206</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>0.2731285195859629</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>0.0197620982238175</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.0556585878468132</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.0557377049180327</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.1235544735240413</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.0549450549450549</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.1018704487088503</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0299429051249194</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.0485096508933775</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>-0.0362158835532249</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.1960542765109</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>-0.1122733625312385</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>0.2410422103922216</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>0.0213786434561666</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0.05159344410234</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>-0.0108695180015409</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-0.1487750574201126</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>-0.0885889870129208</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>0.387106135015776</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>0.0026233549743024</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>-0.1936708862796933</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>-0.1256381990168611</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0.3991606220660881</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>0.031520714084673</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.000408918900135</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="J19" s="27" t="n">
+        <v>0.026262986561954</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>0.06799392425498541</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0627906858458999</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>-0.1425531806675255</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>-0.0620008227748822</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>0.1044133754393505</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>-0.07860016151729959</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>-0.2477752140987634</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>-0.1072818415636823</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>0.0655210596212267</v>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="15" t="n">
-        <v>0.0173661554830595</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0694849506302555</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.1458519063039557</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>-0.122364790658432</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0.2636171930649325</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.0205145061613839</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>-0.0285467446983213</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0411765154670266</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.1641026032276642</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.0744198020732777</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0.225460329022473</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>0.0223810594655514</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0.0306241627672483</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0832894033155693</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>-0.1172589484177429</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.2518786862216586</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.07263925691405849</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>0.0267034739778493</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.0517435140063752</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>-0.1553106164932827</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>-0.0892681064853825</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.1017734892899173</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>0.0180337362813238</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.061538473957351</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.0745501285347043</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.08860759493670881</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>0.1232449297971918</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>-0.1014754690653146</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0303591105771636</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.0245003718359859</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.0396825404834755</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.1933333502875434</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.1791972755340619</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>0.0432479046991434</v>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.01768194495492</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>-0.0007077205736818</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>0.0206185567010308</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.173120728929385</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.0450871551413537</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>-0.062282119385654</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.0234029498955229</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.0445250258600058</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.0930232558139535</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>-0.1515151515151515</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.0586206896551724</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.0162517774614465</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0176619745094825</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.1028940851473592</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.07704569731734751</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.1616795390608436</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-0.231415942706893</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.0099801366801068</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.014927802410026</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.1658137063821738</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0801832584158213</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.2146699820643947</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.0817610248078556</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>0.062087038248501</v>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0246165692883249</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>-0.0190620607116771</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.0550632718243176</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.1663875043897771</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.293087096547894</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0.0036869731660258</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0190864561409881</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>0.0283622708857007</v>
+      <c r="J20" s="27" t="n">
+        <v>0.0235895708006696</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>0.0248447886632294</v>
       </c>
     </row>
   </sheetData>
@@ -2987,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3012,7 +2648,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, BIMAS.IS, GARAN.IS, EREGL.IS, SAHOL.IS</t>
+          <t>KCHOL.IS, GARAN.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -3024,7 +2660,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>BIMAS.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -3036,7 +2672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
+          <t>THYAO.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -3048,7 +2684,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS, TOASO.IS, THYAO.IS, ARCLK.IS, FROTO.IS</t>
+          <t>SAHOL.IS, PGSUS.IS, PETKM.IS, EREGL.IS, FROTO.IS, TCELL.IS, ASELS.IS, AKBNK.IS, SISE.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -3060,7 +2696,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3072,7 +2708,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3106,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3143,7 +2779,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3167,7 +2803,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3179,7 +2815,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3251,7 +2887,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3275,7 +2911,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3323,7 +2959,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3357,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3381,7 +3017,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13509.7998046875</v>
+        <v>13284.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3391,7 +3027,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13489.76401855469</v>
+        <v>13501.69251953125</v>
       </c>
     </row>
     <row r="6">
@@ -3402,7 +3038,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Risk ON</t>
+          <t>Risk OFF</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3050,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>volume_heavy</t>
+          <t>low_volatility</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3061,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3436,7 +3072,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
+          <t>BIST100 MA200 altında olduğu için savunmacı rejim izleniyor.</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3096,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3482,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3546,22 +3182,22 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="27" t="n">
+      <c r="D4" s="28" t="n">
         <v>360</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="29" t="n">
         <v>-0.09887359198998746</v>
       </c>
-      <c r="F4" s="27" t="n">
+      <c r="F4" s="28" t="n">
         <v>-69654.44262507732</v>
       </c>
-      <c r="G4" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H4" s="28" t="n">
+      <c r="G4" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3576,22 +3212,22 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="28" t="n">
         <v>206.5</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="29" t="n">
         <v>0.0482233502538072</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="28" t="n">
         <v>140153.6803430272</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H5" s="28" t="n">
+      <c r="G5" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3606,22 +3242,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="28" t="n">
         <v>84.30000305175781</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="29" t="n">
         <v>-0.1264248388418879</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="28" t="n">
         <v>-11101.93142037037</v>
       </c>
-      <c r="G6" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H6" s="28" t="n">
+      <c r="G6" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3636,89 +3272,89 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="28" t="n">
         <v>120.9000015258789</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="29" t="n">
         <v>-0.09370309552116773</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="28" t="n">
         <v>-453776.1194554595</v>
       </c>
-      <c r="G7" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H7" s="28" t="n">
+      <c r="G7" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>299.75</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>272.25</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>-0.09174311926605505</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>-20640.73562494843</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H8" s="28" t="n">
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>38.86000061035156</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>34.77999877929688</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.1049923254496258</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-22854.86544006292</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>38.86000061035156</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>34.77999877929688</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>-0.1049923254496258</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>-22854.86544006292</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H9" s="28" t="n">
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3726,22 +3362,22 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="D10" s="27" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="E10" s="28" t="n">
+      <c r="C10" s="28" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H10" s="28" t="n">
+      <c r="F10" s="28" t="n">
+        <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2118012179582496</v>
+        <v>0.2118012179582497</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21180.12179582496</v>
+        <v>21180.12179582497</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>492.8207489184861</v>
+        <v>492.8207489184928</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>211.3048583304997</v>
@@ -982,7 +982,7 @@
         <v>192.8429199749572</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3518217892616204</v>
+        <v>0.3518217892616246</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2046838490225011</v>
+        <v>0.204683849022501</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20468.38490225011</v>
+        <v>20468.3849022501</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>677.8604291940321</v>
+        <v>677.860429194032</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>124.9038996016319</v>
@@ -1057,7 +1057,7 @@
         <v>0.0296792745067082</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>544.659007315847</v>
+        <v>544.6590073158468</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>89.42764341974173</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.4</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>40000</v>
+        <v>39999.99999999999</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
         <v>405.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316179450966</v>
+        <v>-0.0339316179450965</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1422,7 +1422,7 @@
         <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.0690438632887718</v>
@@ -1539,7 +1539,7 @@
         <v>0.0171415659369608</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.1267042006856777</v>
+        <v>0.1267042006856775</v>
       </c>
       <c r="H11" s="14" t="n">
         <v>367.3776689838708</v>
@@ -1548,7 +1548,7 @@
         <v>408.636624115174</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>452.653412625471</v>
+        <v>452.6534126254709</v>
       </c>
       <c r="K11" s="14" t="n">
         <v>367.3776689838708</v>
@@ -1791,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0072916582962114</v>
+        <v>0.0072916582962112</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>0.0413608561912206</v>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-0.0067339775737629</v>
+        <v>-0.006733977573763</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>0.034051092416993</v>
@@ -1945,7 +1945,7 @@
         <v>0.0194217173689601</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -2014,7 +2014,7 @@
         <v>0.07419786096256679</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.7927264125750395</v>
+        <v>0.7927264125750397</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>0.5974155069582505</v>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.0666308906426155</v>
+        <v>-0.0666308906426154</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-0.16329483698748</v>
+        <v>-0.1632948369874799</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-0.2434669323574443</v>
+        <v>-0.2434669323574442</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0.0447946090151196</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.0144115919578272</v>
+        <v>0.0144115919578273</v>
       </c>
       <c r="K8" s="18" t="n">
         <v>0.0296792745067082</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0172418278494896</v>
+        <v>0.0172418278494895</v>
       </c>
       <c r="K9" s="23" t="n">
         <v>0.0125688346543615</v>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0173415165449425</v>
+        <v>0.0173415165449426</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>-0.0438597808507175</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0355156641914875</v>
+        <v>0.0355156641914876</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>0.002557432846991</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0257858693771773</v>
+        <v>0.0257858693771772</v>
       </c>
       <c r="K13" s="23" t="n">
         <v>0.019070255160478</v>
@@ -2318,7 +2318,7 @@
         <v>-0.1799698795180723</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.0768923210325955</v>
+        <v>-0.0768923210325954</v>
       </c>
       <c r="H14" s="25" t="n">
         <v>-0.0341755137155445</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0228770438599459</v>
+        <v>0.022877043859946</v>
       </c>
       <c r="K14" s="25" t="n">
         <v>-0.000450260009301</v>
@@ -2404,7 +2404,7 @@
         <v>-0.1745689655172413</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>-0.1358303487115206</v>
+        <v>-0.1358303487115205</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.2731285195859629</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0213786434561666</v>
+        <v>0.0213786434561665</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>0.05159344410234</v>
@@ -2533,7 +2533,7 @@
         <v>-0.1936708862796933</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>-0.1256381990168611</v>
+        <v>-0.1256381990168612</v>
       </c>
       <c r="H19" s="27" t="n">
         <v>0.3991606220660881</v>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0235895708006696</v>
+        <v>0.0235895708006695</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.0248447886632294</v>
@@ -2623,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2742,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2993,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3118,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3195,7 +3195,7 @@
         <v>-69654.44262507732</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3225,7 +3225,7 @@
         <v>140153.6803430272</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3255,7 +3255,7 @@
         <v>-11101.93142037037</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3285,7 +3285,7 @@
         <v>-453776.1194554595</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3315,7 +3315,7 @@
         <v>-22854.86544006292</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3375,7 +3375,7 @@
         <v>-4.656612873077393e-10</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1791,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2623,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2742,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2993,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3097,7 +3097,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3118,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3195,7 +3195,7 @@
         <v>-69654.44262507732</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3225,7 +3225,7 @@
         <v>140153.6803430272</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3255,7 +3255,7 @@
         <v>-11101.93142037037</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3285,7 +3285,7 @@
         <v>-453776.1194554595</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3315,7 +3315,7 @@
         <v>-22854.86544006292</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3375,7 +3375,7 @@
         <v>-4.656612873077393e-10</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2262039331984107</v>
+        <v>0.2262039331984106</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22620.39331984107</v>
+        <v>22620.39331984106</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0485933057984229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1099.19968987164</v>
+        <v>1099.199689871639</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>443.2928200262833</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1899558085524913</v>
+        <v>0.1899558085524912</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18995.58085524913</v>
+        <v>18995.58085524912</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0955196579070878</v>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.183840258249098</v>
+        <v>0.1838402582490981</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18384.0258249098</v>
+        <v>18384.02582490982</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>427.7609667454678</v>
+        <v>427.7609667454736</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>221.0259050817818</v>
@@ -1060,7 +1060,7 @@
         <v>205.2</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4653615816464586</v>
+        <v>0.4653615816464639</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1356,13 +1356,13 @@
         <v>422.75</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0340045699699408</v>
+        <v>-0.0340045699699409</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0485933057984229</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0801730736352934</v>
+        <v>0.0801730736352933</v>
       </c>
       <c r="H8" s="14" t="n">
         <v>408.3745680452075</v>
@@ -1371,7 +1371,7 @@
         <v>443.2928200262833</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>456.6431668793203</v>
+        <v>456.6431668793202</v>
       </c>
       <c r="K8" s="14" t="n">
         <v>401.6125</v>
@@ -1416,7 +1416,7 @@
         <v>-0.0120987386157355</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>0.0914169657590902</v>
@@ -1470,7 +1470,7 @@
         <v>410.75</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-0.08640226646425481</v>
+        <v>-0.0864022664642549</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>0.0228858964847257</v>
@@ -1527,7 +1527,7 @@
         <v>22</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>-0.0753137768113169</v>
+        <v>-0.075313776811317</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>-0.0031957788743339</v>
@@ -1641,7 +1641,7 @@
         <v>86.44999694824219</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0445633254802306</v>
+        <v>-0.0445633254802305</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>-0.0062980681240358</v>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,7 +1882,7 @@
         <v>0.0208981225974997</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="E7" s="21" t="n">
-        <v>0.088031688778045</v>
+        <v>0.08803168877804519</v>
       </c>
       <c r="F7" s="21" t="n">
         <v>0.1235955099960948</v>
@@ -1997,7 +1997,7 @@
         <v>-0.1026086779608242</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.2463485508681537</v>
+        <v>-0.2463485508681538</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>0.0294478279074266</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="J8" s="15" t="n">
-        <v>0.0186115303364237</v>
+        <v>0.0186115303364236</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.0955196579070878</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0196382977066572</v>
+        <v>-0.0196382977066574</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.09924027566894179</v>
+        <v>-0.099240275668942</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>0.4295862429600472</v>
+        <v>0.429586242960047</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>-0.0463635917944209</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0260406298593469</v>
+        <v>0.026040629859347</v>
       </c>
       <c r="K9" s="23" t="n">
         <v>0.012842734528077</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0213838784267614</v>
+        <v>0.0213838784267613</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>0.01715475009491</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="J11" s="23" t="n">
-        <v>0.0246367814914132</v>
+        <v>0.0246367814914131</v>
       </c>
       <c r="K11" s="23" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>-0.1695485281901001</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.2232704889680877</v>
+        <v>-0.2232704889680876</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>0.1048848031430502</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="J12" s="21" t="n">
-        <v>0.0147205548238683</v>
+        <v>0.0147205548238684</v>
       </c>
       <c r="K12" s="21" t="n">
         <v>-0.0062980681240358</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0612027694175202</v>
+        <v>-0.0612027694175204</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.09492047500948481</v>
+        <v>-0.0949204750094849</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>-0.0037021562789459</v>
@@ -2226,7 +2226,7 @@
         <v>0.0202362846087154</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0444883459564572</v>
+        <v>0.0444883459564573</v>
       </c>
     </row>
     <row r="14">
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="E15" s="25" t="n">
-        <v>-0.0391304642681914</v>
+        <v>-0.0391304642681913</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>-0.1032462075752526</v>
+        <v>-0.1032462075752523</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.0617924816203567</v>
+        <v>-0.0617924816203565</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.1755718149091731</v>
@@ -2312,7 +2312,7 @@
         <v>0.0205927546794307</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
     </row>
     <row r="16">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0232585633457884</v>
+        <v>0.0232585633457885</v>
       </c>
       <c r="K16" s="25" t="n">
         <v>0.0218373705587808</v>
@@ -2560,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3246,10 +3246,10 @@
         <v>37.93999862670898</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>-0.02367478047330518</v>
+        <v>-0.0236747804733054</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>-5153.556888308289</v>
+        <v>-5153.556888308318</v>
       </c>
       <c r="G8" s="26" t="n">
         <v>20753084.26775555</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2560,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -952,25 +952,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2569227197998707</v>
+        <v>0.2569227197998708</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>25692.27197998708</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1126.231271623031</v>
+        <v>1126.231271623034</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>425.8848472093135</v>
+        <v>425.8848472093136</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>387.6</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8767081965349757</v>
+        <v>0.8767081965349784</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1847809963640967</v>
+        <v>0.1847809963640966</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18478.09963640967</v>
+        <v>18478.09963640966</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0285714285714284</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>527.945703897416</v>
+        <v>527.9457038974157</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>398.0571428571428</v>
@@ -1013,7 +1013,7 @@
         <v>365.767852694762</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5207736503606034</v>
+        <v>0.5207736503606021</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>0.0265059178623019</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>419.5788297265506</v>
+        <v>419.5788297265505</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>129.5450437015751</v>
@@ -1054,7 +1054,7 @@
         <v>116.8727931447235</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3586333936512622</v>
+        <v>0.3586333936512606</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000</v>
+        <v>40000.00000000001</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1353,19 +1353,19 @@
         <v>-0.02667302642785</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0795481196044297</v>
+        <v>0.0795481196044298</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>397.1174052174372</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>425.8848472093135</v>
+        <v>425.8848472093136</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>440.4556327986073</v>
+        <v>440.4556327986074</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>387.6</v>
@@ -1410,22 +1410,22 @@
         <v>-0.0166358032889645</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.0869050204659417</v>
+        <v>0.08690502046594149</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>206.4081388876676</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>214.7839635538469</v>
+        <v>214.783963553847</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>228.1413571618594</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>199.4049942016601</v>
+        <v>199.4049942016602</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1776,7 +1776,7 @@
         <v>0.0194135163494683</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
     </row>
     <row r="5">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.0145540192653316</v>
+        <v>-0.0145540192653313</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1070674427187814</v>
+        <v>0.1070674427187816</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.0870014876331113</v>
+        <v>0.0870014876331117</v>
       </c>
       <c r="H5" s="19" t="n">
         <v>0.0617187790758331</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0209011161906187</v>
+        <v>0.0209011161906186</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0274317148646485</v>
+        <v>0.0274317148646486</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0285714285714284</v>
@@ -1891,7 +1891,7 @@
         <v>-0.0991045140508395</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.2507447940934695</v>
+        <v>-0.2507447940934696</v>
       </c>
       <c r="H7" s="19" t="n">
         <v>0.0145514515489975</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0439394170587713</v>
+        <v>-0.0439394170587712</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.054681670799684</v>
+        <v>-0.0546816707996838</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>-1.088185066944192e-06</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="E9" s="21" t="n">
-        <v>-0.0260638186703872</v>
+        <v>-0.0260638186703869</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>-0.0867830342807164</v>
+        <v>-0.08678303428071631</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0.3162383142651317</v>
@@ -2017,7 +2017,7 @@
         <v>-0.1024930747922437</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>-0.1916167418464079</v>
+        <v>-0.1916167418464081</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>-0.2689530887272393</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0155420014820778</v>
+        <v>0.0155420014820779</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>0.0007363095911598</v>
@@ -2060,10 +2060,10 @@
         <v>0.0051440330833163</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>-0.0886194055078821</v>
+        <v>-0.088619405507882</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>-0.0860617815371082</v>
+        <v>-0.0860617815371079</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>-0.1002489595618008</v>
@@ -2120,7 +2120,7 @@
         <v>0.0202251259166578</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>0.0394096913634611</v>
+        <v>0.0394096913634612</v>
       </c>
     </row>
     <row r="13">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="J14" s="23" t="n">
-        <v>0.0242756658707128</v>
+        <v>0.0242756658707127</v>
       </c>
       <c r="K14" s="23" t="n">
         <v>0.0096600462209198</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="J17" s="23" t="n">
-        <v>0.031484362145451</v>
+        <v>0.0314843621454511</v>
       </c>
       <c r="K17" s="23" t="n">
         <v>0.0414962223049317</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="J18" s="23" t="n">
-        <v>0.0264489111327368</v>
+        <v>0.0264489111327367</v>
       </c>
       <c r="K18" s="23" t="n">
         <v>0.0523180466794031</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>-0.0450127465528696</v>
+        <v>-0.0450127465528694</v>
       </c>
       <c r="F20" s="23" t="n">
         <v>-0.1578709962992962</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="J20" s="23" t="n">
-        <v>0.0274993725325908</v>
+        <v>0.0274993725325907</v>
       </c>
       <c r="K20" s="23" t="n">
         <v>0.0328525399081489</v>
@@ -2497,7 +2497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2616,7 +2616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2867,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2992,7 +2992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3069,7 +3069,7 @@
         <v>-52020.4065174628</v>
       </c>
       <c r="G4" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3096,10 +3096,10 @@
         <v>0.0654822025202253</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>190313.8548415657</v>
+        <v>190313.8548415662</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3129,7 +3129,7 @@
         <v>-9463.945294567529</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3153,13 +3153,13 @@
         <v>126.1999969482422</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>-0.05397299308596093</v>
+        <v>-0.05397299308596082</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-261375.0935518565</v>
+        <v>-261375.0935518555</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3189,7 +3189,7 @@
         <v>17482.85022870218</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3219,7 +3219,7 @@
         <v>-112795.0403937409</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>-0.1061733800350263</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1153,7 +1153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1665,7 +1665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2497,7 +2497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2616,7 +2616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2867,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2992,7 +2992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2211403098513339</v>
+        <v>0.2211403098513338</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22114.03098513339</v>
+        <v>22114.03098513338</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0191938585275912</v>
@@ -984,13 +984,13 @@
         <v>424.4535822034185</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>216.4767693305947</v>
+        <v>216.4767693305948</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>198.3527119886738</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2902180977690499</v>
+        <v>0.2902180977690493</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1370,7 +1370,7 @@
         <v>401</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0205580539159817</v>
+        <v>-0.0205580539159813</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>0.019028938484348</v>
@@ -1379,7 +1379,7 @@
         <v>0.06844627048378669</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>392.7562203796913</v>
+        <v>392.7562203796915</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>408.6306043322236</v>
@@ -1439,7 +1439,7 @@
         <v>198.3527119886738</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>216.4767693305947</v>
+        <v>216.4767693305948</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>227.0649219385337</v>
@@ -1484,7 +1484,7 @@
         <v>392.25</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.08597935286307549</v>
+        <v>-0.0859793528630754</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>0.0195381803197951</v>
@@ -1547,7 +1547,7 @@
         <v>0.0417061216022127</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1388396310918183</v>
+        <v>0.1388396310918185</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>72.11869692957994</v>
@@ -1556,7 +1556,7 @@
         <v>77.50293703672203</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>84.72967029096264</v>
+        <v>84.72967029096267</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>70.68000144958496</v>
@@ -1601,10 +1601,10 @@
         <v>-0.052434175232511</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.0701777996871968</v>
+        <v>0.0701777996871966</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>269.3455856901587</v>
@@ -1613,7 +1613,7 @@
         <v>285.3170073041437</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>304.1980395610857</v>
+        <v>304.1980395610856</v>
       </c>
       <c r="K12" s="15" t="n">
         <v>269.3455856901587</v>
@@ -1655,13 +1655,13 @@
         <v>135.6000061035156</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0537067277155769</v>
+        <v>-0.0537067277155768</v>
       </c>
       <c r="F13" s="22" t="n">
         <v>-0.0194552529182879</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1090029643218295</v>
+        <v>0.1090029643218296</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>128.3173734974835</v>
@@ -1715,7 +1715,7 @@
         <v>-0.07126395669746011</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0091399766450234</v>
+        <v>-0.0091399766450236</v>
       </c>
       <c r="G14" s="22" t="n">
         <v>0.0415042015350602</v>
@@ -1724,7 +1724,7 @@
         <v>249.8299956483832</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>266.5413462824887</v>
+        <v>266.5413462824886</v>
       </c>
       <c r="J14" s="21" t="n">
         <v>280.1646302129312</v>
@@ -1799,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1893,7 +1893,7 @@
         <v>-0.0563137182802316</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.08302253368216519</v>
+        <v>0.083022533682165</v>
       </c>
       <c r="G4" s="16" t="n">
         <v>0.1737397162419263</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.0505140956902753</v>
+        <v>-0.0505140956902752</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1016597019423535</v>
+        <v>0.1016597019423537</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>0.09259259549969311</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J8" s="16" t="n">
-        <v>0.0186262496527776</v>
+        <v>0.0186262496527777</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
     </row>
     <row r="9">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.0256830236584199</v>
+        <v>-0.0256830236584196</v>
       </c>
       <c r="F9" s="24" t="n">
         <v>0.0147979643368136</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.07600211160664</v>
+        <v>-0.0760021116066399</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>-0.0193370165745856</v>
@@ -2168,7 +2168,7 @@
         <v>0.0201048370906429</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.0588821519160343</v>
+        <v>0.058882151916034</v>
       </c>
     </row>
     <row r="11">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.0152502117516968</v>
+        <v>0.0152502117516969</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.0007363095911598</v>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.0157171518226982</v>
+        <v>-0.0157171518226979</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.0635514303902599</v>
+        <v>-0.06355143039025971</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.07734808143556821</v>
+        <v>-0.07734808143556809</v>
       </c>
       <c r="H13" s="24" t="n">
         <v>-0.2330852114160289</v>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0634596530382676</v>
+        <v>-0.0634596530382678</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.094059477926595</v>
+        <v>-0.09405947792659509</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>0.2341201160407111</v>
+        <v>0.2341201160407109</v>
       </c>
       <c r="H14" s="26" t="n">
         <v>-0.222405128083297</v>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="J16" s="28" t="n">
-        <v>0.0186775555598611</v>
+        <v>0.018677555559861</v>
       </c>
       <c r="K16" s="28" t="n">
         <v>-0.0194552529182879</v>
@@ -2452,10 +2452,10 @@
         <v>-0.2030888149171456</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>0.0672181606413582</v>
+        <v>0.0672181606413584</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>-0.010546558689646</v>
+        <v>-0.0105465586896457</v>
       </c>
       <c r="H17" s="26" t="n">
         <v>0.0260650374925286</v>
@@ -2512,7 +2512,7 @@
         <v>0.0254645426742394</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>-0.0091399766450234</v>
+        <v>-0.0091399766450236</v>
       </c>
     </row>
     <row r="19">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.0316386844276283</v>
+        <v>0.0316386844276284</v>
       </c>
       <c r="K19" s="26" t="n">
         <v>0.0478184312002618</v>
@@ -2581,7 +2581,7 @@
         <v>-0.1569326977205356</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1293738284887817</v>
+        <v>-0.1293738284887816</v>
       </c>
       <c r="G20" s="26" t="n">
         <v>-0.1448316943799105</v>
@@ -2631,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2750,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3001,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3126,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3227,7 +3227,7 @@
         <v>212.3999938964844</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.07817255785017441</v>
+        <v>0.07817255785017463</v>
       </c>
       <c r="F5" s="29" t="n">
         <v>227196.4023002572</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1799,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2631,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2750,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3001,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3126,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,15 +188,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 70.95/100</t>
+          <t>Güven Puanı: 72.16/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, FROTO.IS, TUPRS.IS</t>
+          <t>AL: BIMAS.IS, GARAN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: BIMAS.IS, THYAO.IS</t>
+          <t>AZALT: KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: PGSUS.IS, TOASO.IS</t>
+          <t>ÇIK: THYAO.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2211403098513338</v>
+        <v>0.2386068933315149</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22114.03098513338</v>
+        <v>23860.68933315149</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0191938585275912</v>
+        <v>0.0190288554508686</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>424.4535822034185</v>
+        <v>454.0416082786219</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>216.4767693305948</v>
+        <v>410.4138715328373</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>198.3527119886738</v>
+        <v>382.6125</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2902180977690493</v>
+        <v>0.3805771090173714</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1958022278387909</v>
+        <v>0.1842085690247992</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19580.22278387909</v>
+        <v>18420.85690247992</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0417061216022127</v>
+        <v>0.0345887193676873</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>816.6151524228771</v>
+        <v>637.1538499122036</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>77.50293703672203</v>
+        <v>133.7723245715562</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>70.68000144958496</v>
+        <v>122.8350028991699</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.834122432044257</v>
+        <v>0.6917743873537451</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1830574623098753</v>
+        <v>0.177184537643686</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18305.74623098753</v>
+        <v>17718.4537643686</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0195381803197951</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>357.6609707494438</v>
+        <v>346.1863446361859</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>399.9138512304397</v>
+        <v>393.7966221485209</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>358.5245988394586</v>
+        <v>361.2410949552292</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.227242700359821</v>
+        <v>0.3017573994147673</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 7</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>401</v>
+        <v>402.75</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0205580539159813</v>
+        <v>-0.0181176605991072</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.019028938484348</v>
+        <v>0.0190288554508686</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.06844627048378669</v>
+        <v>0.0761518731697465</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>392.7562203796915</v>
+        <v>395.4531121937096</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>408.6306043322236</v>
+        <v>410.4138715328373</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>428.4469544639985</v>
+        <v>433.4201669191154</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>380.95</v>
+        <v>382.6125</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1420,163 +1420,163 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0647872949675653</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.0185279533884517</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0466707608184535</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>194.5242426467464</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>211.853814304798</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>217.7075182502383</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>194.5242426467464</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>-0.0514324059862513</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>0.1281139375574904</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>272.7131832789527</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>283.4648862956888</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>324.3327570477785</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>272.7131832789527</v>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>212.3999938964844</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.06613598075081251</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.0191938585275912</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.06904391931949121</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>198.3527119886738</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>216.4767693305948</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>227.0649219385337</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>198.3527119886738</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0647479742259439</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.0195381803197951</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.1094018425999727</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>361.2410949552292</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>393.7966221485209</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>428.5064617042395</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>361.2410949552292</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O11" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>392.25</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0859793528630754</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0195381803197951</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1188713720805591</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>358.5245988394586</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>399.9138512304397</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>438.8772956985994</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>358.5245988394586</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>74.40000152587891</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.030662695557949</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.0417061216022127</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.1388396310918185</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>72.11869692957994</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>77.50293703672203</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>84.72967029096267</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>70.68000144958496</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1586,64 +1586,64 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>284.25</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-0.052434175232511</v>
+        <v>-0.0492384989131554</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.0037537636029683</v>
+        <v>0.0345887193676873</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.0701777996871966</v>
+        <v>0.0882606294604084</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>269.3455856901587</v>
+        <v>122.9334649920228</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>285.3170073041437</v>
+        <v>133.7723245715562</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>304.1980395610856</v>
+        <v>140.7121027103387</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>269.3455856901587</v>
+        <v>122.8350028991699</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M12" s="14" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
       <c r="N12" s="14" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>135.6000061035156</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0537067277155768</v>
+        <v>-0.0668953740197302</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.0194552529182879</v>
+        <v>-0.0118534116209535</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1090029643218296</v>
+        <v>0.0872554009436483</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>128.3173734974835</v>
+        <v>19.18463061182271</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>132.9618736890503</v>
+        <v>20.31629332934598</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>150.380808730857</v>
+        <v>22.35397046274438</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>128.3173734974835</v>
+        <v>18.94285522134967</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,78 +1681,21 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>269</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.07126395669746011</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.0091399766450236</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>0.0415042015350602</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>249.8299956483832</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>266.5413462824886</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>280.1646302129312</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>249.8299956483832</v>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif</t>
-        </is>
-      </c>
-      <c r="O14" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O14"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1782,7 +1725,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1799,7 +1742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1886,20 +1829,20 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.0563137182802316</v>
+        <v>-0.0577058518103443</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.083022533682165</v>
+        <v>0.0826626225903697</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1737397162419263</v>
+        <v>0.1883204288765572</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.0605774813729588</v>
+        <v>-0.06586916356473491</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -1907,10 +1850,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0191290724367972</v>
+        <v>0.0191282031761057</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.019028938484348</v>
+        <v>0.0190288554508686</v>
       </c>
     </row>
     <row r="5">
@@ -1929,117 +1872,117 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>-0.0726705431564196</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.0861618798955614</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.0941609327815446</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.0526104301604252</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0209519991267496</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.0185279533884517</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>-0.039264828738513</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>-0.1379310344827586</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>-0.0154109589041095</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>-0.1744791215756487</v>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>0.0183342111248289</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.0505140956902752</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.1016597019423537</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.09259259549969311</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0485430687963439</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0207860298554876</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0191938585275912</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>-0.036139677786054</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.4954275911945411</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.5566438543758887</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.1962484737015959</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="E7" s="16" t="n">
+        <v>-0.0565768126863727</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.4656911172793534</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.5121985635198514</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>-0.2247959256692422</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.0280355349385904</v>
-      </c>
-      <c r="K6" s="19" t="n">
+      <c r="J7" s="16" t="n">
+        <v>0.0281724471412737</v>
+      </c>
+      <c r="K7" s="16" t="n">
         <v>0.0195381803197951</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.1137581390056649</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>-0.09046456295602651</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>-0.2589641394905586</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>-0.0586189602200157</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0186206047020004</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.0417061216022127</v>
       </c>
     </row>
     <row r="8">
@@ -2048,7 +1991,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -2058,20 +2001,20 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0556478405315614</v>
+        <v>-0.0307345654596361</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.1748911465892597</v>
+        <v>0.0205209642157904</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>-0.0437342304457527</v>
+        <v>0.0173092415739459</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>-0.1639114710894957</v>
+        <v>-0.1191133144180434</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -2079,10 +2022,10 @@
         </is>
       </c>
       <c r="J8" s="16" t="n">
-        <v>0.0186262496527777</v>
+        <v>0.0220829823689621</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.0037537636029683</v>
+        <v>0.0345887193676873</v>
       </c>
     </row>
     <row r="9">
@@ -2091,12 +2034,12 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -2105,27 +2048,27 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.0256830236584196</v>
+        <v>-0.08852258687332409</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.0147979643368136</v>
+        <v>-0.08461068384632239</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.0147979643368136</v>
+        <v>-0.2280247788856223</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.1384289250641028</v>
+        <v>-0.0749760335276649</v>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.0263431621899088</v>
+        <v>0.0186285784449945</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.0012391857819089</v>
+        <v>0.1028056950580804</v>
       </c>
     </row>
     <row r="10">
@@ -2134,7 +2077,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -2148,27 +2091,27 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.0760021116066399</v>
+        <v>-0.0425859380940586</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>-0.0193370165745856</v>
+        <v>-0.0866373192033314</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.0326975476839237</v>
+        <v>0.3116310491927303</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.07408657888789739</v>
+        <v>-0.2316984786697485</v>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.0201048370906429</v>
+        <v>0.0256941804933773</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.058882151916034</v>
+        <v>0.019070255160478</v>
       </c>
     </row>
     <row r="11">
@@ -2177,7 +2120,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -2191,16 +2134,16 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.0431869167532524</v>
+        <v>-0.0300196404347403</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.003875968992248</v>
+        <v>-0.0958715316352494</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.0140648416890173</v>
+        <v>-0.060533826327491</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.1007340676179966</v>
+        <v>-0.2407365854282926</v>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
@@ -2208,10 +2151,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.0221911300146039</v>
+        <v>0.020549051226188</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.0265059178623019</v>
+        <v>0.0034066979194351</v>
       </c>
     </row>
     <row r="12">
@@ -2234,16 +2177,16 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.1561844998696046</v>
+        <v>-0.1491043340185853</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.1860465241859903</v>
+        <v>-0.1717948717948717</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.2708333434114132</v>
+        <v>-0.244621152035703</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.0268120563432003</v>
+        <v>0.0108941768229855</v>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
@@ -2251,10 +2194,10 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.0152502117516969</v>
+        <v>0.0152042217780923</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.0007363095911598</v>
+        <v>0.0318627708566732</v>
       </c>
     </row>
     <row r="13">
@@ -2263,7 +2206,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -2277,16 +2220,16 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.0157171518226979</v>
+        <v>-0.020994533707539</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.06355143039025971</v>
+        <v>0.0392961939163964</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.07734808143556809</v>
+        <v>0.0320325704494266</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.2330852114160289</v>
+        <v>-0.1457413007169843</v>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
@@ -2294,10 +2237,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.0206102435815252</v>
+        <v>0.0260744241772801</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.0124594158070348</v>
+        <v>0.0653045409271195</v>
       </c>
     </row>
     <row r="14">
@@ -2306,7 +2249,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -2320,27 +2263,27 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0634596530382678</v>
+        <v>-0.0589459097079656</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.09405947792659509</v>
+        <v>0.0029563480226335</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>0.2341201160407109</v>
+        <v>-0.0202166285325473</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>-0.222405128083297</v>
+        <v>0.0018435798894262</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.0256071566045418</v>
+        <v>0.0239007500913969</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0.0190703728875496</v>
+        <v>0.0111110916693351</v>
       </c>
     </row>
     <row r="15">
@@ -2349,7 +2292,7 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -2363,16 +2306,16 @@
         </is>
       </c>
       <c r="E15" s="26" t="n">
-        <v>-0.06579843212013919</v>
+        <v>-0.1191983405906471</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>-0.0087272505326704</v>
+        <v>-0.063901313265174</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>-0.0305832351713553</v>
+        <v>-0.0649496400173262</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>0.0331064851884299</v>
+        <v>0.0009450280090033001</v>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -2380,53 +2323,53 @@
         </is>
       </c>
       <c r="J15" s="26" t="n">
-        <v>0.0239822715859189</v>
+        <v>0.0213692066505879</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>0.0111110916693351</v>
+        <v>0.048351558995445</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>-0.1234647137783514</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <v>-0.2032901966223208</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>-0.2399102536842193</v>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>-0.102048370776654</v>
-      </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.123287728499864</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.1874244325510758</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.2320000348772322</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>-0.09256794568438829</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n">
-        <v>0.018677555559861</v>
-      </c>
-      <c r="K16" s="28" t="n">
-        <v>-0.0194552529182879</v>
+      <c r="J16" s="26" t="n">
+        <v>0.0184209265016707</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2435,127 +2378,127 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.0885640584694754</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-0.12106135986733</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>0.0515873015873016</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>-0.1698261549468688</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.0255179500222131</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.009805545465515699</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.1185696361355082</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.00354609929078</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>0.027046783625731</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0.0102367776137011</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.0310769985189652</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.1070429210315777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.2030888149171456</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>0.0672181606413584</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.0105465586896457</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0.0260650374925286</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0394224350412246</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.07582576484113181</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="28" t="n">
-        <v>-0.081127241673783</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>-0.1114781172584641</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>0.0112781954887217</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>-0.1670440637480758</v>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="n">
-        <v>0.0254645426742394</v>
-      </c>
-      <c r="K18" s="28" t="n">
-        <v>-0.0091399766450236</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>-0.1330018645121193</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>-0.0574324324324324</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>0.03486646884273</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>-0.0046009331250927</v>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.0316386844276284</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>0.0478184312002618</v>
+      <c r="E19" s="28" t="n">
+        <v>-0.1769415595392859</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>0.0383838514225449</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>-0.062043823248996</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>-0.07030959147250811</v>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>0.0393274388764336</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>-0.0118534116209535</v>
       </c>
     </row>
     <row r="20">
@@ -2578,16 +2521,16 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.1569326977205356</v>
+        <v>-0.1366318717686869</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1293738284887816</v>
+        <v>-0.1182197159544896</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-0.1448316943799105</v>
+        <v>-0.1202191379963973</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>-0.0441114367350677</v>
+        <v>-0.0841787164039297</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -2595,10 +2538,10 @@
         </is>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.0269505186174669</v>
+        <v>0.0269596069705385</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.0809523100911218</v>
+        <v>0.1001577768561146</v>
       </c>
     </row>
   </sheetData>
@@ -2623,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2631,7 +2574,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2656,7 +2599,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TUPRS.IS, FROTO.IS</t>
+          <t>BIMAS.IS, TUPRS.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2611,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, THYAO.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2623,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PGSUS.IS, TOASO.IS</t>
+          <t>THYAO.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2635,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, SAHOL.IS, GARAN.IS, ARCLK.IS, TCELL.IS, EREGL.IS, AKBNK.IS, PETKM.IS, ASELS.IS, SISE.IS</t>
+          <t>FROTO.IS, EREGL.IS, TCELL.IS, ARCLK.IS, YKBNK.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2647,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.92 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2685,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2750,7 +2693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2811,7 +2754,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2778,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2790,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2802,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2936,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3001,7 +2944,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3025,7 +2968,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12266</v>
+        <v>12150.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3035,7 +2978,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13602.73352050781</v>
+        <v>13606.9315234375</v>
       </c>
     </row>
     <row r="6">
@@ -3069,7 +3012,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
     </row>
     <row r="9">
@@ -3103,7 +3046,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -3112,7 +3055,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3126,7 +3069,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3194,19 +3137,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>348.75</v>
+        <v>351.25</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>-0.1270337922403004</v>
+        <v>-0.1207759699624531</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>-89492.73324614356</v>
+        <v>-85084.2242192399</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="5">
@@ -3224,19 +3167,19 @@
         <v>197</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>212.3999938964844</v>
+        <v>208</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.07817255785017463</v>
+        <v>0.05583756345177671</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>227196.4023002572</v>
+        <v>162283.208818242</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="6">
@@ -3254,19 +3197,19 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>88.75</v>
+        <v>83.5</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.0803108808290155</v>
+        <v>-0.1347150259067358</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-7052.458199202025</v>
+        <v>-11829.92988253244</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="7">
@@ -3284,19 +3227,19 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>128.5</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.03673159011001659</v>
+        <v>-0.03073456545963615</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-177880.1258255821</v>
+        <v>-148838.3256695392</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="8">
@@ -3314,19 +3257,19 @@
         <v>405.5</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>401</v>
+        <v>402.75</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.01109741060419234</v>
+        <v>-0.006781750924784169</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-31469.13041166309</v>
+        <v>-19231.13525157189</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="9">
@@ -3344,19 +3287,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>74.40000152587891</v>
+        <v>74.65000152587891</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>-0.03875968915836447</v>
+        <v>-0.03552971506183411</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>-173530.4240112733</v>
+        <v>-159069.555343667</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="10">
@@ -3374,19 +3317,19 @@
         <v>387</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>392.25</v>
+        <v>386.25</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>0.01356589147286824</v>
+        <v>-0.001937984496124034</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>58578.40995691251</v>
+        <v>-8368.344279558398</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,7 +157,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -211,10 +211,10 @@
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 72.16/100</t>
+          <t>Güven Puanı: 76.06/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, GARAN.IS, TUPRS.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS</t>
+          <t>AZALT: YKBNK.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, PETKM.IS</t>
+          <t>ÇIK: THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2386068933315149</v>
+        <v>0.2224992347307692</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>23860.68933315149</v>
+        <v>22249.92347307692</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0190288554508686</v>
+        <v>0.019028938484348</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>454.0416082786219</v>
+        <v>423.3924250506313</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>410.4138715328373</v>
+        <v>404.044974109044</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>382.6125</v>
+        <v>376.675</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805771090173714</v>
+        <v>0.3805787696869603</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1842085690247992</v>
+        <v>0.2084179173556735</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18420.85690247992</v>
+        <v>20841.79173556735</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0345887193676873</v>
+        <v>0.018527596735292</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>637.1538499122036</v>
+        <v>386.1483125175334</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>133.7723245715562</v>
+        <v>210.7333535479328</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>122.8350028991699</v>
+        <v>193.4955029631254</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6917743873537451</v>
+        <v>0.2859757726351672</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.177184537643686</v>
+        <v>0.1690828479135573</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17718.4537643686</v>
+        <v>16908.28479135573</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0195381803197951</v>
+        <v>0.0195382798743581</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>346.1863446361859</v>
+        <v>330.3588004488608</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>393.7966221485209</v>
+        <v>392.2673531816593</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>361.2410949552292</v>
+        <v>351.8320840903206</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3017573994147673</v>
+        <v>0.2283666196330747</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1367,28 +1367,28 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>402.75</v>
+        <v>396.5</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0181176605991072</v>
+        <v>-0.0339317012120768</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0190288554508686</v>
+        <v>0.019028938484348</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0761518731697465</v>
+        <v>0.07229912231651719</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>395.4531121937096</v>
+        <v>383.0460804694115</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>410.4138715328373</v>
+        <v>404.044974109044</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>433.4201669191154</v>
+        <v>425.1666019984991</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>382.6125</v>
+        <v>376.675</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>72.16</v>
+        <v>76.06</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1410,114 +1410,114 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>208</v>
-      </c>
-      <c r="E9" s="19" t="n">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>206.8999938964844</v>
+      </c>
+      <c r="E9" s="16" t="n">
         <v>-0.0647872949675653</v>
       </c>
-      <c r="F9" s="19" t="n">
-        <v>0.0185279533884517</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.0466707608184535</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>194.5242426467464</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>211.853814304798</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>217.7075182502383</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>194.5242426467464</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="F9" s="16" t="n">
+        <v>0.018527596735292</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.0466708728798923</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>193.4955029631254</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>210.7333535479328</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>216.5561972104777</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>193.4955029631254</v>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="14" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="21" t="n">
-        <v>287.5</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-0.0514324059862513</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>-0.0140351781019522</v>
-      </c>
-      <c r="G10" s="22" t="n">
+      <c r="D10" s="18" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.0628618693134822</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>-0.0241174841137557</v>
+      </c>
+      <c r="G10" s="19" t="n">
         <v>0.1281139375574904</v>
       </c>
-      <c r="H10" s="21" t="n">
-        <v>272.7131832789527</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>283.4648862956888</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>324.3327570477785</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>272.7131832789527</v>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="H10" s="18" t="n">
+        <v>267.7872208436725</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>278.8584289144943</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>322.3585576570529</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>267.7872208436725</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="20" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="M10" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="20" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
@@ -1538,28 +1538,28 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>386.25</v>
+        <v>384.75</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0647479742259439</v>
+        <v>-0.0855566365423768</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0195381803197951</v>
+        <v>0.0195382798743581</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.1094018425999727</v>
+        <v>0.1009766152812969</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>361.2410949552292</v>
+        <v>351.8320840903206</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>393.7966221485209</v>
+        <v>392.2673531816593</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>428.5064617042395</v>
+        <v>423.600752729479</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>361.2410949552292</v>
+        <v>351.8320840903206</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="M11" s="14" t="n">
-        <v>72.16</v>
+        <v>76.06</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1581,121 +1581,235 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>129.3000030517578</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0492384989131554</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.0345887193676873</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.0882606294604084</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>122.9334649920228</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>133.7723245715562</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>140.7121027103387</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>122.8350028991699</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>35.70000076293945</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.053387959227386</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.0895632063722737</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>33.79405057778999</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>35.74423969629903</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>38.89740729876093</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>33.79405057778999</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.0476629979133642</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-0.0123915741984644</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.1088380129700114</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>75.90125616000299</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>78.71238852244066</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>88.37438624980484</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>75.71499710083008</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>259.25</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.1122727836453332</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>-0.0351689285600669</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.0835562048104195</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>230.1432808399474</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>250.1324552708026</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>280.9119460971012</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>230.1432808399474</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
-        <v>20.55999946594238</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0668953740197302</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.0872554009436483</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>19.18463061182271</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>20.31629332934598</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>22.35397046274438</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>18.94285522134967</v>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="D15" s="18" t="n">
+        <v>341.75</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.0977678549854652</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>-0.005529134834197</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1083753514763447</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>308.3378355587172</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>339.8604181704131</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>378.7872763670408</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>308.3378355587172</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="20" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+      <c r="M15" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1725,7 +1839,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1742,7 +1856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1833,16 +1947,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.0577058518103443</v>
+        <v>-0.0824642322042362</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.0826626225903697</v>
+        <v>0.0374477363977292</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1883204288765572</v>
+        <v>0.103857588951256</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.06586916356473491</v>
+        <v>-0.06741185359372349</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -1850,96 +1964,96 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0191282031761057</v>
+        <v>0.0189524792403736</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0190288554508686</v>
+        <v>0.019028938484348</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.0726705431564196</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.0861618798955614</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.0941609327815446</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0526104301604252</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>-0.0824833973548364</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.082679159017976</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0.0273088389606748</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>-0.0597960627732419</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0209519991267496</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0185279533884517</v>
+      <c r="J5" s="16" t="n">
+        <v>0.0209647836935707</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>0.018527596735292</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="22" t="n">
-        <v>-0.039264828738513</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>-0.1379310344827586</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>-0.0154109589041095</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>-0.1744791215756487</v>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="E6" s="19" t="n">
+        <v>-0.048293089092423</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>-0.1234662576687116</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.0985804416403786</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.1838035473419896</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="22" t="n">
-        <v>0.0183342111248289</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>-0.0140351781019522</v>
+      <c r="J6" s="19" t="n">
+        <v>0.018156884273008</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>-0.0241174841137557</v>
       </c>
     </row>
     <row r="7">
@@ -1962,16 +2076,16 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-0.0565768126863727</v>
+        <v>-0.0528542750964556</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.4656911172793534</v>
+        <v>0.4465180215722137</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.5121985635198514</v>
+        <v>0.5603375976000915</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>-0.2247959256692422</v>
+        <v>-0.2244550284745238</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -1979,53 +2093,53 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0281724471412737</v>
+        <v>0.028200042319893</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0195381803197951</v>
+        <v>0.0195382798743581</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0307345654596361</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0205209642157904</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.0173092415739459</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>-0.1191133144180434</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>0.0220829823689621</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.0345887193676873</v>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>-0.0272479558368244</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0.0512367999227174</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>-0.0490143875256759</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>-0.1525930514087783</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0.0260785342604604</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>0.0012391857819089</v>
       </c>
     </row>
     <row r="9">
@@ -2034,12 +2148,12 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -2048,27 +2162,27 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.08852258687332409</v>
+        <v>-0.0456853548743018</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>-0.08461068384632239</v>
+        <v>-0.1021968119588387</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.2280247788856223</v>
+        <v>0.2884126747282864</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.0749760335276649</v>
+        <v>-0.246774969672824</v>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.0186285784449945</v>
+        <v>0.0255018791340404</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.1028056950580804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2191,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -2091,27 +2205,27 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.0425859380940586</v>
+        <v>-0.0327868405107442</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>-0.0866373192033314</v>
+        <v>0.0069822280674132</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.3116310491927303</v>
+        <v>-0.0559999778053977</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.2316984786697485</v>
+        <v>-0.1419483389452992</v>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.0256941804933773</v>
+        <v>0.021982568542005</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.019070255160478</v>
+        <v>0.0426715939840771</v>
       </c>
     </row>
     <row r="11">
@@ -2120,84 +2234,84 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>-0.1086300563157068</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.0888341061879893</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>-0.2745579935142653</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>-0.0764441679740844</v>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>0.0186569658567114</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.102805642445124</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>-0.0300196404347403</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>-0.0958715316352494</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>-0.060533826327491</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>-0.2407365854282926</v>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.1680585134722519</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>-0.1863195565962446</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>-0.2877569628110316</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>-0.0044326364510109</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="24" t="n">
-        <v>0.020549051226188</v>
-      </c>
-      <c r="K11" s="24" t="n">
-        <v>0.0034066979194351</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>-0.1491043340185853</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>-0.1717948717948717</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>-0.244621152035703</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>0.0108941768229855</v>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>0.0152042217780923</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>0.0318627708566732</v>
+      <c r="J12" s="19" t="n">
+        <v>0.0152262854483399</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>-0.0123915741984644</v>
       </c>
     </row>
     <row r="13">
@@ -2206,7 +2320,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -2220,16 +2334,16 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.020994533707539</v>
+        <v>-0.0598349196247974</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.0392961939163964</v>
+        <v>-0.010853835261384</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.0320325704494266</v>
+        <v>-0.0976897891205136</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.1457413007169843</v>
+        <v>-0.0288025021689304</v>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
@@ -2237,10 +2351,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.0260744241772801</v>
+        <v>0.0237657020847789</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.0653045409271195</v>
+        <v>0.0111110916693351</v>
       </c>
     </row>
     <row r="14">
@@ -2249,7 +2363,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -2263,16 +2377,16 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0589459097079656</v>
+        <v>-0.1149003591499333</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>0.0029563480226335</v>
+        <v>-0.0570150771170184</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.0202166285325473</v>
+        <v>-0.12454592828274</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.0018435798894262</v>
+        <v>0.0117628907218287</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -2280,10 +2394,10 @@
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.0239007500913969</v>
+        <v>0.0214095607902122</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0.0111110916693351</v>
+        <v>0.0483517655572096</v>
       </c>
     </row>
     <row r="15">
@@ -2292,7 +2406,7 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -2306,16 +2420,16 @@
         </is>
       </c>
       <c r="E15" s="26" t="n">
-        <v>-0.1191983405906471</v>
+        <v>-0.0621986223534939</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>-0.063901313265174</v>
+        <v>-0.1175135871766351</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>-0.0649496400173262</v>
+        <v>-0.1254496162867269</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>0.0009450280090033001</v>
+        <v>-0.28242131227121</v>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -2323,10 +2437,10 @@
         </is>
       </c>
       <c r="J15" s="26" t="n">
-        <v>0.0213692066505879</v>
+        <v>0.0205397708069739</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>0.048351558995445</v>
+        <v>0.0124595339704571</v>
       </c>
     </row>
     <row r="16">
@@ -2349,16 +2463,16 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.123287728499864</v>
+        <v>-0.1381323182445148</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>-0.1874244325510758</v>
+        <v>-0.1993976271296121</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-0.2320000348772322</v>
+        <v>-0.2854839037823421</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>-0.09256794568438829</v>
+        <v>-0.1118784227705204</v>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
@@ -2366,7 +2480,7 @@
         </is>
       </c>
       <c r="J16" s="26" t="n">
-        <v>0.0184209265016707</v>
+        <v>0.0184277553287016</v>
       </c>
       <c r="K16" s="26" t="n">
         <v>0</v>
@@ -2378,84 +2492,84 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.1782819920633277</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>0.0346938924459749</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-0.0249999312254073</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>-0.1010948896538656</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.0393464526538943</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.0706630475858574</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.0885640584694754</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>-0.12106135986733</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>0.0515873015873016</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.1698261549468688</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>-0.1351125938281902</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.1211864406779661</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>-0.0442396313364055</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.2157061124078084</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0255179500222131</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.009805545465515699</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.1185696361355082</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.00354609929078</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>0.027046783625731</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.0102367776137011</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.0310769985189652</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.1070429210315777</v>
+      <c r="J18" s="28" t="n">
+        <v>0.0255197014582361</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>-0.0351689285600669</v>
       </c>
     </row>
     <row r="19">
@@ -2464,7 +2578,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
@@ -2478,27 +2592,27 @@
         </is>
       </c>
       <c r="E19" s="28" t="n">
-        <v>-0.1769415595392859</v>
+        <v>-0.1320634920634921</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>0.0383838514225449</v>
+        <v>-0.0193687230989957</v>
       </c>
       <c r="G19" s="28" t="n">
-        <v>-0.062043823248996</v>
+        <v>-0.0565907522429262</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>-0.07030959147250811</v>
+        <v>0.0129751276111689</v>
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J19" s="28" t="n">
-        <v>0.0393274388764336</v>
+        <v>0.0312353919675467</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>-0.0118534116209535</v>
+        <v>-0.005529134834197</v>
       </c>
     </row>
     <row r="20">
@@ -2521,16 +2635,16 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.1366318717686869</v>
+        <v>-0.1640729467145814</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1182197159544896</v>
+        <v>-0.1376146837152142</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-0.1202191379963973</v>
+        <v>-0.1843966326020115</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>-0.0841787164039297</v>
+        <v>-0.1831940100157078</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -2538,10 +2652,10 @@
         </is>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.0269596069705385</v>
+        <v>0.0269414901477214</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.1001577768561146</v>
+        <v>0.0597309519640328</v>
       </c>
     </row>
   </sheetData>
@@ -2566,7 +2680,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2574,7 +2688,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2599,7 +2713,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TUPRS.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2725,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2737,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, PETKM.IS</t>
+          <t>THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2749,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, EREGL.IS, TCELL.IS, ARCLK.IS, YKBNK.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
+          <t>EREGL.IS, GARAN.IS, FROTO.IS, AKBNK.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2761,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2799,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2693,7 +2807,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2790,7 +2904,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2916,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2936,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2944,7 +3058,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2968,7 +3082,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12150.7001953125</v>
+        <v>12250.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -2978,7 +3092,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13606.9315234375</v>
+        <v>13611.73302246094</v>
       </c>
     </row>
     <row r="6">
@@ -3012,7 +3126,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>72.16</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="9">
@@ -3039,7 +3153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3049,13 +3163,13 @@
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3069,7 +3183,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3125,215 +3239,185 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>399.5</v>
+        <v>197</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>351.25</v>
+        <v>206.8999938964844</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>-0.1207759699624531</v>
+        <v>0.05025377612428628</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>-85084.2242192399</v>
+        <v>146054.7978911358</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>197</v>
+        <v>96.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>208</v>
+        <v>84.34999847412109</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.05583756345177671</v>
+        <v>-0.1259067515635119</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>162283.208818242</v>
+        <v>-11056.43585567767</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>96.5</v>
+        <v>133.3999938964844</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>83.5</v>
+        <v>129.8000030517578</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.1347150259067358</v>
+        <v>-0.02698643935111478</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-11829.92988253244</v>
+        <v>-130687.2698127953</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>133.3999938964844</v>
+        <v>405.5</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>129.3000030517578</v>
+        <v>396.5</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.03073456545963615</v>
+        <v>-0.02219482120838467</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-148838.3256695392</v>
+        <v>-62938.26082332665</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>405.5</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>402.75</v>
+        <v>73.84999847412109</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.006781750924784169</v>
+        <v>-0.04586567159912602</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-19231.13525157189</v>
+        <v>-205344.5116042821</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>77.40000152587891</v>
+        <v>387</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>74.65000152587891</v>
+        <v>384.75</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>-0.03552971506183411</v>
+        <v>-0.005813953488372103</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>-159069.555343667</v>
+        <v>-25105.03283867612</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.1049328663164039</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>387</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>386.25</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>-0.001937984496124034</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>-8368.344279558398</v>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>19902071.12003835</v>
-      </c>
-      <c r="H10" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H10"/>
+  <autoFilter ref="A3:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -99,11 +99,6 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -158,9 +153,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,12 +201,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -599,7 +585,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -624,7 +610,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +678,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 76.06/100</t>
+          <t>Güven Puanı: 80.91/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +738,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -786,7 +772,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
+          <t>ÇIK: THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -972,25 +958,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2224992347307692</v>
+        <v>0.2298474453949678</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22249.92347307692</v>
+        <v>22984.74453949678</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.019028938484348</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>423.3924250506313</v>
+        <v>898.1864427738836</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>404.044974109044</v>
+        <v>427.3206234500898</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>376.675</v>
+        <v>390.6875</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805787696869603</v>
+        <v>0.781550076600111</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1015,25 +1001,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2084179173556735</v>
+        <v>0.1890962006107245</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20841.79173556735</v>
+        <v>18909.62006107245</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.018527596735292</v>
+        <v>0.0185277170790933</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>386.1483125175334</v>
+        <v>350.3520905646974</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>210.7333535479328</v>
+        <v>216.4371398793074</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>193.4955029631254</v>
+        <v>201.875</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2859757726351672</v>
+        <v>0.3705543415818685</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1047,7 +1033,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,62 +1042,62 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1690828479135573</v>
+        <v>0.1810563539943076</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>16908.28479135573</v>
+        <v>18105.63539943076</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0195382798743581</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>330.3588004488608</v>
+        <v>599.6122234998426</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>392.2673531816593</v>
+        <v>135.6483225135468</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>351.8320840903206</v>
+        <v>123.815263377019</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2283666196330747</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.5809580093299256</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>39999.99999999999</v>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000.00000000001</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1129,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1201,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1353,463 +1339,349 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>396.5</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0339317012120768</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.019028938484348</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.07229912231651719</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>383.0460804694115</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>404.044974109044</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>425.1666019984991</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>376.675</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="D8" s="14" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0205581560241685</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0390775038300055</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.0814230337123209</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>402.7954583350607</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>427.3206234500898</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>444.735222614192</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>390.6875</v>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="M8" s="13" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>206.8999938964844</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.0647872949675653</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.018527596735292</v>
-      </c>
-      <c r="G9" s="16" t="n">
+      <c r="D9" s="14" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0302466271968858</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.0185277170790933</v>
+      </c>
+      <c r="G9" s="15" t="n">
         <v>0.0466708728798923</v>
       </c>
-      <c r="H9" s="15" t="n">
-        <v>193.4955029631254</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>210.7333535479328</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>216.5561972104777</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>193.4955029631254</v>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="n">
+        <v>206.0725917206618</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>216.4371398793074</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>222.4175604869771</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>201.875</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="14" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="M9" s="13" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="14" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>131.3000030517578</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0570048705314075</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.0795559387098858</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>123.815263377019</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>135.6483225135468</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>141.7456980471513</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>123.815263377019</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>285.75</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0628618693134822</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1281139375574904</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>267.7872208436725</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>278.8584289144943</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>322.3585576570529</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>267.7872208436725</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="D11" s="17" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0553651563181906</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>-0.0341997901255592</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.1114960523971878</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>270.4017240039179</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>276.4603100765587</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>318.165744998695</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>270.4017240039179</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M11" s="16" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>384.75</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0855566365423768</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0195382798743581</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.1009766152812969</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>351.8320840903206</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>392.2673531816593</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>423.600752729479</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>351.8320840903206</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>36.41999816894531</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.053387959227386</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.1033217154246511</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>34.47560879164018</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>36.46512931285342</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>40.18297485552339</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>34.47560879164018</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="14" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
+      <c r="M12" s="19" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>35.70000076293945</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.053387959227386</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.0895632063722737</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>33.79405057778999</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>35.74423969629903</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>38.89740729876093</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>33.79405057778999</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>78.40000152587891</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.0445633254802306</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.0772325318535918</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>74.9062367402306</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>77.07198604420731</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>84.45503214104799</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>74.48000144958496</v>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="20" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>79.69999694824219</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.0476629979133642</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.0123915741984644</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.1088380129700114</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>75.90125616000299</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>78.71238852244066</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>88.37438624980484</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>75.71499710083008</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="M13" s="16" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>259.25</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.1122727836453332</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>-0.0351689285600669</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.0835562048104195</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>230.1432808399474</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>250.1324552708026</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>280.9119460971012</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>230.1432808399474</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>341.75</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0977678549854652</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>-0.005529134834197</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1083753514763447</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>308.3378355587172</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>339.8604181704131</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>378.7872763670408</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>308.3378355587172</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1839,7 +1711,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1856,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1928,734 +1800,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>-0.0824642322042362</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.0374477363977292</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.103857588951256</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>-0.06741185359372349</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="n">
+        <v>-0.0372591422531518</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.0441335285670299</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.1255556536498179</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>-0.0492395802835036</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>0.0191384637845102</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>0.0390775038300055</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0576496674057649</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.0786802030456852</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.06462922596201839</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>-0.0576587433953539</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0189524792403736</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.019028938484348</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="J5" s="15" t="n">
+        <v>0.0208840053323224</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.0185277170790933</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
-        <v>-0.0824833973548364</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>0.082679159017976</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0.0273088389606748</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>-0.0597960627732419</v>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="E6" s="15" t="n">
+        <v>-0.0194174082392906</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.0202020681054191</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>-0.039502516584027</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-0.1369664216105703</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="16" t="n">
-        <v>0.0209647836935707</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>0.018527596735292</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="J6" s="15" t="n">
+        <v>0.0220263134795572</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
-        <v>-0.048293089092423</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>-0.1234662576687116</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>-0.0985804416403786</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.1838035473419896</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="E7" s="18" t="n">
+        <v>-0.0313028764805414</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>-0.1325757575757575</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>-0.1040688575899843</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.1936358141344232</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.018156884273008</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="J7" s="18" t="n">
+        <v>0.0180723854988791</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>-0.0341997901255592</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>-0.0060044002283821</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>0.08651544366282859</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>-0.0324123602679612</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>-0.1255658644328388</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0.0261239227485806</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0528542750964556</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.4465180215722137</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.5603375976000915</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>-0.2244550284745238</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>-0.0555317409253494</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0.3717472667621082</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>0.539853563379223</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>-0.2309781767799872</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>0.028200042319893</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.0195382798743581</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="J9" s="23" t="n">
+        <v>0.0274366815632304</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0195382818194833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>-0.1113149660442947</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>-0.139218006961732</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>-0.2891389070914403</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>-0.0627516685691355</v>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>0.0179308105833148</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>0.102805769808545</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>-0.0272479558368244</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.0512367999227174</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>-0.0490143875256759</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>-0.1525930514087783</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>-0.0288086380242014</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.1136363667271895</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1306818564530771</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>-0.2821456295959658</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>0.0206173299279643</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.0124595339704571</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>-0.0411735013815761</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>-0.1543350621836327</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.2547050709559768</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>-0.2495341591699014</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="22" t="n">
-        <v>0.0260785342604604</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="J12" s="23" t="n">
+        <v>0.0245820513339388</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0.029948947983406</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.1690513747344368</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.2068790820831018</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>-0.3086419711556413</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>0.0004404513674984</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0.0152318656113831</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
-        <v>-0.0456853548743018</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>-0.1021968119588387</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0.2884126747282864</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>-0.246774969672824</v>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>0.0255018791340404</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="E14" s="25" t="n">
+        <v>-0.0523777104329941</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>0.0021866112130526</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.0869854287689156</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0241364620182464</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.023757732105983</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.0111110916693351</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n">
-        <v>-0.0327868405107442</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0.0069822280674132</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.0559999778053977</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>-0.1419483389452992</v>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="E15" s="25" t="n">
+        <v>-0.09794624245678241</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.0514950317688653</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>-0.1219887355571381</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.0276953346162978</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="24" t="n">
-        <v>0.021982568542005</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0.0426715939840771</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="J15" s="25" t="n">
+        <v>0.0214678685986214</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.0483516300336255</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
-        <v>-0.1086300563157068</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>-0.0888341061879893</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>-0.2745579935142653</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>-0.0764441679740844</v>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="E16" s="25" t="n">
+        <v>-0.153256699007633</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.2093022747970567</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.2844036485715657</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.1628946465915355</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="24" t="n">
-        <v>0.0186569658567114</v>
-      </c>
-      <c r="K11" s="24" t="n">
-        <v>0.102805642445124</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0183461054684322</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0073660782405308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.1680585134722519</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>-0.1863195565962446</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>-0.2877569628110316</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>-0.0044326364510109</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>-0.1174979165077881</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>0.0126090354486556</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.0242990872445344</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>-0.1072208885749907</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.0389793391056107</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.07582576484113181</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.08355321020228661</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.1459016393442622</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.0612612612612613</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.2255174654706502</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="19" t="n">
-        <v>0.0152262854483399</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>-0.0123915741984644</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="J18" s="25" t="n">
+        <v>0.0251248630786822</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0532805395405533</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n">
-        <v>-0.0598349196247974</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>-0.010853835261384</v>
-      </c>
-      <c r="G13" s="24" t="n">
-        <v>-0.0976897891205136</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>-0.0288025021689304</v>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="E19" s="25" t="n">
+        <v>-0.0583892617449663</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.0049645390070921</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.0690112806901127</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>0.0091218873182385</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="24" t="n">
-        <v>0.0237657020847789</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>0.0111110916693351</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="J19" s="25" t="n">
+        <v>0.031377917776001</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0478181869880385</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.1149003591499333</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.0570150771170184</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>-0.12454592828274</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.0117628907218287</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="E20" s="25" t="n">
+        <v>-0.1295955728475251</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1582221984863281</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1733665773215752</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.1990612037864825</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0214095607902122</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.0483517655572096</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>-0.0621986223534939</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>-0.1175135871766351</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>-0.1254496162867269</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>-0.28242131227121</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="26" t="n">
-        <v>0.0205397708069739</v>
-      </c>
-      <c r="K15" s="26" t="n">
-        <v>0.0124595339704571</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>-0.1381323182445148</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.1993976271296121</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.2854839037823421</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>-0.1118784227705204</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.0184277553287016</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.1782819920633277</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>0.0346938924459749</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.0249999312254073</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.1010948896538656</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0393464526538943</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.0706630475858574</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="n">
-        <v>-0.1351125938281902</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>-0.1211864406779661</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>-0.0442396313364055</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>-0.2157061124078084</v>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="n">
-        <v>0.0255197014582361</v>
-      </c>
-      <c r="K18" s="28" t="n">
-        <v>-0.0351689285600669</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="n">
-        <v>-0.1320634920634921</v>
-      </c>
-      <c r="F19" s="28" t="n">
-        <v>-0.0193687230989957</v>
-      </c>
-      <c r="G19" s="28" t="n">
-        <v>-0.0565907522429262</v>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>0.0129751276111689</v>
-      </c>
-      <c r="I19" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="28" t="n">
-        <v>0.0312353919675467</v>
-      </c>
-      <c r="K19" s="28" t="n">
-        <v>-0.005529134834197</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.1640729467145814</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.1376146837152142</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.1843966326020115</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>-0.1831940100157078</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0269414901477214</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>0.0597309519640328</v>
+      <c r="J20" s="25" t="n">
+        <v>0.026615207399564</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0190112247110776</v>
       </c>
     </row>
   </sheetData>
@@ -2680,7 +2552,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2688,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2713,7 +2585,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2609,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
+          <t>THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2621,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, GARAN.IS, FROTO.IS, AKBNK.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, SISE.IS</t>
+          <t>TUPRS.IS, FROTO.IS, TCELL.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2671,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2807,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2904,7 +2776,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3012,7 +2884,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3050,7 +2922,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3058,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3082,7 +2954,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12250.7001953125</v>
+        <v>12118.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3092,7 +2964,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13611.73302246094</v>
+        <v>13615.6240234375</v>
       </c>
     </row>
     <row r="6">
@@ -3126,7 +2998,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>76.06</v>
+        <v>80.91</v>
       </c>
     </row>
     <row r="9">
@@ -3163,13 +3035,13 @@
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3183,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3247,23 +3119,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="26" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="29" t="n">
-        <v>206.8999938964844</v>
-      </c>
-      <c r="E4" s="30" t="n">
-        <v>0.05025377612428628</v>
-      </c>
-      <c r="F4" s="29" t="n">
-        <v>146054.7978911358</v>
-      </c>
-      <c r="G4" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H4" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D4" s="26" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>0.07868020304568524</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>228671.7942438866</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="5">
@@ -3277,23 +3149,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="26" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="29" t="n">
-        <v>84.34999847412109</v>
-      </c>
-      <c r="E5" s="30" t="n">
-        <v>-0.1259067515635119</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>-11056.43585567767</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H5" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D5" s="26" t="n">
+        <v>85.65000152587891</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>-0.1124352173484051</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>-9873.440090341275</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="6">
@@ -3307,23 +3179,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="26" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D6" s="29" t="n">
-        <v>129.8000030517578</v>
-      </c>
-      <c r="E6" s="30" t="n">
-        <v>-0.02698643935111478</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>-130687.2698127953</v>
-      </c>
-      <c r="G6" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H6" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D6" s="26" t="n">
+        <v>131.3000030517578</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>-0.01574206102555076</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>-76234.10224256478</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="7">
@@ -3337,23 +3209,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="26" t="n">
         <v>405.5</v>
       </c>
-      <c r="D7" s="29" t="n">
-        <v>396.5</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>-0.02219482120838467</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <v>-62938.26082332665</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H7" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D7" s="26" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>0.0141800246609125</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>40210.55552601442</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="8">
@@ -3367,23 +3239,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="26" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D8" s="29" t="n">
-        <v>73.84999847412109</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>-0.04586567159912602</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>-205344.5116042821</v>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D8" s="26" t="n">
+        <v>72.65000152587891</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>-0.06136950783407702</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>-274756.5046845153</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="9">
@@ -3397,23 +3269,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="26" t="n">
         <v>387</v>
       </c>
-      <c r="D9" s="29" t="n">
-        <v>384.75</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>-0.005813953488372103</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>-25105.03283867612</v>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H9" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D9" s="26" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>-0.003229974160206761</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>-13947.24046593066</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -91,12 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,22 +185,19 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -585,7 +582,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -610,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -627,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -678,7 +675,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.91/100</t>
+          <t>Güven Puanı: 80.75/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -755,7 +752,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: YKBNK.IS</t>
+          <t>AZALT: -</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -772,7 +769,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, ARCLK.IS</t>
+          <t>ÇIK: THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -958,25 +955,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2298474453949678</v>
+        <v>0.2155269052313723</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22984.74453949678</v>
+        <v>21552.69052313723</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>898.1864427738836</v>
+        <v>410.1248568516434</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>427.3206234500898</v>
+        <v>415.763807558775</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>390.6875</v>
+        <v>387.6</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.781550076600111</v>
+        <v>0.3805788019007346</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1001,25 +998,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1890962006107245</v>
+        <v>0.1994846123862184</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18909.62006107245</v>
+        <v>19948.46123862184</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0185277170790933</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>350.3520905646974</v>
+        <v>464.1623736709059</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>216.4371398793074</v>
+        <v>216.1142151794203</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>201.875</v>
+        <v>200.6399971008301</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3705543415818685</v>
+        <v>0.4653615816464591</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1042,25 +1039,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1810563539943076</v>
+        <v>0.1849884823824094</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18105.63539943076</v>
+        <v>18498.84823824093</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>599.6122234998426</v>
+        <v>612.6344245652119</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>135.6483225135468</v>
+        <v>134.8218254118378</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>123.815263377019</v>
+        <v>122.5244533762957</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.5809580093299256</v>
+        <v>0.5418845397997932</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1083,10 +1080,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>40000.00000000001</v>
+        <v>40000</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1115,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1138,7 +1135,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1159,7 +1156,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1201,7 +1198,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1353,28 +1350,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>411.25</v>
+        <v>408</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0205581560241685</v>
+        <v>-0.0205577496905355</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0814230337123209</v>
+        <v>0.0542750535284166</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>402.7954583350607</v>
+        <v>399.6124381262615</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>427.3206234500898</v>
+        <v>415.763807558775</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>444.735222614192</v>
+        <v>430.144221839594</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>390.6875</v>
+        <v>387.6</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1382,7 +1379,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1410,28 +1407,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>212.5</v>
+        <v>211.1999969482422</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>-0.0302466271968858</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0185277170790933</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.0466708728798923</v>
+        <v>0.0914169657590902</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>206.0725917206618</v>
+        <v>204.8119093765653</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>216.4371398793074</v>
+        <v>216.1142151794203</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>222.4175604869771</v>
+        <v>230.5072598375796</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>201.875</v>
+        <v>200.6399971008301</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1439,7 +1436,7 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1467,28 +1464,28 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>131.3000030517578</v>
+        <v>130.5</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0570048705314075</v>
+        <v>-0.0611152997985</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.0795559387098858</v>
+        <v>0.0795560183272892</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>123.815263377019</v>
+        <v>122.5244533762957</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>135.6483225135468</v>
+        <v>134.8218254118378</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>141.7456980471513</v>
+        <v>140.8820603917112</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>123.815263377019</v>
+        <v>122.5244533762957</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1496,7 +1493,7 @@
         </is>
       </c>
       <c r="M10" s="13" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1505,7 +1502,7 @@
       </c>
       <c r="O10" s="13" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1524,28 +1521,28 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>286.25</v>
+        <v>279.25</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0553651563181906</v>
+        <v>-0.0628618693134822</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>-0.0341997901255592</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.1114960523971878</v>
+        <v>0.051230381576059</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>270.4017240039179</v>
+        <v>261.6958229942101</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>276.4603100765587</v>
+        <v>269.6997086074376</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>318.165744998695</v>
+        <v>293.5560840551145</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>270.4017240039179</v>
+        <v>261.6958229942101</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
@@ -1553,7 +1550,7 @@
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
@@ -1567,121 +1564,235 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>36.41999816894531</v>
-      </c>
-      <c r="E12" s="21" t="n">
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>35.93999862670898</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <v>-0.053387959227386</v>
       </c>
-      <c r="F12" s="21" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.1033217154246511</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>34.47560879164018</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>36.46512931285342</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>40.18297485552339</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>34.47560879164018</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="F12" s="18" t="n">
+        <v>-0.0095238891213882</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.0919881126195933</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>34.02123544539393</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>35.59771006476537</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>39.24605126793072</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>34.02123544539393</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>80.91</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
+      <c r="M12" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>98.30000305175781</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.039929164947756</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0056461366774436</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.0253202830653163</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>94.37496601553926</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>97.74498779913446</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>100.7889869543498</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>93.38500289916992</v>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>78.40000152587891</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.0445633254802306</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.0169389726508262</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.0772325318535918</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>74.9062367402306</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>77.07198604420731</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>84.45503214104799</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>74.48000144958496</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="D14" s="17" t="n">
+        <v>76.55000305175781</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>-0.0514249572914607</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-0.016938908556182</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.1080537552156288</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>72.61342241415998</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>75.25332955008864</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>84.8215183432681</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>72.61342241415998</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="16" t="n">
-        <v>80.91</v>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="M14" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>348</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>-0.097767991594519</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>-0.0055291931010313</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0.1083753223429276</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>313.9767389251074</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>346.0758408008411</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>385.7146121753388</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>313.9767389251074</v>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1711,7 +1822,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1728,7 +1839,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1819,27 +1930,27 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0372591422531518</v>
+        <v>-0.012704174228675</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0441335285670299</v>
+        <v>0.0633892203471258</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.1255556536498179</v>
+        <v>0.0988178293379029</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0492395802835036</v>
+        <v>-0.0462534110402206</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0191384637845102</v>
+        <v>0.0188656249393633</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0190289400950367</v>
       </c>
     </row>
     <row r="5">
@@ -1862,16 +1973,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-0.0576496674057649</v>
+        <v>-0.0347349451440264</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0786802030456852</v>
+        <v>0.0720812027829551</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.06462922596201839</v>
+        <v>0.0352941026874618</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.0576587433953539</v>
+        <v>-0.0799832003221837</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1879,10 +1990,10 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0208840053323224</v>
+        <v>0.0209049144524068</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0185277170790933</v>
+        <v>0.0232680790823229</v>
       </c>
     </row>
     <row r="6">
@@ -1905,16 +2016,16 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.0194174082392906</v>
+        <v>0.0211267361797222</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.0202020681054191</v>
+        <v>0.0291797859557771</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.039502516584027</v>
+        <v>-0.070512780105842</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-0.1369664216105703</v>
+        <v>-0.1541701320588953</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -1922,7 +2033,7 @@
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>0.0220263134795572</v>
+        <v>0.0219560472301172</v>
       </c>
       <c r="K6" s="15" t="n">
         <v>0.0331174361060366</v>
@@ -1948,16 +2059,16 @@
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-0.0313028764805414</v>
+        <v>-0.021034180543383</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.1325757575757575</v>
+        <v>-0.1525037936267071</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-0.1040688575899843</v>
+        <v>-0.1361175560711524</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.1936358141344232</v>
+        <v>-0.202007399453498</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -1965,225 +2076,225 @@
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0180723854988791</v>
+        <v>0.0182902909452241</v>
       </c>
       <c r="K7" s="18" t="n">
         <v>-0.0341997901255592</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>-0.0060044002283821</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>0.08651544366282859</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>-0.0324123602679612</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>-0.1255658644328388</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0.0363321312123852</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.081878305420131</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>-0.0703569899492693</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>-0.1410192860246872</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>0.0261239227485806</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.0012391857819089</v>
+      <c r="J8" s="18" t="n">
+        <v>0.0261570210933936</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>-0.0095238891213882</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>-0.0555317409253494</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>0.3717472667621082</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>0.539853563379223</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>-0.2309781767799872</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="n">
+        <v>-0.0351351420553087</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.3759956869540564</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.5638771539369436</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>-0.2403921002344196</v>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0274366815632304</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.0195382818194833</v>
+      <c r="J9" s="20" t="n">
+        <v>0.0274488615475791</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.0266028003670319</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
-        <v>-0.1113149660442947</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>-0.139218006961732</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>-0.2891389070914403</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>-0.0627516685691355</v>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="E10" s="20" t="n">
+        <v>-0.0835459556667959</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>-0.1405502417997924</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>-0.3176638519297585</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>-0.07722106603181431</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
-        <v>0.0179308105833148</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0.102805769808545</v>
+      <c r="J10" s="20" t="n">
+        <v>0.0179418586662416</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0.0955199358563398</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>-0.0303188682253351</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>-0.1237600769858882</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.2014201044256922</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>-0.2707792314346859</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0.0241314061543816</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.0190703728875496</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.0288086380242014</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.1136363667271895</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.1306818564530771</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>-0.2821456295959658</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0110663828695687</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>-0.0940091884630616</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>-0.1619778303979786</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>-0.2987318037968683</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0206173299279643</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.0124595339704571</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>-0.0411735013815761</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>-0.1543350621836327</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>0.2547050709559768</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>-0.2495341591699014</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>0.0245820513339388</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0.029948947983406</v>
+      <c r="J12" s="18" t="n">
+        <v>0.0202669303577498</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>-0.0056461366774436</v>
       </c>
     </row>
     <row r="13">
@@ -2206,16 +2317,16 @@
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-0.1690513747344368</v>
+        <v>-0.1606359033630071</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>-0.2068790820831018</v>
+        <v>-0.2156761859780638</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-0.3086419711556413</v>
+        <v>-0.3473998204588225</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.0004404513674984</v>
+        <v>0.0167865251532108</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -2223,311 +2334,311 @@
         </is>
       </c>
       <c r="J13" s="18" t="n">
-        <v>0.0152318656113831</v>
+        <v>0.015398835227913</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>-0.0169389726508262</v>
+        <v>-0.016938908556182</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.0523777104329941</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>0.0021866112130526</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.0869854287689156</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.0241364620182464</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="E14" s="22" t="n">
+        <v>-0.0352265200594379</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>0.009022533445429901</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>-0.1441326891814895</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>-0.0324538470874489</v>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.023757732105983</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.0111110916693351</v>
+      <c r="J14" s="22" t="n">
+        <v>0.0236332051822288</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>0.0132478544110439</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n">
-        <v>-0.09794624245678241</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.0514950317688653</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>-0.1219887355571381</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0.0276953346162978</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="E15" s="22" t="n">
+        <v>-0.0614618257385515</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-0.0412896093085516</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>-0.1691176470588234</v>
+      </c>
+      <c r="H15" s="22" t="n">
+        <v>0.0103087844515024</v>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0214678685986214</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.0483516300336255</v>
+      <c r="J15" s="22" t="n">
+        <v>0.0213468675694466</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>0.0540671532455347</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.153256699007633</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.2093022747970567</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.2844036485715657</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.1628946465915355</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="E16" s="22" t="n">
+        <v>-0.1353333536783854</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.2210210393498968</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>-0.3115711191609415</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>-0.1814248975650475</v>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0183461054684322</v>
-      </c>
-      <c r="K16" s="25" t="n">
+      <c r="J16" s="22" t="n">
+        <v>0.0184858230413237</v>
+      </c>
+      <c r="K16" s="22" t="n">
         <v>0.0073660782405308</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.1174979165077881</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>0.0126090354486556</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>-0.0242990872445344</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.1072208885749907</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="E17" s="22" t="n">
+        <v>-0.08377423249402149</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>-0.0076408712192667</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>-0.027153553704721</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>-0.1247594319985501</v>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0389793391056107</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.07582576484113181</v>
+      <c r="J17" s="22" t="n">
+        <v>0.0389407713074076</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>0.0827739194543963</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>-0.0769230769230768</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.0099573257467994</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>-0.1267252195734002</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>0.011602209270932</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>0.0313925821554888</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>-0.0055291931010313</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.08355321020228661</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.1459016393442622</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.0612612612612613</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.2255174654706502</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="E19" s="22" t="n">
+        <v>-0.119613016710642</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>-0.1868399675060925</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>-0.1211589113257243</v>
+      </c>
+      <c r="H19" s="22" t="n">
+        <v>-0.2339115262360762</v>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0251248630786822</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0532805395405533</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="J19" s="22" t="n">
+        <v>0.0255128092543047</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <v>0.0369101913701237</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0583892617449663</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.0049645390070921</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.0690112806901127</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>0.0091218873182385</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="E20" s="22" t="n">
+        <v>-0.1174529051347802</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>-0.1533937211982809</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>-0.2009624849968089</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>-0.2354993133065573</v>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n">
-        <v>0.031377917776001</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0478181869880385</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.1295955728475251</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1582221984863281</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.1733665773215752</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.1990612037864825</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.026615207399564</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.0190112247110776</v>
+      <c r="J20" s="22" t="n">
+        <v>0.0265720710599121</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <v>0.1001577768561146</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2663,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2560,7 +2671,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2597,7 +2708,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2720,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ARCLK.IS</t>
+          <t>THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2732,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, FROTO.IS, TCELL.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
+          <t>TUPRS.IS, FROTO.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2744,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2782,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2922,7 +3033,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2930,7 +3041,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2954,7 +3065,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12118.2998046875</v>
+        <v>12070.2001953125</v>
       </c>
     </row>
     <row r="5">
@@ -2964,7 +3075,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13615.6240234375</v>
+        <v>13619.50302246094</v>
       </c>
     </row>
     <row r="6">
@@ -2998,7 +3109,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="9">
@@ -3032,7 +3143,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -3041,7 +3152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3055,7 +3166,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,23 +3230,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="25" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="26" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>0.07868020304568524</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>228671.7942438866</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D4" s="25" t="n">
+        <v>211.1999969482422</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.07208120278295516</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>209492.8245427259</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="5">
@@ -3149,23 +3260,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="25" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="26" t="n">
-        <v>85.65000152587891</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>-0.1124352173484051</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>-9873.440090341275</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D5" s="25" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.1217616580310881</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-10692.43662459664</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="6">
@@ -3179,23 +3290,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="25" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>131.3000030517578</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>-0.01574206102555076</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>-76234.10224256478</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D6" s="25" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.02173908567593119</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-105275.9023986077</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="7">
@@ -3209,23 +3320,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="25" t="n">
         <v>405.5</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>411.25</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0.0141800246609125</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>40210.55552601442</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D7" s="25" t="n">
+        <v>408</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.006165228113440113</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>17482.85022870218</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="8">
@@ -3239,23 +3350,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="25" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>72.65000152587891</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>-0.06136950783407702</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>-274756.5046845153</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D8" s="25" t="n">
+        <v>71.84999847412109</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.07170546437136893</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-321031.4609451308</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="9">
@@ -3269,23 +3380,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="25" t="n">
         <v>387</v>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>385.75</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>-0.003229974160206761</v>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>-13947.24046593066</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D9" s="25" t="n">
+        <v>391</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.01033591731266159</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>44631.16949098092</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.75/100</t>
+          <t>Güven Puanı: 81.06/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,7 +735,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
+          <t>ÇIK: GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %40</t>
+          <t>NAKIT: %60</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -884,7 +884,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 3</t>
+          <t>Qualified opportunities count: 2</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 2</t>
+          <t>Rejected opportunities count: 3</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -955,25 +955,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2155269052313723</v>
+        <v>0.2077980275017419</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21552.69052313723</v>
+        <v>20779.80275017419</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>410.1248568516434</v>
+        <v>395.4176217197435</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>415.763807558775</v>
+        <v>409.1401194481572</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>387.6</v>
+        <v>381.425</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805788019007346</v>
+        <v>0.3805788019007332</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %40</t>
+          <t>Cash allocation %: %60</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -998,25 +998,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1994846123862184</v>
+        <v>0.1922019724982581</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19948.46123862184</v>
+        <v>19220.19724982581</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0185279533884517</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>464.1623736709059</v>
+        <v>356.1109187616202</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>216.1142151794203</v>
+        <v>214.8075391530232</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>200.6399971008301</v>
+        <v>196.9519159598</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4653615816464591</v>
+        <v>0.2801493707073222</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1025,83 +1025,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0.1849884823824094</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>18498.84823824093</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>612.6344245652119</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>134.8218254118378</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>122.5244533762957</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.5418845397997932</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D22" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K23"/>
+  <autoFilter ref="A19:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1112,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1135,7 +1094,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1156,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1198,7 +1157,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1350,28 +1309,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>408</v>
+        <v>401.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0205577496905355</v>
+        <v>-0.0339316023388089</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0542750535284166</v>
+        <v>0.0722991184716234</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>399.6124381262615</v>
+        <v>387.8764616609682</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>415.763807558775</v>
+        <v>409.1401194481572</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>430.144221839594</v>
+        <v>430.5280960663567</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>387.6</v>
+        <v>381.425</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1379,7 +1338,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1407,28 +1366,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>211.1999969482422</v>
+        <v>210.8999938964844</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0302466271968858</v>
+        <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0185279533884517</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.0914169657590902</v>
+        <v>0.06904391931949121</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>204.8119093765653</v>
+        <v>196.9519159598</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>216.1142151794203</v>
+        <v>214.8075391530232</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>230.5072598375796</v>
+        <v>225.4613560595544</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>200.6399971008301</v>
+        <v>196.9519159598</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1436,7 +1395,7 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1445,62 +1404,62 @@
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>130.5</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0611152997985</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.0795560183272892</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>122.5244533762957</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>134.8218254118378</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>140.8820603917112</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>122.5244533762957</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0597515338203614</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>-0.008288919948726801</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1264267348706023</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>125.8992638826324</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>132.7901075659414</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>150.8285329240105</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>125.8992638826324</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr">
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
@@ -1512,7 +1471,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1521,28 +1480,28 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>279.25</v>
+        <v>36.29999923706055</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0628618693134822</v>
+        <v>-0.053387959227386</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>-0.0341997901255592</v>
+        <v>-0.0095238891213882</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.051230381576059</v>
+        <v>0.09198805801759501</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>261.6958229942101</v>
+        <v>34.36201635783821</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>269.6997086074376</v>
+        <v>35.95428206922031</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>293.5560840551145</v>
+        <v>39.63916567291793</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>261.6958229942101</v>
+        <v>34.36201635783821</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
@@ -1550,16 +1509,16 @@
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1528,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -1578,28 +1537,28 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>35.93999862670898</v>
+        <v>276.75</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-0.053387959227386</v>
+        <v>-0.0532251759639228</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-0.0095238891213882</v>
+        <v>-0.0241174841137557</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.0919881126195933</v>
+        <v>0.1059543201175193</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>34.02123544539393</v>
+        <v>262.0199325519844</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>35.59771006476537</v>
+        <v>270.0754862715181</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>39.24605126793072</v>
+        <v>306.0728580925235</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>34.02123544539393</v>
+        <v>262.0199325519844</v>
       </c>
       <c r="L12" s="16" t="inlineStr">
         <is>
@@ -1607,26 +1566,26 @@
         </is>
       </c>
       <c r="M12" s="16" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N12" s="16" t="inlineStr">
         <is>
-          <t>3A momentum destekli; trend desteği var</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1635,28 +1594,28 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>98.30000305175781</v>
+        <v>76.55000305175781</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-0.039929164947756</v>
+        <v>-0.0514249572914607</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>-0.0056461366774436</v>
+        <v>-0.0169388433571329</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.0253202830653163</v>
+        <v>0.1080536875032713</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>94.37496601553926</v>
+        <v>72.61342241415998</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>97.74498779913446</v>
+        <v>75.25333454107604</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>100.7889869543498</v>
+        <v>84.82151315988692</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>93.38500289916992</v>
+        <v>72.61342241415998</v>
       </c>
       <c r="L13" s="16" t="inlineStr">
         <is>
@@ -1664,7 +1623,7 @@
         </is>
       </c>
       <c r="M13" s="16" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N13" s="16" t="inlineStr">
         <is>
@@ -1673,126 +1632,12 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>76.55000305175781</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.0514249572914607</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.016938908556182</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.1080537552156288</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>75.25332955008864</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>84.8215183432681</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>348</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>-0.097767991594519</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>-0.0055291931010313</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.1083753223429276</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>313.9767389251074</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>346.0758408008411</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>385.7146121753388</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>313.9767389251074</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1822,7 +1667,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1839,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1930,16 +1775,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.012704174228675</v>
+        <v>-0.0098643649815043</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0633892203471258</v>
+        <v>0.009822246565652301</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.0988178293379029</v>
+        <v>0.09148572652625959</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0462534110402206</v>
+        <v>-0.08444800886198769</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1947,7 +1792,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0188656249393633</v>
+        <v>0.0184398313048768</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1973,16 +1818,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-0.0347349451440264</v>
+        <v>0.0213074764962923</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0720812027829551</v>
+        <v>0.0555555088848078</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.0352941026874618</v>
+        <v>0.0333169406644697</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.0799832003221837</v>
+        <v>-0.123075695465797</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1990,53 +1835,53 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0209049144524068</v>
+        <v>0.0208420951766543</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0185279533884517</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.0211267361797222</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.0291797859557771</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>-0.070512780105842</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>-0.1541701320588953</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.1075268172583339</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.0772324264604336</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-0.0346070883732535</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>-0.1962057044093192</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0219560472301172</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0331174361060366</v>
+      <c r="J6" s="18" t="n">
+        <v>0.022027028856444</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>-0.008288919948726801</v>
       </c>
     </row>
     <row r="7">
@@ -2045,7 +1890,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -2059,27 +1904,27 @@
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-0.021034180543383</v>
+        <v>0.1301370001300466</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.1525037936267071</v>
+        <v>0.1033433906836516</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-0.1361175560711524</v>
+        <v>-0.0462428290258961</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.202007399453498</v>
+        <v>-0.2101215518778449</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0182902909452241</v>
+        <v>0.0261382572155817</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>-0.0341997901255592</v>
+        <v>-0.0095238891213882</v>
       </c>
     </row>
     <row r="8">
@@ -2088,7 +1933,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -2102,27 +1947,27 @@
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0.0363321312123852</v>
+        <v>0.0137362637362636</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0.081878305420131</v>
+        <v>-0.15625</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-0.0703569899492693</v>
+        <v>-0.1262825572217837</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-0.1410192860246872</v>
+        <v>-0.2534142788573249</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.0261570210933936</v>
+        <v>0.0183068090727517</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-0.0095238891213882</v>
+        <v>-0.0241174841137557</v>
       </c>
     </row>
     <row r="9">
@@ -2131,7 +1976,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -2145,27 +1990,27 @@
         </is>
       </c>
       <c r="E9" s="20" t="n">
-        <v>-0.0351351420553087</v>
+        <v>0.0753307314128375</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.3759956869540564</v>
+        <v>-0.142201769844607</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.5638771539369436</v>
+        <v>0.1846415657271476</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-0.2403921002344196</v>
+        <v>-0.3282924529445142</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J9" s="20" t="n">
-        <v>0.0274488615475791</v>
+        <v>0.0238267651578265</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>0.0266028003670319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2174,12 +2019,12 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -2188,27 +2033,27 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-0.0835459556667959</v>
+        <v>-0.0257865512061281</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-0.1405502417997924</v>
+        <v>0.2728139134011862</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.3176638519297585</v>
+        <v>0.482538893227584</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>-0.07722106603181431</v>
+        <v>-0.2597158164725923</v>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.0179418586662416</v>
+        <v>0.026572024756061</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>0.0955199358563398</v>
+        <v>0.0195382818194833</v>
       </c>
     </row>
     <row r="11">
@@ -2217,7 +2062,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
@@ -2231,113 +2076,113 @@
         </is>
       </c>
       <c r="E11" s="20" t="n">
-        <v>-0.0303188682253351</v>
+        <v>0.0429448340922553</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>-0.1237600769858882</v>
+        <v>0.0172027158134355</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.2014201044256922</v>
+        <v>-0.1214470457437393</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>-0.2707792314346859</v>
+        <v>-0.08903919072576209</v>
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J11" s="20" t="n">
-        <v>0.0241314061543816</v>
+        <v>0.0236824282904043</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>0.0190703728875496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0110663828695687</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0940091884630616</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>-0.1619778303979786</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>-0.2987318037968683</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-0.0522438237931836</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>-0.1439806570620914</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-0.3255481508973484</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>-0.1339984914720539</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="18" t="n">
-        <v>0.0202669303577498</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>-0.0056461366774436</v>
+      <c r="J12" s="20" t="n">
+        <v>0.0179810570574388</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0.0696037442997602</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.1606359033630071</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.2156761859780638</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>-0.3473998204588225</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>0.0167865251532108</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0.0124554612615923</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>-0.0410112530997629</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>-0.1387487407841955</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>-0.0375289263812521</v>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="18" t="n">
-        <v>0.015398835227913</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>-0.016938908556182</v>
+      <c r="J13" s="20" t="n">
+        <v>0.021348496351713</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0.0406249908410989</v>
       </c>
     </row>
     <row r="14">
@@ -2346,7 +2191,7 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -2360,16 +2205,16 @@
         </is>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0352265200594379</v>
+        <v>0.0219320989464344</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.009022533445429901</v>
+        <v>-0.1072080306896575</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.1441326891814895</v>
+        <v>-0.1542782968447803</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>-0.0324538470874489</v>
+        <v>-0.3546968211243853</v>
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
@@ -2377,53 +2222,53 @@
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>0.0236332051822288</v>
+        <v>0.0202170048918636</v>
       </c>
       <c r="K14" s="22" t="n">
-        <v>0.0132478544110439</v>
+        <v>0.0124596506797498</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>-0.0614618257385515</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>-0.0412896093085516</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>-0.1691176470588234</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>0.0103087844515024</v>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>-0.1185952285932669</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.2224478880176887</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.3578019713792729</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.0237804713987</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="22" t="n">
-        <v>0.0213468675694466</v>
-      </c>
-      <c r="K15" s="22" t="n">
-        <v>0.0540671532455347</v>
+      <c r="J15" s="24" t="n">
+        <v>0.0153242689052913</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>-0.0169388433571329</v>
       </c>
     </row>
     <row r="16">
@@ -2446,16 +2291,16 @@
         </is>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.1353333536783854</v>
+        <v>-0.1088154503019023</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.2210210393498968</v>
+        <v>-0.2143291056820785</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>-0.3115711191609415</v>
+        <v>-0.2955906584312952</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>-0.1814248975650475</v>
+        <v>-0.2320606108523896</v>
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
@@ -2463,10 +2308,10 @@
         </is>
       </c>
       <c r="J16" s="22" t="n">
-        <v>0.0184858230413237</v>
+        <v>0.0184647467983716</v>
       </c>
       <c r="K16" s="22" t="n">
-        <v>0.0073660782405308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2489,70 +2334,70 @@
         </is>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-0.08377423249402149</v>
+        <v>-0.0305052146621838</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>-0.0076408712192667</v>
+        <v>-0.1039647811027634</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>-0.027153553704721</v>
+        <v>-0.0837838083977292</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>-0.1247594319985501</v>
+        <v>-0.1681446065012396</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J17" s="22" t="n">
-        <v>0.0389407713074076</v>
+        <v>0.0375357321501754</v>
       </c>
       <c r="K17" s="22" t="n">
-        <v>0.0827739194543963</v>
+        <v>0.0166223768740767</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0769230769230768</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0099573257467994</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-0.1267252195734002</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>0.011602209270932</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>-0.009873060648801101</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>-0.1547260686333533</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>-0.0144960244423122</v>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0313925821554888</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>-0.0055291931010313</v>
+      <c r="J18" s="22" t="n">
+        <v>0.0313929461035974</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>0.0401887662276918</v>
       </c>
     </row>
     <row r="19">
@@ -2575,16 +2420,16 @@
         </is>
       </c>
       <c r="E19" s="22" t="n">
-        <v>-0.119613016710642</v>
+        <v>-0.0953167931983184</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>-0.1868399675060925</v>
+        <v>-0.1837613817671655</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>-0.1211589113257243</v>
+        <v>-0.1319823680995319</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>-0.2339115262360762</v>
+        <v>-0.2413179433792739</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -2592,10 +2437,10 @@
         </is>
       </c>
       <c r="J19" s="22" t="n">
-        <v>0.0255128092543047</v>
+        <v>0.0254782595170972</v>
       </c>
       <c r="K19" s="22" t="n">
-        <v>0.0369101913701237</v>
+        <v>0.0350217789493367</v>
       </c>
     </row>
     <row r="20">
@@ -2618,16 +2463,16 @@
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.1174529051347802</v>
+        <v>-0.0251178144560054</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.1533937211982809</v>
+        <v>-0.1626966669318381</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>-0.2009624849968089</v>
+        <v>-0.2097097391095529</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>-0.2354993133065573</v>
+        <v>-0.3491513513096235</v>
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
@@ -2635,10 +2480,10 @@
         </is>
       </c>
       <c r="J20" s="22" t="n">
-        <v>0.0265720710599121</v>
+        <v>0.0265476448629649</v>
       </c>
       <c r="K20" s="22" t="n">
-        <v>0.1001577768561146</v>
+        <v>0.0905550350972887</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2508,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2671,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2696,7 +2541,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2565,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
+          <t>GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2577,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, FROTO.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, SISE.IS</t>
+          <t>EREGL.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2589,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2601,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2627,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2790,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2887,7 +2732,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3033,7 +2878,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3041,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3065,7 +2910,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12070.2001953125</v>
+        <v>11721.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3075,7 +2920,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13619.50302246094</v>
+        <v>13622.35702148438</v>
       </c>
     </row>
     <row r="6">
@@ -3109,7 +2954,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="9">
@@ -3136,14 +2981,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -3152,7 +2997,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3166,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3234,19 +3079,19 @@
         <v>197</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>211.1999969482422</v>
+        <v>210.8999938964844</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>0.07208120278295516</v>
+        <v>0.0705583446522049</v>
       </c>
       <c r="F4" s="25" t="n">
-        <v>209492.8245427259</v>
+        <v>205066.873825042</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="5">
@@ -3264,143 +3109,113 @@
         <v>96.5</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>84.75</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>-0.1217616580310881</v>
+        <v>-0.1155440572629939</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>-10692.43662459664</v>
+        <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>133.3999938964844</v>
+        <v>405.5</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>130.5</v>
+        <v>401.5</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>-0.02173908567593119</v>
+        <v>-0.009864364981504337</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>-105275.9023986077</v>
+        <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>405.5</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>408</v>
+        <v>70.75</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>0.006165228113440113</v>
+        <v>-0.08591733068190521</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>17482.85022870218</v>
+        <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>77.40000152587891</v>
+        <v>387</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>71.84999847412109</v>
+        <v>384.5</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>-0.07170546437136893</v>
+        <v>-0.006459948320413411</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>-321031.4609451308</v>
+        <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>-0.1157107556416009</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>387</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>391</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>0.01033591731266159</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>44631.16949098092</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>19904979.91163881</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1312,7 +1312,7 @@
         <v>401.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316023388089</v>
+        <v>-0.0339316023388087</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1321,7 +1321,7 @@
         <v>0.0722991184716234</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>387.8764616609682</v>
+        <v>387.8764616609683</v>
       </c>
       <c r="I8" s="14" t="n">
         <v>409.1401194481572</v>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1781,7 +1781,7 @@
         <v>0.009822246565652301</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.09148572652625959</v>
+        <v>0.0914857265262594</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>-0.08444800886198769</v>
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0213074764962923</v>
+        <v>0.0213074764962926</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>0.0555555088848078</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.0333169406644697</v>
+        <v>0.0333169406644699</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-0.123075695465797</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0208420951766543</v>
+        <v>0.0208420951766542</v>
       </c>
       <c r="K5" s="15" t="n">
         <v>0.0185279533884517</v>
@@ -1864,7 +1864,7 @@
         <v>0.1075268172583339</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0.0772324264604336</v>
+        <v>0.0772324264604338</v>
       </c>
       <c r="G6" s="18" t="n">
         <v>-0.0346070883732535</v>
@@ -1993,7 +1993,7 @@
         <v>0.0753307314128375</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>-0.142201769844607</v>
+        <v>-0.1422017698446069</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0.1846415657271476</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.0179810570574388</v>
+        <v>0.0179810570574387</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>0.0696037442997602</v>
@@ -2182,7 +2182,7 @@
         <v>0.021348496351713</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>0.0406249908410989</v>
+        <v>0.0406249908410991</v>
       </c>
     </row>
     <row r="14">
@@ -2211,7 +2211,7 @@
         <v>-0.1072080306896575</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.1542782968447803</v>
+        <v>-0.1542782968447804</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>-0.3546968211243853</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>0.0202170048918636</v>
+        <v>0.0202170048918635</v>
       </c>
       <c r="K14" s="22" t="n">
         <v>0.0124596506797498</v>
@@ -2251,10 +2251,10 @@
         <v>-0.1185952285932669</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.2224478880176887</v>
+        <v>-0.2224478880176889</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.3578019713792729</v>
+        <v>-0.357801971379273</v>
       </c>
       <c r="H15" s="24" t="n">
         <v>-0.0237804713987</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0153242689052913</v>
+        <v>0.0153242689052914</v>
       </c>
       <c r="K15" s="24" t="n">
         <v>-0.0169388433571329</v>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="J16" s="22" t="n">
-        <v>0.0184647467983716</v>
+        <v>0.0184647467983715</v>
       </c>
       <c r="K16" s="22" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2635,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2886,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2990,7 +2990,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3011,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3082,13 +3082,13 @@
         <v>210.8999938964844</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>0.0705583446522049</v>
+        <v>0.07055834465220512</v>
       </c>
       <c r="F4" s="25" t="n">
-        <v>205066.873825042</v>
+        <v>205066.8738250425</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3118,7 +3118,7 @@
         <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3148,7 +3148,7 @@
         <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3178,7 +3178,7 @@
         <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3208,7 +3208,7 @@
         <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>-0.1192206512468987</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2516,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2635,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2886,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2990,7 +2990,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3011,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3088,7 +3088,7 @@
         <v>205066.8738250425</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3118,7 +3118,7 @@
         <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3148,7 +3148,7 @@
         <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3178,7 +3178,7 @@
         <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3208,7 +3208,7 @@
         <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>-0.1192206512468987</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,19 +185,28 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -571,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -582,7 +591,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -607,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -624,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -675,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 81.06/100</t>
+          <t>Güven Puanı: 77.21/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS</t>
+          <t>AL: GARAN.IS, BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -752,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: -</t>
+          <t>AZALT: THYAO.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -769,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
+          <t>ÇIK: EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -786,7 +795,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %60</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -884,7 +893,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 2</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -941,12 +950,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 3</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -955,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2077980275017419</v>
+        <v>0.2088152294530557</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20779.80275017419</v>
+        <v>20881.52294530557</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0567878660082687</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>395.4176217197435</v>
+        <v>1185.817127066601</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>409.1401194481572</v>
+        <v>138.9676043800874</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>381.425</v>
+        <v>124.925</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805788019007332</v>
+        <v>1.135757320165376</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -984,83 +993,124 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %60</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0.2002676363786851</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>20026.76363786851</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0.0190289400950367</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>381.0880855624591</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>388.250026176209</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.3805788019007357</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>0.1922019724982581</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>19220.19724982581</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>0.0185279533884517</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>356.1109187616202</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>214.8075391530232</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>196.9519159598</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.2801493707073222</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="D22" s="7" t="n">
+        <v>0.1909171341682591</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>19091.71341682591</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.0185278352337725</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>353.7281205173542</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>207.7796783876896</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>190.5082770636984</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.2801479400025187</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000.00000000001</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K22"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1071,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1115,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1157,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1309,28 +1359,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>401.5</v>
+        <v>381</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316023388087</v>
+        <v>-0.0339317167690779</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0722991184716234</v>
+        <v>0.0770488931257379</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>387.8764616609683</v>
+        <v>368.0720159109813</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>409.1401194481572</v>
+        <v>388.250026176209</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>430.5280960663567</v>
+        <v>410.3556282809061</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>381.425</v>
+        <v>361.95</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1338,11 +1388,11 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>81.06</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="13" t="inlineStr">
@@ -1366,28 +1416,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>210.8999938964844</v>
+        <v>204</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.06613598075081251</v>
+        <v>-0.0661358967465763</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0185279533884517</v>
+        <v>0.0185278352337725</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.06904391931949121</v>
+        <v>0.06904386578716611</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>196.9519159598</v>
+        <v>190.5082770636984</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>214.8075391530232</v>
+        <v>207.7796783876896</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>225.4613560595544</v>
+        <v>218.0849486205819</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>196.9519159598</v>
+        <v>190.5082770636984</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1395,73 +1445,73 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>81.06</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>133.8999938964844</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0597515338203614</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.008288919948726801</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1264267348706023</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>125.8992638826324</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>132.7901075659414</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>150.8285329240105</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>125.8992638826324</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0446735031448903</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.0567878660082687</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.1240418332017574</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>125.6254343364469</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>138.9676043800874</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>147.8115010660311</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>124.925</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1471,173 +1521,287 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0478683703056284</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.0115131578947369</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.128113826384147</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>260.4080007214106</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>276.6488486842106</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>308.5391315160642</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>259.825</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>36.29999923706055</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.053387959227386</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.0095238891213882</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.09198805801759501</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>34.36201635783821</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>35.95428206922031</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>39.63916567291793</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>34.36201635783821</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="D12" s="20" t="n">
+        <v>36.2599983215332</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0653061001718057</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.0210279373987021</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.0338076907416818</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>33.89199923891765</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>35.49752534675096</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>37.4858651310815</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>33.89199923891765</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="M12" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
-        <v>276.75</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0532251759639228</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.1059543201175193</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>262.0199325519844</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>270.0754862715181</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>306.0728580925235</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>262.0199325519844</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="D13" s="20" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0627802516039144</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.012693954565347</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.06657407220854521</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>62.65313875019448</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>66.00140763079708</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>71.30047509967838</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>62.65313875019448</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="M13" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>75.05000305175781</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.056962015212765</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.1080536875032713</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>70.77500363620553</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>73.77873310261967</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>83.15943262863202</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>70.77500363620553</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>76.55000305175781</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.0514249572914607</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.0169388433571329</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.1080536875032713</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>75.25333454107604</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>84.82151315988692</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="D15" s="20" t="n">
+        <v>19.70999908447266</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>-0.1036118867092948</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.0471306356513333</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>17.66780889229197</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>19.47636835227578</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>20.63894387001105</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>17.66780889229197</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M15" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1667,7 +1831,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1684,7 +1848,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1775,16 +1939,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0098643649815043</v>
+        <v>-0.0885167464114832</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.009822246565652301</v>
+        <v>-0.0246694885084334</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.0914857265262594</v>
+        <v>0.0247374545953591</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.08444800886198769</v>
+        <v>-0.0713714963421137</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1792,7 +1956,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0184398313048768</v>
+        <v>0.0194215259434294</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1818,16 +1982,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0213074764962926</v>
+        <v>-0.06721535049550589</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0555555088848078</v>
+        <v>0.0124069478908188</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.0333169406644699</v>
+        <v>-0.0111488270370058</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.123075695465797</v>
+        <v>-0.1779043813425157</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1835,53 +1999,53 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0208420951766542</v>
+        <v>0.0212480672808465</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0185279533884517</v>
+        <v>0.0185278352337725</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>0.1075268172583339</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>0.0772324264604338</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>-0.0346070883732535</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>-0.1962057044093192</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.0075471698113207</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.0587761934873471</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>-0.0607142857142857</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-0.2401145978594463</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0.022027028856444</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>-0.008288919948726801</v>
+      <c r="J6" s="15" t="n">
+        <v>0.0221600754600607</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.0567878660082687</v>
       </c>
     </row>
     <row r="7">
@@ -1890,7 +2054,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1900,203 +2064,203 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>-0.0544511668107173</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>-0.1385826771653543</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>-0.1558641975308642</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.2990371871898438</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.0179550241285408</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.0115131578947369</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>0.1301370001300466</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0.1033433906836516</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>-0.0462428290258961</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-0.2101215518778449</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="E8" s="21" t="n">
+        <v>0.0033203910877523</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>-0.1427896223278293</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>0.1682462518215937</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>-0.4166007613604728</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0261382572155817</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>-0.0095238891213882</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="J8" s="21" t="n">
+        <v>0.0238393622678929</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>-0.0210279373987021</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>0.0137362637362636</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>-0.15625</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>-0.1262825572217837</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>-0.2534142788573249</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>-0.0584988467066824</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.035067855436785</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>-0.1512437507287779</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>-0.0469174948540891</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0183068090727517</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="J9" s="23" t="n">
+        <v>0.0213332669094879</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0125687493441779</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>0.0753307314128375</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>-0.1422017698446069</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.1846415657271476</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>-0.3282924529445142</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="E10" s="23" t="n">
+        <v>-0.0722597663968105</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0.2349885919682477</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0.4288934039768077</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>-0.2797918847497309</v>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="20" t="n">
-        <v>0.0238267651578265</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="J10" s="23" t="n">
+        <v>0.0267961516085757</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>0.0186683182612425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
-        <v>-0.0257865512061281</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.2728139134011862</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.482538893227584</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>-0.2597158164725923</v>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>0.026572024756061</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>0.0195382818194833</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0.0429448340922553</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0.0172027158134355</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>-0.1214470457437393</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>-0.08903919072576209</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="E11" s="23" t="n">
+        <v>-0.0237014466763041</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.1318385376523962</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1676698150327801</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>-0.3947890261345917</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
-        <v>0.0236824282904043</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0</v>
+      <c r="J11" s="23" t="n">
+        <v>0.0201020435035757</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.0008189588123605</v>
       </c>
     </row>
     <row r="12">
@@ -2105,385 +2269,385 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0656883910156765</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0.0022488985418591</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>-0.1478648683922098</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>-0.1463350037254664</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0.023782163861295</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>-0.012693954565347</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>0.0107588072309898</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0.08642727023240621</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>-0.0525477581263276</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>-0.2608541483895467</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.0262386681832899</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
-        <v>-0.0522438237931836</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>-0.1439806570620914</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>-0.3255481508973484</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>-0.1339984914720539</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="E14" s="25" t="n">
+        <v>-0.1052291054566574</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1454993297703778</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.3468425631630822</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.184823647196279</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="20" t="n">
-        <v>0.0179810570574387</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0.0696037442997602</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="J14" s="25" t="n">
+        <v>0.0180080585291347</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.0417059171430678</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>-0.163788266832782</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.2388437706573017</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.3629032164049853</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-0.0341178763549946</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0154349832021613</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n">
-        <v>0.0124554612615923</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>-0.0410112530997629</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>-0.1387487407841955</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>-0.0375289263812521</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="E16" s="25" t="n">
+        <v>-0.1498002693552206</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.2180037075212559</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.3174773234502706</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.2911065832810884</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="20" t="n">
-        <v>0.021348496351713</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0.0406249908410991</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0184935998639454</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0147321564810616</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.08495829866634361</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.07551597717622929</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>-0.1065276717299021</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.2143560266767461</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0369537734981878</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="22" t="n">
-        <v>0.0219320989464344</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.1072080306896575</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>-0.1542782968447804</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>-0.3546968211243853</v>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="E18" s="25" t="n">
+        <v>-0.1040157998683344</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0548611111111111</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.1736490588949605</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.018716959054709</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="22" t="n">
-        <v>0.0202170048918635</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>0.0124596506797498</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="J18" s="25" t="n">
+        <v>0.0315706199152426</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0339372257730323</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.1185952285932669</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.2224478880176889</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.357801971379273</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.0237804713987</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>-0.1484320770157339</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.1853333536783854</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.1798657922936766</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.2416322795488767</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0153242689052914</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>-0.0169388433571329</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="J19" s="25" t="n">
+        <v>0.02548291720417</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0428598924856524</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="22" t="n">
-        <v>-0.1088154503019023</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-0.2143291056820785</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>-0.2955906584312952</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>-0.2320606108523896</v>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="E20" s="25" t="n">
+        <v>-0.1000497866408884</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1625752757792875</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.2381455010880332</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.4221787009784454</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="22" t="n">
-        <v>0.0184647467983715</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>-0.0305052146621838</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>-0.1039647811027634</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>-0.0837838083977292</v>
-      </c>
-      <c r="H17" s="22" t="n">
-        <v>-0.1681446065012396</v>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>0.0375357321501754</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>0.0166223768740767</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>-0.009873060648801101</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>-0.1547260686333533</v>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>-0.0144960244423122</v>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>0.0313929461035974</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>0.0401887662276918</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>-0.0953167931983184</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>-0.1837613817671655</v>
-      </c>
-      <c r="G19" s="22" t="n">
-        <v>-0.1319823680995319</v>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>-0.2413179433792739</v>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="n">
-        <v>0.0254782595170972</v>
-      </c>
-      <c r="K19" s="22" t="n">
-        <v>0.0350217789493367</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>-0.0251178144560054</v>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>-0.1626966669318381</v>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>-0.2097097391095529</v>
-      </c>
-      <c r="H20" s="22" t="n">
-        <v>-0.3491513513096235</v>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="n">
-        <v>0.0265476448629649</v>
-      </c>
-      <c r="K20" s="22" t="n">
-        <v>0.0905550350972887</v>
+      <c r="J20" s="25" t="n">
+        <v>0.0265453263368255</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0905550690718651</v>
       </c>
     </row>
   </sheetData>
@@ -2508,7 +2672,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2516,7 +2680,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2541,7 +2705,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2717,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2729,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
+          <t>EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2741,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
+          <t>SAHOL.IS, TUPRS.IS, TCELL.IS, YKBNK.IS, FROTO.IS, PGSUS.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2753,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2765,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2791,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2635,7 +2799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2732,7 +2896,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2878,7 +3042,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2886,7 +3050,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2910,7 +3074,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11721.7001953125</v>
+        <v>11430.099609375</v>
       </c>
     </row>
     <row r="5">
@@ -2920,7 +3084,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13622.35702148438</v>
+        <v>13623.40651855469</v>
       </c>
     </row>
     <row r="6">
@@ -2954,7 +3118,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>81.06</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2981,15 +3145,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -2997,7 +3161,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3011,7 +3175,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3075,23 +3239,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>210.8999938964844</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.07055834465220512</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>205066.8738250425</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D4" s="28" t="n">
+        <v>204</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>0.03553299492385786</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>103271.1328843357</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="5">
@@ -3105,23 +3269,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>85.34999847412109</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.1155440572629939</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-10146.44124932901</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D5" s="28" t="n">
+        <v>85.30000305175781</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>-0.1160621445413699</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>-10191.93681402173</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="6">
@@ -3135,23 +3299,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="28" t="n">
         <v>405.5</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>401.5</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.009864364981504337</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-27972.56036592275</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D6" s="28" t="n">
+        <v>381</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-0.06041923551171391</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-171331.9322412787</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="7">
@@ -3165,23 +3329,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="28" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.08591733068190521</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-384659.1948204595</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D7" s="28" t="n">
+        <v>69.30000305175781</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>-0.1046511410133867</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>-468532.056568299</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="8">
@@ -3195,27 +3359,57 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="28" t="n">
         <v>387</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.006459948320413411</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-27894.48093186226</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D8" s="28" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.02971576227390182</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-128314.6122865686</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>-0.1446511824786558</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>1.862645149230957e-09</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H8"/>
+  <autoFilter ref="A3:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,28 +185,19 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -580,14 +571,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -616,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +675,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 77.21/100</t>
+          <t>Güven Puanı: 80.94/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +735,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: GARAN.IS, BIMAS.IS, KCHOL.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +752,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: THYAO.IS</t>
+          <t>AZALT: -</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +769,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
+          <t>ÇIK: GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -795,7 +786,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %40</t>
+          <t>NAKIT: %60</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -893,7 +884,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 3</t>
+          <t>Qualified opportunities count: 2</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -950,12 +941,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 2</t>
+          <t>Rejected opportunities count: 3</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -964,25 +955,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2088152294530557</v>
+        <v>0.20384932543041</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20881.52294530557</v>
+        <v>20384.932543041</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0567878660082687</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1185.817127066601</v>
+        <v>387.9036602028913</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>138.9676043800874</v>
+        <v>378.0597367752586</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>124.925</v>
+        <v>352.45</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.135757320165376</v>
+        <v>0.3805788019007337</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -993,12 +984,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %40</t>
+          <t>Cash allocation %: %60</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,25 +998,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2002676363786851</v>
+        <v>0.19615067456959</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20026.76363786851</v>
+        <v>19615.067456959</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0185277148899571</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>381.0880855624591</v>
+        <v>363.4223773898121</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>388.250026176209</v>
+        <v>206.6592671345725</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>361.95</v>
+        <v>192.7549942016601</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3805788019007357</v>
+        <v>0.3705542977991442</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1034,83 +1025,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0.1909171341682591</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>19091.71341682591</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.0185278352337725</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>353.7281205173542</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>207.7796783876896</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>190.5082770636984</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.2801479400025187</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0.4000000000000001</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>40000.00000000001</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D22" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K23"/>
+  <autoFilter ref="A19:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1121,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1094,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1157,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1359,28 +1309,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339317167690779</v>
+        <v>-0.0205581560241685</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0770488931257379</v>
+        <v>0.06844627048378669</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>368.0720159109813</v>
+        <v>363.3729241150335</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>388.250026176209</v>
+        <v>378.0597367752586</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>410.3556282809061</v>
+        <v>396.3935663494848</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>361.95</v>
+        <v>352.45</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1388,11 +1338,11 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+          <t>trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="13" t="inlineStr">
@@ -1416,28 +1366,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>204</v>
+        <v>202.8999938964844</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0661358967465763</v>
+        <v>-0.0302466271968858</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0185278352337725</v>
+        <v>0.0185277148899571</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.06904386578716611</v>
+        <v>0.0466707608184535</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>190.5082770636984</v>
+        <v>196.762953422847</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>207.7796783876896</v>
+        <v>206.6592671345725</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>218.0849486205819</v>
+        <v>212.3694909816929</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>190.5082770636984</v>
+        <v>192.7549942016601</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1445,73 +1395,73 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
+          <t>trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0597513661055632</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>-0.0082889988742848</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1264267348706023</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>124.5829439910129</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>131.4017076491573</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>149.2515423703548</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>124.5829439910129</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
           <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0446735031448903</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0567878660082687</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.1240418332017574</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>125.6254343364469</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>138.9676043800874</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>147.8115010660311</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>124.925</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1476,32 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>273.5</v>
+        <v>266</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0478683703056284</v>
+        <v>-0.0628618693134822</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.0115131578947369</v>
+        <v>-0.0241174841137557</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.128113826384147</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>260.4080007214106</v>
+        <v>249.2787427626137</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>276.6488486842106</v>
+        <v>259.584749225741</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>308.5391315160642</v>
+        <v>300.0782778181831</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>259.825</v>
+        <v>249.2787427626137</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
@@ -1559,7 +1509,7 @@
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
@@ -1568,240 +1518,297 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>36.09999847412109</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0432691842646411</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>-0.0089743807627755</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.1020406439773782</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>34.53798098819109</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>35.77602334227872</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>39.78366556600278</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>34.20459175018073</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>35.61999893188477</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.0653061001718057</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0089037202852425</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.0346109210006035</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>33.29379571351949</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>35.30284842483463</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>36.85283990095781</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>33.29379571351949</v>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>96.19999694824219</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>-0.0435844439966387</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-0.005646063733711</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.0266034411993621</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>92.0071735687747</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>95.65684563428961</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>98.75924791043356</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>91.38999710083007</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>36.2599983215332</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0653061001718057</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.0210279373987021</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.0338076907416818</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>33.89199923891765</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>35.49752534675096</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>37.4858651310815</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>33.89199923891765</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="D15" s="17" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>-0.056962015212765</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>-0.016938908556182</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0.0772325318535918</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>68.37025389707453</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>71.27192912967681</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>78.09935855938541</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>68.37025389707453</v>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="M15" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>66.84999847412109</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.0627802516039144</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.012693954565347</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.06657407220854521</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>62.65313875019448</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>66.00140763079708</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>71.30047509967838</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>62.65313875019448</v>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="D16" s="17" t="n">
+        <v>19.35000038146973</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>-0.1036118867092948</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>0.0471306356513333</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>17.34511033412008</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>19.12063686208256</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>20.26197819930194</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>17.34511033412008</v>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>75.05000305175781</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.056962015212765</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.0169389726508262</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>0.1080536875032713</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>70.77500363620553</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>73.77873310261967</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>83.15943262863202</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>70.77500363620553</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>19.70999908447266</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.1036118867092948</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.0471306356513333</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>17.66780889229197</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>19.47636835227578</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>20.63894387001105</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>17.66780889229197</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
+      <c r="M16" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1831,7 +1838,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1848,7 +1855,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1930,7 +1937,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -1939,16 +1946,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0885167464114832</v>
+        <v>-0.1161405598570577</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>-0.0246694885084334</v>
+        <v>-0.06630545471470151</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.0247374545953591</v>
+        <v>-0.0034836882092904</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0713714963421137</v>
+        <v>-0.06869623298648229</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1956,7 +1963,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0194215259434294</v>
+        <v>0.0195645190366367</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1982,16 +1989,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-0.06721535049550589</v>
+        <v>-0.0549604248695095</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0124069478908188</v>
+        <v>-0.0068527123561459</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>-0.0111488270370058</v>
+        <v>-0.0235804094480834</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.1779043813425157</v>
+        <v>-0.2218187629716418</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1999,53 +2006,53 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0212480672808465</v>
+        <v>0.0211896104248744</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0185278352337725</v>
+        <v>0.0185277148899571</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0075471698113207</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.0587761934873471</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>-0.0607142857142857</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>-0.2401145978594463</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.0200154443855289</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.052422544830267</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-0.0453890699801251</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>-0.2655962934158726</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0221600754600607</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0567878660082687</v>
+      <c r="J6" s="18" t="n">
+        <v>0.022117758262729</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>-0.0082889988742848</v>
       </c>
     </row>
     <row r="7">
@@ -2064,20 +2071,20 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-0.0544511668107173</v>
+        <v>-0.0683012259194395</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.1385826771653543</v>
+        <v>-0.1713395638629283</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-0.1558641975308642</v>
+        <v>-0.1667971808927173</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.2990371871898438</v>
+        <v>-0.3045283536767756</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -2085,182 +2092,182 @@
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0179550241285408</v>
+        <v>0.0181503837264588</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>0.0115131578947369</v>
+        <v>-0.0241174841137557</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>-0.0038632228990456</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.08931801867797361</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>-0.0393827377547005</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>-0.2810937155408158</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.0262521718013245</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>-0.0089743807627755</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>-0.0283929575621983</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>-0.0398428224821392</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>-0.1496023424516733</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>-0.0475215182332378</v>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>0.0213113629797197</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.0125688346543615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>0.0033203910877523</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-0.1427896223278293</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>0.1682462518215937</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>-0.4166007613604728</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="E10" s="18" t="n">
+        <v>-0.0219659329291974</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>-0.1567235436440995</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1410975132262459</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>-0.4374885110924027</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>0.0238393622678929</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>-0.0210279373987021</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="J10" s="18" t="n">
+        <v>0.0239188266614011</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>-0.0089037202852425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>-0.0584988467066824</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>-0.035067855436785</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>-0.1512437507287779</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>-0.0469174948540891</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0102880661666325</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>-0.1333333608266469</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>-0.1784799470385798</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>-0.4297401766535514</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0213332669094879</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.0125687493441779</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>-0.0722597663968105</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>0.2349885919682477</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0.4288934039768077</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>-0.2797918847497309</v>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>0.0267961516085757</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0.0186683182612425</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.0237014466763041</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.1318385376523962</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.1676698150327801</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>-0.3947890261345917</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0201020435035757</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.0008189588123605</v>
+      <c r="J11" s="18" t="n">
+        <v>0.0201065650051323</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>-0.005646063733711</v>
       </c>
     </row>
     <row r="12">
@@ -2279,375 +2286,375 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-0.0502121014936132</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>0.009015754269078699</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-0.1489226840654248</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>-0.1727093423606177</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>0.0237856144820836</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>-0.1296752843077038</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.1574278255139025</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.3900210619989481</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>-0.2907817358936067</v>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>0.0276004494794109</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0.0195381803197951</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>-0.1210525914242393</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.1798648796241673</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>-0.3745318245039286</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>-0.1855480646588513</v>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>0.0184803206796285</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>0.020342480870896</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0656883910156765</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.0022488985418591</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-0.1478648683922098</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>-0.1463350037254664</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="E15" s="24" t="n">
+        <v>-0.1681009898953201</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.2643328487577674</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.3887015098417582</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.083775766156647</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="21" t="n">
-        <v>0.023782163861295</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>-0.012693954565347</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="J15" s="24" t="n">
+        <v>0.0158754109693756</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>-0.016938908556182</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="23" t="n">
-        <v>0.0107588072309898</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>0.08642727023240621</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>-0.0525477581263276</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>-0.2608541483895467</v>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="E16" s="22" t="n">
+        <v>-0.1348239046908782</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.2165644359003546</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>-0.3218268992107163</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>-0.2941763752031232</v>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="23" t="n">
-        <v>0.0262386681832899</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="J16" s="22" t="n">
+        <v>0.0184980759114234</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>0.0147321564810616</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>-0.09748134797235231</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>-0.1291628722130455</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>-0.1204545281150124</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.2354957719389704</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.0366080697765715</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.1052291054566574</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.1454993297703778</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.3468425631630822</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.184823647196279</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="E18" s="22" t="n">
+        <v>-0.1739894551845342</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>-0.2100840336134454</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>-0.2140468227424748</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>-0.2230967507945747</v>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0180080585291347</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.0417059171430678</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="J18" s="22" t="n">
+        <v>0.0258657962097724</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>0.0378562161969006</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="n">
-        <v>-0.163788266832782</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.2388437706573017</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-0.3629032164049853</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-0.0341178763549946</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>-0.1354795439302482</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>-0.129054054054054</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>-0.2267546490701859</v>
+      </c>
+      <c r="H19" s="22" t="n">
+        <v>0.0091614930640857</v>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0154349832021613</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>-0.0169389726508262</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="J19" s="22" t="n">
+        <v>0.032041761700043</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <v>0.0248447188033209</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.1498002693552206</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.2180037075212559</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.3174773234502706</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.2911065832810884</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="E20" s="22" t="n">
+        <v>-0.1039878607510293</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>-0.1861531208325939</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>-0.2542225752588232</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>-0.4324468295623667</v>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0184935998639454</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.0147321564810616</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="n">
-        <v>-0.08495829866634361</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.07551597717622929</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>-0.1065276717299021</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.2143560266767461</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="27" t="n">
-        <v>0.0369537734981878</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.1040157998683344</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0548611111111111</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.1736490588949605</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.018716959054709</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0315706199152426</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0339372257730323</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.1484320770157339</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.1853333536783854</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.1798657922936766</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.2416322795488767</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.02548291720417</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0428598924856524</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.1000497866408884</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1625752757792875</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.2381455010880332</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.4221787009784454</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0265453263368255</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.0905550690718651</v>
+      <c r="J20" s="22" t="n">
+        <v>0.0265684710708643</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <v>0.0569024956991131</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2679,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,7 +2687,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2705,7 +2712,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2724,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2736,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
+          <t>GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2748,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, TUPRS.IS, TCELL.IS, YKBNK.IS, FROTO.IS, PGSUS.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
+          <t>SAHOL.IS, AKBNK.IS, TUPRS.IS, FROTO.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2760,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2772,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2798,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2799,7 +2806,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2896,7 +2903,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3050,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3074,7 +3081,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11430.099609375</v>
+        <v>11797.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3084,7 +3091,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13623.40651855469</v>
+        <v>13626.08751953125</v>
       </c>
     </row>
     <row r="6">
@@ -3118,7 +3125,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="9">
@@ -3145,7 +3152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3153,7 +3160,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3161,7 +3168,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3175,7 +3182,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3239,23 +3246,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>204</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0.03553299492385786</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>103271.1328843357</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D4" s="25" t="n">
+        <v>202.8999938964844</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.02994920759636743</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>87042.72195722954</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="5">
@@ -3269,23 +3276,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>85.30000305175781</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>-0.1160621445413699</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>-10191.93681402173</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D5" s="25" t="n">
+        <v>85.55000305175781</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.1134714709662403</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-9964.438162434555</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="6">
@@ -3299,23 +3306,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>405.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>381</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.06041923551171391</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-171331.9322412787</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D6" s="25" t="n">
+        <v>371</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.0850801479654747</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-241263.333156086</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="7">
@@ -3329,23 +3336,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>69.30000305175781</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-0.1046511410133867</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-468532.056568299</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D7" s="25" t="n">
+        <v>66.80000305175781</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.1369508819786903</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-613140.7432443597</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="8">
@@ -3359,57 +3366,27 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="25" t="n">
         <v>387</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>375.5</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.02971576227390182</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-128314.6122865686</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-0.1446511824786558</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>1.862645149230957e-09</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D8" s="25" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.07816537467700257</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-337523.2192755393</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,6 +158,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -571,14 +579,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -607,7 +615,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -624,7 +632,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -675,7 +683,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.94/100</t>
+          <t>Güven Puanı: 81.03/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,7 +743,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS</t>
+          <t>AL: GARAN.IS, KCHOL.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
+          <t>ÇIK: BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -786,7 +794,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %60</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -884,7 +892,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 2</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -941,12 +949,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 3</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -955,25 +963,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.20384932543041</v>
+        <v>0.2225985965411588</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20384.932543041</v>
+        <v>22259.85965411588</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0567878719657279</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>387.9036602028913</v>
+        <v>1264.090060013005</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>378.0597367752586</v>
+        <v>142.2436540167083</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>352.45</v>
+        <v>125.881001496126</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805788019007337</v>
+        <v>0.8766651994557298</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -984,7 +992,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %60</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -998,25 +1006,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.19615067456959</v>
+        <v>0.2095677741579692</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19615.067456959</v>
+        <v>20956.77741579692</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0185277148899571</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>363.4223773898121</v>
+        <v>487.6239542214013</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>206.6592671345725</v>
+        <v>213.2490614352234</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>192.7549942016601</v>
+        <v>197.9799942016601</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3705542977991442</v>
+        <v>0.4653615816464596</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1025,42 +1033,83 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.167833629300872</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>16783.3629300872</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.007822546905052701</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>131.2886437451299</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>89.89776810830038</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>82.25680639116948</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.1004971927995564</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="D23" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K22"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1071,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1143,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1115,7 +1164,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1157,7 +1206,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 9</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1295,520 +1344,577 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>208.3999938964844</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0302466271968858</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.0914169657590902</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>202.0965969732642</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>213.2490614352234</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>227.4512890027139</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>197.9799942016601</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0475400966137377</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>-0.0036968334151564</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0383027129081878</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>367.1732927554041</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>384.0748707184572</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>400.2656958261064</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>366.225</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>371</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0205581560241685</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.0190289400950367</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0.06844627048378669</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>363.3729241150335</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>378.0597367752586</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>396.3935663494848</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>352.45</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="D10" s="15" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.06477714867772109</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.0567878719657279</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.1272216922975995</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>125.881001496126</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>142.2436540167083</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>151.7240466632721</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>125.881001496126</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
-        <is>
-          <t>trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O8" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="M10" s="14" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.0621242939763079</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.0948783870299643</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>256.5090055974798</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>269.6613787891161</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>299.4492388526953</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>256.5090055974798</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
-        <v>202.8999938964844</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0302466271968858</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.0185277148899571</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0.0466707608184535</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>196.762953422847</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>206.6592671345725</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>212.3694909816929</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>192.7549942016601</v>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N9" s="13" t="inlineStr">
-        <is>
-          <t>trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="D12" s="15" t="n">
+        <v>89.19999694824219</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.0778384618230588</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.007822546905052701</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.093714156045322</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>82.25680639116948</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>89.89776810830038</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>97.55929938149201</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>82.25680639116948</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0597513661055632</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.0082889988742848</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1264267348706023</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>124.5829439910129</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>131.4017076491573</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>149.2515423703548</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>124.5829439910129</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="D13" s="18" t="n">
+        <v>36.65999984741211</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.053387959227386</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-0.0095238211722357</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.0919879432419712</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>34.7027972702825</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>36.31085656469117</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>40.03227783262653</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>34.7027972702825</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="M13" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>266</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0628618693134822</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.128113826384147</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>249.2787427626137</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>259.584749225741</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>300.0782778181831</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>249.2787427626137</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="D14" s="18" t="n">
+        <v>37.18000030517578</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.0653061001718057</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>-0.0210280210184544</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.0345194815014007</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>34.75191948085821</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>36.3981784772924</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>38.46343463793237</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>34.75191948085821</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="M14" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>132</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.0759511873012769</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>-0.0097276264591439</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1305235121113319</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>121.9744432762314</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>130.715953307393</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>149.2291035986958</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>121.9744432762314</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
-        <v>36.09999847412109</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0432691842646411</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0089743807627755</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.1020406439773782</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>34.53798098819109</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>35.77602334227872</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>39.78366556600278</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>34.20459175018073</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="D16" s="18" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>-0.110731767703003</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>-0.0588766952961986</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.0478184256278046</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>304.7966866197957</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>322.570012687228</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>359.1397653839301</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>304.7966866197957</v>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="M16" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>35.61999893188477</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.0653061001718057</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.0089037202852425</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.0346109210006035</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>33.29379571351949</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>35.30284842483463</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>36.85283990095781</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>33.29379571351949</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="D17" s="18" t="n">
+        <v>19.60000038146973</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0502792716997244</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.0113636098814375</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>18.61452663697511</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>19.36767350917732</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>19.82272713948078</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>18.16560873150732</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>96.19999694824219</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.0435844439966387</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.005646063733711</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.0266034411993621</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>92.0071735687747</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>95.65684563428961</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>98.75924791043356</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>91.38999710083007</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>-0.056962015212765</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>-0.016938908556182</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.0772325318535918</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>68.37025389707453</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>71.27192912967681</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>78.09935855938541</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>68.37025389707453</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>19.35000038146973</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>-0.1036118867092948</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>0.0471306356513333</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>17.34511033412008</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>19.12063686208256</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>20.26197819930194</v>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v>17.34511033412008</v>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="M17" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O16" s="16" t="inlineStr">
+      <c r="O17" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O16"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1838,7 +1944,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1855,7 +1961,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1927,734 +2033,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>-0.0625281554856169</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.0514631539116814</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.0190708747994345</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-0.2313857694396462</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.0211053561538639</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>-0.1096997690531177</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>-0.0068319270468597</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.0451798027804024</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.0900637285735935</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0199896884255374</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>-0.0036968334151564</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.1161405598570577</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>-0.06630545471470151</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>-0.0034836882092904</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>-0.06869623298648229</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E6" s="16" t="n">
+        <v>0.0112697214967323</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.07680004882812499</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>-0.0175182036239734</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>-0.2872987491383497</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>0.0195645190366367</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0.0190289400950367</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="J6" s="16" t="n">
+        <v>0.0221699973140994</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.0567878719657279</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>-0.06814310051107331</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>-0.1254996003197441</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>-0.1379038613081166</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>-0.3211878254901774</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.0183237247160637</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.0549604248695095</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>-0.0068527123561459</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>-0.0235804094480834</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>-0.2218187629716418</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="E8" s="16" t="n">
+        <v>-0.0149089570184107</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0142126213004374</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>-0.1035176186106312</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>-0.0581451764026649</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.0219273868966153</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.007822546905052701</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>0.0021869330878356</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.1022249458045725</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>-0.0218783272369083</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>-0.2972354995612898</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="15" t="n">
-        <v>0.0211896104248744</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.0185277148899571</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="J9" s="19" t="n">
+        <v>0.0263089279639388</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>-0.0095238211722357</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>0.0200154443855289</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>0.052422544830267</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>-0.0453890699801251</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>-0.2655962934158726</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="E10" s="19" t="n">
+        <v>-0.005350475046135</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>-0.158823537026944</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.2195967321886922</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>-0.4672271139985361</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0.022117758262729</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>-0.0082889988742848</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="J10" s="19" t="n">
+        <v>0.0238351539109441</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>-0.0210280210184544</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-0.0225225221785121</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.06999998546781989</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>-0.1675191902357281</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>-0.4414806906738988</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0.019083963827017</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>0.0139752661812804</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.1196778060214621</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.2272727272727273</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>-0.3405172413793104</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>-0.08619076076584919</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0.0175460603555207</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>0.0318628326773948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.1115441285294764</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0.1716600104443737</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.3749516646374315</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>-0.3150624841004493</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>0.0276418940598797</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>0.0195382818194833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>-0.0572808015361147</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0.0186428030291823</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>-0.1254800974882294</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>-0.1873317437379973</v>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>0.0238625739044733</v>
+      </c>
+      <c r="K14" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>-0.1207450444460015</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>-0.13790937490181</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>-0.3536355433241898</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>-0.201379322000936</v>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>0.0185820899062162</v>
+      </c>
+      <c r="K15" s="23" t="n">
+        <v>0.0758986426936193</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>-0.0683012259194395</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>-0.1713395638629283</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>-0.1667971808927173</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-0.3045283536767756</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="E16" s="25" t="n">
+        <v>-0.1269841093635378</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.1770573252939933</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.2903225806451612</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.3213083269485385</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0181503837264588</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0190171517281646</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>-0.0097276264591439</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
-        <v>-0.0038632228990456</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>0.08931801867797361</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>-0.0393827377547005</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>-0.2810937155408158</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0262521718013245</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>-0.0089743807627755</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="E17" s="25" t="n">
+        <v>-0.0932539682539682</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>-0.08903654485049831</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.166058394160584</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0.0228223229737185</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.0330049754383154</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>-0.0588766952961986</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>-0.0283929575621983</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>-0.0398428224821392</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>-0.1496023424516733</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>-0.0475215182332378</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="E18" s="23" t="n">
+        <v>-0.1803448381095097</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>-0.1696069975607259</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>-0.1753686142298622</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>-0.2029227843381598</v>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="20" t="n">
-        <v>0.0213113629797197</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0.0125688346543615</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="J18" s="23" t="n">
+        <v>0.0255519291609806</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <v>0.0378562161969006</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0219659329291974</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.1567235436440995</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1410975132262459</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>-0.4374885110924027</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.0239188266614011</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>-0.0089037202852425</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="E19" s="25" t="n">
+        <v>-0.0798121557034113</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.1312056362829798</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.1358024639445516</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.2500893749285049</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0.0365916230113574</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0102880661666325</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.1333333608266469</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>-0.1784799470385798</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>-0.4297401766535514</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>-0.1020812405743142</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>-0.1703296376998283</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>-0.2172493539078707</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>-0.4529853867406843</v>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
-        <v>0.0201065650051323</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>-0.005646063733711</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>-0.0502121014936132</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>0.009015754269078699</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>-0.1489226840654248</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>-0.1727093423606177</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>0.0237856144820836</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>-0.1296752843077038</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>0.1574278255139025</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0.3900210619989481</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>-0.2907817358936067</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>0.0276004494794109</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0.0195381803197951</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.1210525914242393</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.1798648796241673</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>-0.3745318245039286</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>-0.1855480646588513</v>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>0.0184803206796285</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>0.020342480870896</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.1681009898953201</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.2643328487577674</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.3887015098417582</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.083775766156647</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0158754109693756</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>-0.016938908556182</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>-0.1348239046908782</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-0.2165644359003546</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>-0.3218268992107163</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>-0.2941763752031232</v>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="n">
-        <v>0.0184980759114234</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <v>0.0147321564810616</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>-0.09748134797235231</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.1291628722130455</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-0.1204545281150124</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.2354957719389704</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0366080697765715</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>-0.1739894551845342</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>-0.2100840336134454</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>-0.2140468227424748</v>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>-0.2230967507945747</v>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>0.0258657962097724</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>0.0378562161969006</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>-0.1354795439302482</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>-0.129054054054054</v>
-      </c>
-      <c r="G19" s="22" t="n">
-        <v>-0.2267546490701859</v>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>0.0091614930640857</v>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="n">
-        <v>0.032041761700043</v>
-      </c>
-      <c r="K19" s="22" t="n">
-        <v>0.0248447188033209</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>-0.1039878607510293</v>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>-0.1861531208325939</v>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>-0.2542225752588232</v>
-      </c>
-      <c r="H20" s="22" t="n">
-        <v>-0.4324468295623667</v>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="n">
-        <v>0.0265684710708643</v>
-      </c>
-      <c r="K20" s="22" t="n">
-        <v>0.0569024956991131</v>
+      <c r="J20" s="23" t="n">
+        <v>0.0267319379708561</v>
+      </c>
+      <c r="K20" s="23" t="n">
+        <v>0.0595845018212652</v>
       </c>
     </row>
   </sheetData>
@@ -2679,7 +2785,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2687,7 +2793,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2712,7 +2818,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS</t>
+          <t>KCHOL.IS, GARAN.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2842,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
+          <t>BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2854,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, AKBNK.IS, TUPRS.IS, FROTO.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
+          <t>TCELL.IS, ARCLK.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2866,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.78 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2878,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2904,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2806,7 +2912,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2973,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2903,7 +3009,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3057,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3155,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3057,7 +3163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3081,7 +3187,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11797.7001953125</v>
+        <v>11577.099609375</v>
       </c>
     </row>
     <row r="5">
@@ -3091,7 +3197,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13626.08751953125</v>
+        <v>13626.481015625</v>
       </c>
     </row>
     <row r="6">
@@ -3125,7 +3231,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.94</v>
+        <v>81.03</v>
       </c>
     </row>
     <row r="9">
@@ -3157,18 +3263,18 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3182,7 +3288,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3246,23 +3352,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="26" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>202.8999938964844</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.02994920759636743</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>87042.72195722954</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>-0.1659296840794658</v>
+      <c r="D4" s="26" t="n">
+        <v>208.3999938964844</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>0.05786798932225579</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>168184.326366351</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="5">
@@ -3276,113 +3382,113 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>85.55000305175781</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.1134714709662403</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-9964.438162434555</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>-0.1659296840794658</v>
+      <c r="D5" s="26" t="n">
+        <v>89.19999694824219</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>-0.07564770001821564</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>-6642.963403428294</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>371</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.0850801479654747</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-241263.333156086</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>-0.1659296840794658</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>77.40000152587891</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>68.44999694824219</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>-0.1156331317983793</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>-517699.3630867111</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>77.40000152587891</v>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>66.80000305175781</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.1369508819786903</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-613140.7432443597</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>-0.1659296840794658</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>387</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>362</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>-0.06459948320413433</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>-278944.8093186272</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>387</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>356.75</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.07816537467700257</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-337523.2192755393</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>-0.1659296840794658</v>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,7 +157,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -181,31 +190,31 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,7 +596,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -615,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -632,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -683,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 81.03/100</t>
+          <t>Güven Puanı: 80.80/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -760,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: -</t>
+          <t>AZALT: BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -777,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
+          <t>ÇIK: YKBNK.IS, THYAO.IS, ARCLK.IS, PGSUS.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2225985965411588</v>
+        <v>0.2253112896284994</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22259.85965411588</v>
+        <v>22531.12896284994</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0567878719657279</v>
+        <v>0.05678787196572799</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1264.090060013005</v>
+        <v>1279.494866785628</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>142.2436540167083</v>
+        <v>140.1300782727768</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>125.881001496126</v>
+        <v>125.9700057983398</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8766651994557298</v>
+        <v>1.135757439314558</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2095677741579692</v>
+        <v>0.2055238060841062</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20956.77741579692</v>
+        <v>20552.38060841062</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.01852771488995719</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>487.6239542214013</v>
+        <v>380.7886482225169</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>213.2490614352234</v>
+        <v>207.0666875454282</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>197.9799942016601</v>
+        <v>193.1350028991699</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4653615816464596</v>
+        <v>0.3705542977991433</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1047,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.167833629300872</v>
+        <v>0.1691649042873944</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>16783.3629300872</v>
+        <v>16916.49042873943</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.007822546905052701</v>
+        <v>0.01031479137899316</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>131.2886437451299</v>
+        <v>174.4900696371818</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>89.89776810830038</v>
+        <v>89.05925040167628</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>82.25680639116948</v>
+        <v>81.14630294548057</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1004971927995564</v>
+        <v>0.1298241015600161</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1120,16 +1129,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
@@ -1143,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1164,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1206,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1349,45 +1358,45 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>208.3999938964844</v>
+        <v>385.5</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0302466271968858</v>
+        <v>-0.02055785179873293</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.006068867739039252</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0914169657590902</v>
+        <v>0.06844627048378671</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>202.0965969732642</v>
+        <v>377.5749481315884</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>213.2490614352234</v>
+        <v>387.8395485133996</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>227.4512890027139</v>
+        <v>411.8860372714998</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>197.9799942016601</v>
+        <v>366.225</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>81.03</v>
+        <v>80.8</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1406,515 +1415,458 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>203.3000030517578</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.03024662719688587</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.01852771488995719</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0466707658152421</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>197.1508636503255</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>207.0666875454282</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>212.7881698844244</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>193.1350028991699</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.0446736587600064</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.05678787196572799</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.1240418332017574</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>126.6762786792724</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>140.1300782727768</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>149.0479539431599</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>125.9700057983398</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>385.5</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0475400966137377</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>-0.0036968334151564</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.0383027129081878</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>367.1732927554041</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>384.0748707184572</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>400.2656958261064</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>366.225</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="D11" s="21" t="n">
+        <v>36.41999816894531</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.02777781264366352</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>-0.00924906731649483</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.07188239616583897</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>35.40833028332578</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>36.08314715421412</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>39.03795490568457</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>34.50212993691391</v>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="M11" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
-        <v>134.6000061035156</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.06477714867772109</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0567878719657279</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.1272216922975995</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>125.881001496126</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>142.2436540167083</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>151.7240466632721</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>125.881001496126</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="D12" s="18" t="n">
+        <v>88.15000152587891</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.07945205285495327</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.01031479137899316</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.09404613143246554</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>81.14630294548057</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>89.05925040167628</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>96.44016815515374</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>81.14630294548057</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
-        <v>273.5</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.0621242939763079</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>-0.0140351781019522</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.0948783870299643</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>256.5090055974798</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>269.6613787891161</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>299.4492388526953</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>256.5090055974798</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="D13" s="21" t="n">
+        <v>265</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.06286186931348225</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.03419979012555929</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.05123038157605908</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>248.3416046319272</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>255.9370556167268</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>278.5760511176557</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>248.3416046319272</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M13" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>89.19999694824219</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0778384618230588</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.007822546905052701</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.093714156045322</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>82.25680639116948</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>89.89776810830038</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>97.55929938149201</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>82.25680639116948</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>-0.056962015212765</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.01693897265082622</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>0.1111908721424226</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>70.25632986664901</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>73.23804653751344</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>82.78371997461049</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>70.25632986664901</v>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="M14" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>36.65999984741211</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.053387959227386</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.0095238211722357</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.0919879432419712</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>34.7027972702825</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>36.31085656469117</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>40.03227783262653</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>34.7027972702825</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="D15" s="21" t="n">
+        <v>129.3000030517578</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>-0.05370672771557694</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-0.02052976338254109</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>0.1090029643218295</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>122.3557229942338</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>126.6455045837434</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>143.394086671221</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>122.3557229942338</v>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="M15" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>37.18000030517578</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.0653061001718057</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>-0.0210280210184544</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.0345194815014007</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>34.75191948085821</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>36.3981784772924</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>38.46343463793237</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>34.75191948085821</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="D16" s="21" t="n">
+        <v>19.04999923706055</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>-0.1689400445284157</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.05027927169972446</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>0.01865484715630311</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>15.83169151768525</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>18.09217914954084</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>19.4053740611556</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>15.83169151768525</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>132</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0759511873012769</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>-0.0097276264591439</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1305235121113319</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>121.9744432762314</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>130.715953307393</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>149.2291035986958</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>121.9744432762314</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>342.75</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>-0.110731767703003</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>-0.0588766952961986</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.0478184256278046</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>304.7966866197957</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>322.570012687228</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>359.1397653839301</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>304.7966866197957</v>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="M16" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>19.60000038146973</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>-0.0502792716997244</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.0113636098814375</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>18.61452663697511</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>19.36767350917732</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>19.82272713948078</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>18.16560873150732</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1932,19 +1884,19 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1961,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2038,7 +1990,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -2048,20 +2000,20 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.0625281554856169</v>
+        <v>-0.1040092969203951</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.0514631539116814</v>
+        <v>0.01993983580440606</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.0190708747994345</v>
+        <v>0.01922116148021913</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.2313857694396462</v>
+        <v>-0.09548611179691424</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2069,10 +2021,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0211053561538639</v>
+        <v>0.01970341923595139</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.006068867739039252</v>
       </c>
     </row>
     <row r="5">
@@ -2081,7 +2033,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -2091,332 +2043,332 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>-0.08050656969870962</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.02884613751102894</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>-0.04013219961060555</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.2427035483688954</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.02134321070648489</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.01852771488995719</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>-0.009708647141341564</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.05238100082155261</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.09426221563046211</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.3034241564012312</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>0.022247395736596</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.05678787196572799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.1096997690531177</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>-0.0068319270468597</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.0451798027804024</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0900637285735935</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E7" s="22" t="n">
+        <v>-0.009249188468779868</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>0.09172654384317469</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>-0.07328247134924482</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>-0.3067808245277756</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0199896884255374</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>-0.0036968334151564</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="J7" s="22" t="n">
+        <v>0.02632987820502872</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>-0.00924906731649483</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0112697214967323</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.07680004882812499</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>-0.0175182036239734</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>-0.2872987491383497</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="E8" s="19" t="n">
+        <v>-0.03291278057903546</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.01205514431862809</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>-0.1612749495178709</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>-0.06089244453678866</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0.02194467792107834</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0.01031479137899316</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>-0.1107382550335571</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>-0.1506410256410257</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>-0.1945288753799392</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-0.3526028585518355</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>0.01868741571633192</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>-0.03419979012555929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>-0.03437332753967359</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>-0.1561922022226782</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>0.1553234033959283</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>-0.4698951097882514</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>0.0221699973140994</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.0567878719657279</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="J10" s="24" t="n">
+        <v>0.02380020121545784</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.06814310051107331</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>-0.1254996003197441</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>-0.1379038613081166</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>-0.3211878254901774</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>-0.05284150439180801</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.0838958264635673</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>-0.2116182572614108</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>-0.4329946693010961</v>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0183237247160637</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>-0.0140351781019522</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J11" s="24" t="n">
+        <v>0.01931544065071443</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.01245929909775567</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0149089570184107</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0142126213004374</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>-0.1035176186106312</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>-0.0581451764026649</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>0.0219273868966153</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.007822546905052701</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>0.0021869330878356</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.1022249458045725</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>-0.0218783272369083</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>-0.2972354995612898</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>-0.07887210208546558</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>0.2019319283588819</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>0.4454062761127906</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>-0.3490137343630424</v>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="19" t="n">
-        <v>0.0263089279639388</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>-0.0095238211722357</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.005350475046135</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>-0.158823537026944</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.2195967321886922</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>-0.4672271139985361</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0238351539109441</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>-0.0210280210184544</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0225225221785121</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.06999998546781989</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.1675191902357281</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>-0.4414806906738988</v>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>0.019083963827017</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0.0139752661812804</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.1196778060214621</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.2272727272727273</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-0.3405172413793104</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>-0.08619076076584919</v>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>0.0175460603555207</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>0.0318628326773948</v>
+      <c r="J12" s="24" t="n">
+        <v>0.02730165577321778</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0.01866835301293379</v>
       </c>
     </row>
     <row r="13">
@@ -2425,7 +2377,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2435,332 +2387,332 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.1534090909090909</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.2474747474747475</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>-0.3723672964163184</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>-0.1084551721176786</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>0.01775942047506572</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>-0.01693897265082622</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.1115441285294764</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>0.1716600104443737</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.3749516646374315</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>-0.3150624841004493</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>0.0276418940598797</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>0.0195382818194833</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="E14" s="26" t="n">
+        <v>-0.1559343301767033</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-0.1537974876693532</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-0.3883806348800831</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>-0.2265403160351237</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.01877018636727422</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0.1100915187953706</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>-0.1454064742647366</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>-0.1998762489592203</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>-0.3433214471315104</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>-0.3450696693831004</v>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>0.01909646760520952</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>-0.02052976338254109</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="23" t="n">
-        <v>-0.0572808015361147</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>0.0186428030291823</v>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>-0.1254800974882294</v>
-      </c>
-      <c r="H14" s="23" t="n">
-        <v>-0.1873317437379973</v>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="E16" s="26" t="n">
+        <v>-0.08071137686777963</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.005917182469050486</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.1956912687769392</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>-0.2002797183603302</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="23" t="n">
-        <v>0.0238625739044733</v>
-      </c>
-      <c r="K14" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="J16" s="26" t="n">
+        <v>0.02393358873201926</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0.02272459099683133</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="23" t="n">
-        <v>-0.1207450444460015</v>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>-0.13790937490181</v>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>-0.3536355433241898</v>
-      </c>
-      <c r="H15" s="23" t="n">
-        <v>-0.201379322000936</v>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="E17" s="26" t="n">
+        <v>-0.07676902536715624</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-0.09072978303747536</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-0.1648550724637681</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>0.05168476071470662</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="23" t="n">
-        <v>0.0185820899062162</v>
-      </c>
-      <c r="K15" s="23" t="n">
-        <v>0.0758986426936193</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="J17" s="26" t="n">
+        <v>0.03299519539563162</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.07743072735755496</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.1269841093635378</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.1770573252939933</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.2903225806451612</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.3213083269485385</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="E18" s="28" t="n">
+        <v>-0.08938818510581359</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.1348774368283894</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>-0.1333030193902212</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.2567757456456938</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0190171517281646</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>-0.0097276264591439</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="J18" s="28" t="n">
+        <v>0.03663594021851863</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>-0.05027927169972446</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.0932539682539682</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.08903654485049831</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>-0.166058394160584</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>0.0228223229737185</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>-0.1968282153427864</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>-0.1889679932509453</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>-0.2261460309117679</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>-0.1869806033062829</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0330049754383154</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>-0.0588766952961986</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="J19" s="26" t="n">
+        <v>0.02593876575596387</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0.03285253990814896</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="23" t="n">
-        <v>-0.1803448381095097</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>-0.1696069975607259</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>-0.1753686142298622</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>-0.2029227843381598</v>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="E20" s="26" t="n">
+        <v>-0.1241927523212472</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-0.1879318330613905</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-0.2611033187848746</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>-0.4636418708734003</v>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="23" t="n">
-        <v>0.0255519291609806</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>0.0378562161969006</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0798121557034113</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.1312056362829798</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.1358024639445516</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.2500893749285049</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0365916230113574</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>-0.1020812405743142</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <v>-0.1703296376998283</v>
-      </c>
-      <c r="G20" s="23" t="n">
-        <v>-0.2172493539078707</v>
-      </c>
-      <c r="H20" s="23" t="n">
-        <v>-0.4529853867406843</v>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="n">
-        <v>0.0267319379708561</v>
-      </c>
-      <c r="K20" s="23" t="n">
-        <v>0.0595845018212652</v>
+      <c r="J20" s="26" t="n">
+        <v>0.02690597743166475</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>0.1001576921543033</v>
       </c>
     </row>
   </sheetData>
@@ -2785,7 +2737,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2793,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2830,7 +2782,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2794,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
+          <t>YKBNK.IS, THYAO.IS, ARCLK.IS, PGSUS.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2806,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, ARCLK.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, TOASO.IS, SISE.IS</t>
+          <t>EREGL.IS, TCELL.IS, TUPRS.IS, FROTO.IS, AKBNK.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2818,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.78 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.03 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2856,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2912,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3155,7 +3107,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3163,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3187,7 +3139,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11577.099609375</v>
+        <v>11220.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3197,7 +3149,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13626.481015625</v>
+        <v>13624.07301757812</v>
       </c>
     </row>
     <row r="6">
@@ -3231,7 +3183,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>81.03</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="9">
@@ -3268,13 +3220,13 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3288,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3352,23 +3304,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="29" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="26" t="n">
-        <v>208.3999938964844</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>0.05786798932225579</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>168184.326366351</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D4" s="29" t="n">
+        <v>203.3000030517578</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0.03197971092262852</v>
+      </c>
+      <c r="F4" s="29" t="n">
+        <v>92944.06461854326</v>
+      </c>
+      <c r="G4" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H4" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="5">
@@ -3382,23 +3334,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="29" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="26" t="n">
-        <v>89.19999694824219</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>-0.07564770001821564</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>-6642.963403428294</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D5" s="29" t="n">
+        <v>88.15000152587891</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>-0.0865284815971098</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>-7598.453574469648</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="6">
@@ -3412,23 +3364,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="29" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>68.44999694824219</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>-0.1156331317983793</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>-517699.3630867111</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D6" s="29" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>-0.1363049463019763</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>-610248.8342972519</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="7">
@@ -3442,23 +3394,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="29" t="n">
         <v>387</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>362</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>-0.06459948320413433</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>-278944.8093186272</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D7" s="29" t="n">
+        <v>359.25</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>-0.07170542635658916</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>-309628.7383436766</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="8">
@@ -3472,23 +3424,23 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="29" t="n">
         <v>134.6000061035156</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>134.6000061035156</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D8" s="29" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>-0.01485884033661844</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>-267407.6121233664</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,15 +188,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.80/100</t>
+          <t>Güven Puanı: 79.14/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: GARAN.IS, KCHOL.IS, SAHOL.IS</t>
+          <t>AL: GARAN.IS, SAHOL.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: BIMAS.IS</t>
+          <t>AZALT: KCHOL.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: YKBNK.IS, THYAO.IS, ARCLK.IS, PGSUS.IS, PETKM.IS</t>
+          <t>ÇIK: THYAO.IS, TUPRS.IS, EREGL.IS, PGSUS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2253112896284994</v>
+        <v>0.2062966470662178</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22531.12896284994</v>
+        <v>20629.66470662178</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.05678787196572799</v>
+        <v>0.03311743610603668</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1279.494866785628</v>
+        <v>683.2016028105068</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>140.1300782727768</v>
+        <v>132.7555905396257</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>125.9700057983398</v>
+        <v>122.075</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.135757439314558</v>
+        <v>0.6623487221207304</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,29 +1015,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2055238060841062</v>
+        <v>0.2052078655889579</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20552.38060841062</v>
+        <v>20520.78655889579</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.01852771488995719</v>
+        <v>0.02241108024750615</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>380.7886482225169</v>
+        <v>459.8929943133593</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>207.0666875454282</v>
+        <v>89.51209319582017</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>193.1350028991699</v>
+        <v>80.12817985417844</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3705542977991433</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.2643676751424494</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1691649042873944</v>
+        <v>0.1884954873448242</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>16916.49042873943</v>
+        <v>18849.54873448243</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.01031479137899316</v>
+        <v>0.01547529527999503</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>174.4900696371818</v>
+        <v>291.7023325607721</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>89.05925040167628</v>
+        <v>94.74384814860821</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>81.14630294548057</v>
+        <v>88.63500289916992</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1298241015600161</v>
+        <v>0.3095059055999017</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1358,37 +1358,37 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>385.5</v>
+        <v>87.55000305175781</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.02055785179873293</v>
+        <v>-0.08477239222015492</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.006068867739039252</v>
+        <v>0.02241108024750615</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.06844627048378671</v>
+        <v>0.1293436503428227</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>377.5749481315884</v>
+        <v>80.12817985417844</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>387.8395485133996</v>
+        <v>89.51209319582017</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>411.8860372714998</v>
+        <v>98.87404003399743</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>366.225</v>
+        <v>80.12817985417844</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1396,16 +1396,16 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>3A momentum destekli; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1420,49 +1420,49 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>203.3000030517578</v>
+        <v>196.1000061035156</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>-0.03024662719688587</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.01852771488995719</v>
+        <v>0.01244258503774698</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.0466707658152421</v>
+        <v>0.07297590341186155</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>197.1508636503255</v>
+        <v>190.1686423255956</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>207.0666875454282</v>
+        <v>198.5399971053613</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>212.7881698844244</v>
+        <v>210.4105812079912</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>193.1350028991699</v>
+        <v>186.2950057983398</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O9" s="17" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1472,168 +1472,168 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>369</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.01299463649111321</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.01286270803657807</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.0890313241273375</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>364.2049791347793</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>373.7463392654973</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>401.8525586029875</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>132.6000061035156</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0446736587600064</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.05678787196572799</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1240418332017574</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>126.6762786792724</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>140.1300782727768</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>149.0479539431599</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>125.9700057983398</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.04923849891315546</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.03311743610603668</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.07411146367770827</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>122.1728528896595</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>132.7555905396257</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>138.0233230825855</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>122.075</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>36.41999816894531</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.02777781264366352</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-0.00924906731649483</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.07188239616583897</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>35.40833028332578</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>36.08314715421412</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>39.03795490568457</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>34.50212993691391</v>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="M11" s="14" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>93.30000305175781</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.04480283081837821</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.01547529527999503</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.06738542065873321</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>89.11989879967574</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>94.74384814860821</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>99.58706300486161</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>88.63500289916992</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="20" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>88.15000152587891</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.07945205285495327</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.01031479137899316</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.09404613143246554</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>81.14630294548057</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>89.05925040167628</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>96.44016815515374</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>81.14630294548057</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M12" s="14" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.06286186931348225</v>
+        <v>-0.05964963819696248</v>
       </c>
       <c r="F13" s="22" t="n">
         <v>-0.03419979012555929</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.05123038157605908</v>
+        <v>0.1088930485621326</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>248.3416046319272</v>
+        <v>243.5507437069867</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>255.9370556167268</v>
+        <v>250.1422543574801</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>278.5760511176557</v>
+        <v>287.2032995775924</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>248.3416046319272</v>
+        <v>243.5507437069867</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1696,11 +1696,11 @@
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1709,28 +1709,28 @@
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>74.5</v>
+        <v>352.25</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.056962015212765</v>
+        <v>-0.06378737541528234</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.01693897265082622</v>
+        <v>-0.004932991768213713</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.1111908721424226</v>
+        <v>0.1114567484586793</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>70.25632986664901</v>
+        <v>329.7808970099668</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>73.23804653751344</v>
+        <v>350.5123536496467</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>82.78371997461049</v>
+        <v>391.5106396445698</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>70.25632986664901</v>
+        <v>329.7808970099668</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1738,26 +1738,26 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -1766,28 +1766,28 @@
         </is>
       </c>
       <c r="D15" s="21" t="n">
-        <v>129.3000030517578</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.05370672771557694</v>
+        <v>-0.06530610017180571</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.02052976338254109</v>
+        <v>-0.0327142098683611</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.1090029643218295</v>
+        <v>0.03380764349298043</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>122.3557229942338</v>
+        <v>32.80775445773991</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>126.6455045837434</v>
+        <v>33.95172975765954</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>143.394086671221</v>
+        <v>36.28664670913834</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>122.3557229942338</v>
+        <v>32.80775445773991</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -1795,26 +1795,26 @@
         </is>
       </c>
       <c r="M15" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>19.04999923706055</v>
+        <v>126.4000015258789</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.1689400445284157</v>
+        <v>-0.05280088922285953</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.05027927169972446</v>
+        <v>-0.01999250815041453</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.01865484715630311</v>
+        <v>0.07265370930011067</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>15.83169151768525</v>
+        <v>119.7259690475417</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>18.09217914954084</v>
+        <v>123.8729484651604</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>19.4053740611556</v>
+        <v>135.5834304922737</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>15.83169151768525</v>
+        <v>119.7259690475417</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="M16" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>Model skoru portföy için yeterli</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -1896,7 +1896,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1913,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -2000,31 +2000,31 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.1040092969203951</v>
+        <v>-0.03896811725382998</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.01993983580440606</v>
+        <v>0.005166527962344514</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.01922116148021913</v>
+        <v>-0.1491739382555853</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.09548611179691424</v>
+        <v>-0.04844649347959362</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.01970341923595139</v>
+        <v>0.02196356699278244</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.006068867739039252</v>
+        <v>0.02241108024750615</v>
       </c>
     </row>
     <row r="5">
@@ -2043,31 +2043,31 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.08050656969870962</v>
+        <v>-0.113071005472046</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.02884613751102894</v>
+        <v>-0.003050283955441269</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.04013219961060555</v>
+        <v>-0.05721150911771333</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>-0.2427035483688954</v>
+        <v>-0.2468483865708974</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.02134321070648489</v>
+        <v>0.02181413948502545</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.01852771488995719</v>
+        <v>0.01244258503774698</v>
       </c>
     </row>
     <row r="6">
@@ -2076,127 +2076,127 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>-0.1492795389048991</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>-0.03135733752469394</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.01278883216321314</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.07347950792520175</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>0.02041898757966615</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.01286270803657807</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
-        <v>-0.009708647141341564</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.05238100082155261</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>-0.09426221563046211</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.3034241564012312</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>0.022247395736596</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.05678787196572799</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="E7" s="16" t="n">
+        <v>-0.0396113821440468</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.01101496099674582</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>-0.1076388888888888</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>-0.2927906668456071</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.02258494644566083</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0.03311743610603668</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>-0.009249188468779868</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>0.09172654384317469</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>-0.07328247134924482</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>-0.3067808245277756</v>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>0.02632987820502872</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>-0.00924906731649483</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E8" s="19" t="n">
-        <v>-0.03291278057903546</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0.01205514431862809</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>-0.1612749495178709</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>-0.06089244453678866</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="E8" s="16" t="n">
+        <v>-0.07440475965212989</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>-0.08797653696497476</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>-0.2073066654981658</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>-0.4243953306595553</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="19" t="n">
-        <v>0.02194467792107834</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>0.01031479137899316</v>
+      <c r="J8" s="16" t="n">
+        <v>0.01936842231179195</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.01547529527999503</v>
       </c>
     </row>
     <row r="9">
@@ -2219,16 +2219,16 @@
         </is>
       </c>
       <c r="E9" s="22" t="n">
-        <v>-0.1107382550335571</v>
+        <v>-0.1323283082077052</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-0.1506410256410257</v>
+        <v>-0.1855345911949685</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>-0.1945288753799392</v>
+        <v>-0.210967250571211</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>-0.3526028585518355</v>
+        <v>-0.3540421314127118</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
@@ -2236,96 +2236,96 @@
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.01868741571633192</v>
+        <v>0.01864965832453677</v>
       </c>
       <c r="K9" s="22" t="n">
         <v>-0.03419979012555929</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>-0.1275855678325234</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>0.2269027416333513</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>0.4061268119256807</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>-0.3715833849196634</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>0.02691085205225696</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>-0.004932991768213713</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>-0.03437332753967359</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>-0.1561922022226782</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>0.1553234033959283</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>-0.4698951097882514</v>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.08925797508272271</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>-0.1886269108649126</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.06838608486729369</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>-0.4772503930064406</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="24" t="n">
-        <v>0.02380020121545784</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>-0.05284150439180801</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>-0.0838958264635673</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>-0.2116182572614108</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>-0.4329946693010961</v>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="24" t="n">
-        <v>0.01931544065071443</v>
-      </c>
-      <c r="K11" s="24" t="n">
-        <v>0.01245929909775567</v>
+      <c r="J11" s="22" t="n">
+        <v>0.02423775780536394</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>-0.0327142098683611</v>
       </c>
     </row>
     <row r="12">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -2348,70 +2348,70 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.07887210208546558</v>
+        <v>-0.1522292604871617</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>0.2019319283588819</v>
+        <v>-0.1495207277730631</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>0.4454062761127906</v>
+        <v>-0.3809302041696948</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.3490137343630424</v>
+        <v>-0.2355839815390756</v>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.02730165577321778</v>
+        <v>0.01875057637810846</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.01866835301293379</v>
+        <v>0.04368743118530438</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="n">
+      <c r="A13" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.1534090909090909</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>-0.2474747474747475</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>-0.3723672964163184</v>
-      </c>
-      <c r="H13" s="22" t="n">
-        <v>-0.1084551721176786</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>-0.04229938525245114</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>0.07355617193639818</v>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>-0.08780995399506775</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>-0.2767307164932796</v>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="22" t="n">
-        <v>0.01775942047506572</v>
-      </c>
-      <c r="K13" s="22" t="n">
-        <v>-0.01693897265082622</v>
+      <c r="J13" s="24" t="n">
+        <v>0.0265660993359823</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>0.001239185781908958</v>
       </c>
     </row>
     <row r="14">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.1559343301767033</v>
+        <v>-0.1913929891482883</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.1537974876693532</v>
+        <v>-0.2809667741030851</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.3883806348800831</v>
+        <v>-0.3865979330764465</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>-0.2265403160351237</v>
+        <v>-0.1116852269527451</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -2451,96 +2451,96 @@
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.01877018636727422</v>
+        <v>0.01834134569296302</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0.1100915187953706</v>
+        <v>0.03186277085667322</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="27" t="n">
+      <c r="A15" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="27" t="inlineStr">
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>-0.114461944118317</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>-0.02784045988086437</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>-0.2107513783943932</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>-0.1733867881279962</v>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.02433725202415014</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>0.01324791187551166</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C15" s="27" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="27" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E15" s="28" t="n">
-        <v>-0.1454064742647366</v>
-      </c>
-      <c r="F15" s="28" t="n">
-        <v>-0.1998762489592203</v>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>-0.3433214471315104</v>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>-0.3450696693831004</v>
-      </c>
-      <c r="I15" s="27" t="inlineStr">
+      <c r="E16" s="28" t="n">
+        <v>-0.1590153096513819</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>-0.2178218022782051</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>-0.3467700179541142</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>-0.3473773658516691</v>
+      </c>
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="28" t="n">
-        <v>0.01909646760520952</v>
-      </c>
-      <c r="K15" s="28" t="n">
-        <v>-0.02052976338254109</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>-0.08071137686777963</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.005917182469050486</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.1956912687769392</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>-0.2002797183603302</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.02393358873201926</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.02272459099683133</v>
+      <c r="J16" s="28" t="n">
+        <v>0.01924144956922427</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <v>-0.01999250815041453</v>
       </c>
     </row>
     <row r="17">
@@ -2563,16 +2563,16 @@
         </is>
       </c>
       <c r="E17" s="26" t="n">
-        <v>-0.07676902536715624</v>
+        <v>-0.1133682830930537</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>-0.09072978303747536</v>
+        <v>-0.06171983356449373</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>-0.1648550724637681</v>
+        <v>-0.1709558823529411</v>
       </c>
       <c r="H17" s="26" t="n">
-        <v>0.05168476071470662</v>
+        <v>0.06755887619341205</v>
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
@@ -2580,53 +2580,53 @@
         </is>
       </c>
       <c r="J17" s="26" t="n">
-        <v>0.03299519539563162</v>
+        <v>0.03245732562343681</v>
       </c>
       <c r="K17" s="26" t="n">
-        <v>0.07743072735755496</v>
+        <v>0.0723430136440395</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n">
+      <c r="A18" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="n">
-        <v>-0.08938818510581359</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>-0.1348774368283894</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>-0.1333030193902212</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>-0.2567757456456938</v>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.1982078962428595</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.1790825800064507</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>-0.2339041200402665</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>-0.1680410891024359</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="28" t="n">
-        <v>0.03663594021851863</v>
-      </c>
-      <c r="K18" s="28" t="n">
-        <v>-0.05027927169972446</v>
+      <c r="J18" s="26" t="n">
+        <v>0.02578066762240372</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.009589578526037035</v>
       </c>
     </row>
     <row r="19">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
@@ -2649,16 +2649,16 @@
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>-0.1968282153427864</v>
+        <v>-0.2043478592582371</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>-0.1889679932509453</v>
+        <v>-0.09226193573559605</v>
       </c>
       <c r="G19" s="26" t="n">
-        <v>-0.2261460309117679</v>
+        <v>-0.185943077860043</v>
       </c>
       <c r="H19" s="26" t="n">
-        <v>-0.1869806033062829</v>
+        <v>-0.2646692436810894</v>
       </c>
       <c r="I19" s="25" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.02593876575596387</v>
+        <v>0.03541162207403946</v>
       </c>
       <c r="K19" s="26" t="n">
-        <v>0.03285253990814896</v>
+        <v>0.1001577768561146</v>
       </c>
     </row>
     <row r="20">
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.1241927523212472</v>
+        <v>-0.1564356301020394</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1879318330613905</v>
+        <v>-0.2067038510861499</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-0.2611033187848746</v>
+        <v>-0.2789696619621984</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>-0.4636418708734003</v>
+        <v>-0.4715708320331669</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.02690597743166475</v>
+        <v>0.02716394562150875</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.1001576921543033</v>
+        <v>0.05973090857545427</v>
       </c>
     </row>
   </sheetData>
@@ -2737,7 +2737,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2745,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, GARAN.IS, SAHOL.IS</t>
+          <t>SAHOL.IS, GARAN.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS, BIMAS.IS</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, THYAO.IS, ARCLK.IS, PGSUS.IS, PETKM.IS</t>
+          <t>THYAO.IS, TUPRS.IS, EREGL.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, TCELL.IS, TUPRS.IS, FROTO.IS, AKBNK.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
+          <t>FROTO.IS, YKBNK.IS, ARCLK.IS, AKBNK.IS, ASELS.IS, TOASO.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.03 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.55 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2864,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3115,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11220.400390625</v>
+        <v>11117</v>
       </c>
     </row>
     <row r="5">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13624.07301757812</v>
+        <v>13619.53901855469</v>
       </c>
     </row>
     <row r="6">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
     </row>
     <row r="9">
@@ -3226,7 +3226,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,19 +3308,19 @@
         <v>197</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>203.3000030517578</v>
+        <v>196.1000061035156</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>0.03197971092262852</v>
+        <v>-0.00456849693646888</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>92944.06461854326</v>
+        <v>-13277.62703984696</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>28683903.43350858</v>
+        <v>27933492.00133482</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1552028889831436</v>
+        <v>-0.1812317286467454</v>
       </c>
     </row>
     <row r="5">
@@ -3338,19 +3338,19 @@
         <v>96.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>88.15000152587891</v>
+        <v>87.55000305175781</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>-0.0865284815971098</v>
+        <v>-0.09274608236520399</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>-7598.453574469648</v>
+        <v>-8144.448949737256</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>28683903.43350858</v>
+        <v>27933492.00133482</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1552028889831436</v>
+        <v>-0.1812317286467454</v>
       </c>
     </row>
     <row r="6">
@@ -3368,79 +3368,79 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>66.84999847412109</v>
+        <v>66.55000305175781</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.1363049463019763</v>
+        <v>-0.1401808560752207</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-610248.8342972519</v>
+        <v>-627601.611911966</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>28683903.43350858</v>
+        <v>27933492.00133482</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1552028889831436</v>
+        <v>-0.1812317286467454</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>387</v>
+        <v>134.6000061035156</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>359.25</v>
+        <v>128.5</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.07170542635658916</v>
+        <v>-0.04531950837226817</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-309628.7383436766</v>
+        <v>-815594.0330395401</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>28683903.43350858</v>
+        <v>27933492.00133482</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1552028889831436</v>
+        <v>-0.1812317286467454</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>134.6000061035156</v>
+        <v>93.30000305175781</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>132.6000061035156</v>
+        <v>93.30000305175781</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.01485884033661844</v>
+        <v>0</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-267407.6121233664</v>
+        <v>0</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>28683903.43350858</v>
+        <v>27933492.00133482</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1552028889831436</v>
+        <v>-0.1812317286467454</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1913,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2745,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2864,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3115,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3240,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-24 06:36</t>
+          <t>Son Güncelleme: 2026-10-25 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
         <v>-13277.62703984696</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H4" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3347,7 +3347,7 @@
         <v>-8144.448949737256</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H5" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3377,7 +3377,7 @@
         <v>-627601.611911966</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3407,7 +3407,7 @@
         <v>-815594.0330395401</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>27933492.00133482</v>
+        <v>31863824.36463429</v>
       </c>
       <c r="H8" s="30" t="n">
         <v>-0.1812317286467454</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1913,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2745,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2864,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3115,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3240,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-25 07:02</t>
+          <t>Son Güncelleme: 2026-10-26 07:09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3317,7 +3317,7 @@
         <v>-13277.62703984696</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H4" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3347,7 +3347,7 @@
         <v>-8144.448949737256</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H5" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3377,7 +3377,7 @@
         <v>-627601.611911966</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3407,7 +3407,7 @@
         <v>-815594.0330395401</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H7" s="30" t="n">
         <v>-0.1812317286467454</v>
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>31863824.36463429</v>
+        <v>35794156.72793375</v>
       </c>
       <c r="H8" s="30" t="n">
         <v>-0.1812317286467454</v>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-22</t>
+          <t>Rapor Tarihi: 2026-10-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-26 07:09</t>
+          <t>Son Güncelleme: 2026-10-27 06:55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 79.14/100</t>
+          <t>Güven Puanı: 80.85/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: GARAN.IS, SAHOL.IS, TCELL.IS</t>
+          <t>AL: BIMAS.IS, SAHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS, BIMAS.IS</t>
+          <t>AZALT: KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, TUPRS.IS, EREGL.IS, PGSUS.IS</t>
+          <t>ÇIK: THYAO.IS, TUPRS.IS, YKBNK.IS, PGSUS.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2062966470662178</v>
+        <v>0.2197461737204993</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20629.66470662178</v>
+        <v>21974.61737204992</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.03311743610603668</v>
+        <v>0.01902885545086863</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>683.2016028105068</v>
+        <v>418.1518175608848</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>132.7555905396257</v>
+        <v>380.097763083174</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>122.075</v>
+        <v>354.35</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.6623487221207304</v>
+        <v>0.3805771090173728</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2052078655889579</v>
+        <v>0.1920657311350166</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20520.78655889579</v>
+        <v>19206.57311350166</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.02241108024750615</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>459.8929943133593</v>
+        <v>430.4400513262798</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>89.51209319582017</v>
+        <v>88.94976398153304</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>80.12817985417844</v>
+        <v>79.62481212946793</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2643676751424494</v>
+        <v>0.2643680426533155</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,29 +1056,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1884954873448242</v>
+        <v>0.188188095144484</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18849.54873448243</v>
+        <v>18818.8095144484</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.01547529527999503</v>
+        <v>0.03311743610603668</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>291.7023325607721</v>
+        <v>623.23072168642</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>94.74384814860821</v>
+        <v>130.6893556674137</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>88.63500289916992</v>
+        <v>120.175</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3095059055999017</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.6623487221207349</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000</v>
+        <v>40000.00000000001</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-22</t>
+          <t>Rapor Tarihi: 2026-10-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-26 07:09</t>
+          <t>Son Güncelleme: 2026-10-27 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1367,45 +1367,45 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>87.55000305175781</v>
+        <v>373</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.08477239222015492</v>
+        <v>-0.03393167283302251</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.02241108024750615</v>
+        <v>0.01902885545086863</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.1293436503428227</v>
+        <v>0.0770489383118369</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>80.12817985417844</v>
+        <v>360.3434860332826</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>89.51209319582017</v>
+        <v>380.097763083174</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>98.87404003399743</v>
+        <v>401.7392539903151</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>80.12817985417844</v>
+        <v>354.35</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>79.14</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1424,159 +1424,159 @@
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>196.1000061035156</v>
+        <v>197.5</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>-0.03024662719688587</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.01244258503774698</v>
+        <v>0.0185279533884517</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.07297590341186155</v>
+        <v>0.07297597558230184</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>190.1686423255956</v>
+        <v>191.526291128615</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>198.5399971053613</v>
+        <v>201.1592707942192</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>210.4105812079912</v>
+        <v>211.9127551775046</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>186.2950057983398</v>
+        <v>187.625</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>87</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.08477227437393192</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.02241108024750615</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.1293435773389155</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>79.62481212946793</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>88.94976398153304</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>98.25289122848565</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>79.62481212946793</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>79.14</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M10" s="14" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>369</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.01299463649111321</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.01286270803657807</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.0890313241273375</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>364.2049791347793</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>373.7463392654973</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>401.8525586029875</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>350.55</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>258</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.06212429397630792</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>-0.01403517810195221</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.09487838702996432</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>241.9719321541126</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>254.3789240496963</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>282.4786238537308</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>241.9719321541126</v>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>79.14</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M11" s="20" t="n">
+        <v>80.84999999999999</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>128.5</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.04923849891315546</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.03311743610603668</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.07411146367770827</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>122.1728528896595</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>132.7555905396257</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>138.0233230825855</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>122.075</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>79.14</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -1595,36 +1595,36 @@
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>93.30000305175781</v>
+        <v>126.5</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-0.04480283081837821</v>
+        <v>-0.04467357917477277</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.01547529527999503</v>
+        <v>0.03311743610603668</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.06738542065873321</v>
+        <v>0.06601726062551605</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>89.11989879967574</v>
+        <v>120.8487922343912</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>94.74384814860821</v>
+        <v>130.6893556674137</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>99.58706300486161</v>
+        <v>134.8511834691278</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>88.63500289916992</v>
+        <v>120.175</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M12" s="14" t="n">
-        <v>79.14</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N12" s="14" t="inlineStr">
         <is>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>259</v>
+        <v>360.75</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.05964963819696248</v>
+        <v>-0.0431169977013468</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.03419979012555929</v>
+        <v>-0.004933116819337835</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1088930485621326</v>
+        <v>0.1114568577760859</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>243.5507437069867</v>
+        <v>345.1955430792391</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>250.1422543574801</v>
+        <v>358.9703781074239</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>287.2032995775924</v>
+        <v>400.958061442723</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>243.5507437069867</v>
+        <v>341.2443971716378</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,16 +1681,16 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>79.14</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1709,28 +1709,28 @@
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>352.25</v>
+        <v>34.68000030517578</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.06378737541528234</v>
+        <v>-0.06608877053775497</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.004932991768213713</v>
+        <v>-0.008974380762775569</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.1114567484586793</v>
+        <v>0.06945754637772672</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>329.7808970099668</v>
+        <v>32.38804172275775</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>350.5123536496467</v>
+        <v>34.36876877758396</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>391.5106396445698</v>
+        <v>37.08878803475211</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>329.7808970099668</v>
+        <v>32.38804172275775</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1738,26 +1738,26 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>79.14</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>3A momentum destekli</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -1766,28 +1766,28 @@
         </is>
       </c>
       <c r="D15" s="21" t="n">
-        <v>35.09999847412109</v>
+        <v>124.6999969482422</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.06530610017180571</v>
+        <v>-0.04456290737821772</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.0327142098683611</v>
+        <v>-0.0171127424349814</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.03380764349298043</v>
+        <v>0.1009389671361502</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>32.80775445773991</v>
+        <v>119.1430025341736</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>33.95172975765954</v>
+        <v>122.5660380188239</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>36.28664670913834</v>
+        <v>137.2870858420789</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>32.80775445773991</v>
+        <v>118.4649971008301</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -1795,26 +1795,26 @@
         </is>
       </c>
       <c r="M15" s="20" t="n">
-        <v>79.14</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>126.4000015258789</v>
+        <v>222.6000061035156</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.05280088922285953</v>
+        <v>-0.1062914431538463</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.01999250815041453</v>
+        <v>-0.03410138248847927</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.07265370930011067</v>
+        <v>0.07484769327601914</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>119.7259690475417</v>
+        <v>198.9395302087179</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>123.8729484651604</v>
+        <v>215.0090381534418</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>135.5834304922737</v>
+        <v>239.2611030835916</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>119.7259690475417</v>
+        <v>198.9395302087179</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
@@ -1852,11 +1852,11 @@
         </is>
       </c>
       <c r="M16" s="20" t="n">
-        <v>79.14</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-22</t>
+          <t>Rapor Tarihi: 2026-10-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1913,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-26 07:09</t>
+          <t>Son Güncelleme: 2026-10-27 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
@@ -2004,27 +2004,27 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.03896811725382998</v>
+        <v>-0.1176818450620934</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.005166527962344514</v>
+        <v>-0.03656871943623985</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>-0.1491739382555853</v>
+        <v>0.002554111013026716</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.04844649347959362</v>
+        <v>-0.05037733115526066</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.02196356699278244</v>
+        <v>0.02035878617018519</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.02241108024750615</v>
+        <v>0.01902885545086863</v>
       </c>
     </row>
     <row r="5">
@@ -2047,16 +2047,16 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.113071005472046</v>
+        <v>-0.08564814814814814</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>-0.003050283955441269</v>
+        <v>0.01282051282051277</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.05721150911771333</v>
+        <v>-0.04126213592233008</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>-0.2468483865708974</v>
+        <v>-0.2364708677628609</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2064,96 +2064,96 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.02181413948502545</v>
+        <v>0.02180173796942599</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.01244258503774698</v>
+        <v>0.0185279533884517</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>-0.1492795389048991</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>-0.03135733752469394</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>-0.01278883216321314</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.07347950792520175</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.01360540804719501</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>-0.004006851519577137</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>-0.1386138613861386</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>-0.02821976319684982</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.02041898757966615</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.01286270803657807</v>
+      <c r="J6" s="16" t="n">
+        <v>0.02197669201469671</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.02241108024750615</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0396113821440468</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.01101496099674582</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>-0.1076388888888888</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>-0.2927906668456071</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>-0.1057192374350087</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>-0.1912225705329154</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>-0.2110091743119266</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>-0.3281327394380832</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>0.02258494644566083</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.03311743610603668</v>
+      <c r="J7" s="22" t="n">
+        <v>0.0186328144170732</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>-0.01403517810195221</v>
       </c>
     </row>
     <row r="8">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -2176,16 +2176,16 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.07440475965212989</v>
+        <v>-0.02241108217365351</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.08797653696497476</v>
+        <v>-0.007064376099682246</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>-0.2073066654981658</v>
+        <v>-0.1078984677184613</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>-0.4243953306595553</v>
+        <v>-0.2894898094878173</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="J8" s="16" t="n">
-        <v>0.01936842231179195</v>
+        <v>0.02267286636230853</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.01547529527999503</v>
+        <v>0.03311743610603668</v>
       </c>
     </row>
     <row r="9">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -2219,27 +2219,27 @@
         </is>
       </c>
       <c r="E9" s="22" t="n">
-        <v>-0.1323283082077052</v>
+        <v>-0.1059898772608041</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>-0.1855345911949685</v>
+        <v>0.2511573494641302</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>-0.210967250571211</v>
+        <v>0.4485785836372789</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>-0.3540421314127118</v>
+        <v>-0.3634116498425045</v>
       </c>
       <c r="I9" s="20" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J9" s="22" t="n">
-        <v>0.01864965832453677</v>
+        <v>0.02703479255490248</v>
       </c>
       <c r="K9" s="22" t="n">
-        <v>-0.03419979012555929</v>
+        <v>-0.004933116819337835</v>
       </c>
     </row>
     <row r="10">
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -2262,70 +2262,70 @@
         </is>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.1275855678325234</v>
+        <v>-0.02857144078334428</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>0.2269027416333513</v>
+        <v>0.05925468928686484</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0.4061268119256807</v>
+        <v>-0.1001556958654978</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>-0.3715833849196634</v>
+        <v>-0.242107976289875</v>
       </c>
       <c r="I10" s="20" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J10" s="22" t="n">
-        <v>0.02691085205225696</v>
+        <v>0.02666939154754869</v>
       </c>
       <c r="K10" s="22" t="n">
-        <v>-0.004932991768213713</v>
+        <v>-0.008974380762775569</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.08925797508272271</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-0.1886269108649126</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.06838608486729369</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>-0.4772503930064406</v>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>0.02423775780536394</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>-0.0327142098683611</v>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>-0.09401708155895883</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.1140609520374385</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>-0.2185603114539773</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>-0.3717989745927658</v>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>0.01980351377872516</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.0124594158070348</v>
       </c>
     </row>
     <row r="12">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -2348,16 +2348,16 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.1522292604871617</v>
+        <v>-0.1746674263408187</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.1495207277730631</v>
+        <v>-0.2682051438551682</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.3809302041696948</v>
+        <v>-0.388078907308417</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.2355839815390756</v>
+        <v>-0.07666647602496834</v>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
@@ -2365,10 +2365,10 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.01875057637810846</v>
+        <v>0.01827231709776036</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.04368743118530438</v>
+        <v>0.03186277085667322</v>
       </c>
     </row>
     <row r="13">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -2391,16 +2391,16 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.04229938525245114</v>
+        <v>-0.159560700654403</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.07355617193639818</v>
+        <v>-0.1611863250560719</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.08780995399506775</v>
+        <v>-0.3714975550554801</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.2767307164932796</v>
+        <v>-0.2080231407259926</v>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.0265660993359823</v>
+        <v>0.01890476153677626</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.001239185781908958</v>
+        <v>0.1028056918712398</v>
       </c>
     </row>
     <row r="14">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -2434,16 +2434,16 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.1913929891482883</v>
+        <v>-0.1033262971563255</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.2809667741030851</v>
+        <v>-0.03723411039524671</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.3865979330764465</v>
+        <v>-0.2154798950573239</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>-0.1116852269527451</v>
+        <v>-0.1452316616202742</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -2451,139 +2451,139 @@
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.01834134569296302</v>
+        <v>0.02442795134935168</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0.03186277085667322</v>
+        <v>0.005555545834667552</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>-0.1441317806441681</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>-0.2191609309256486</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>-0.34437434832254</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>-0.3332219595887419</v>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>0.01925403988606643</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>-0.0171127424349814</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="26" t="n">
-        <v>-0.114461944118317</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>-0.02784045988086437</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>-0.2107513783943932</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>-0.1733867881279962</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="E16" s="26" t="n">
+        <v>-0.0808973487423521</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.05586592178770955</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.1475409836065574</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>0.1006635605110808</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="26" t="n">
-        <v>0.02433725202415014</v>
-      </c>
-      <c r="K15" s="26" t="n">
-        <v>0.01324791187551166</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="J16" s="26" t="n">
+        <v>0.03244688310541337</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0.05366844959199168</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="27" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
+      <c r="D17" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E16" s="28" t="n">
-        <v>-0.1590153096513819</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <v>-0.2178218022782051</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>-0.3467700179541142</v>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>-0.3473773658516691</v>
-      </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="E17" s="28" t="n">
+        <v>-0.2035777956940407</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>-0.1576158709422304</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>-0.2297577643476968</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>-0.1429318307529792</v>
+      </c>
+      <c r="I17" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n">
-        <v>0.01924144956922427</v>
-      </c>
-      <c r="K16" s="28" t="n">
-        <v>-0.01999250815041453</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.1133682830930537</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>-0.06171983356449373</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.1709558823529411</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0.06755887619341205</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.03245732562343681</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.0723430136440395</v>
+      <c r="J17" s="28" t="n">
+        <v>0.0255416360235006</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>-0.03410138248847927</v>
       </c>
     </row>
     <row r="18">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
@@ -2606,16 +2606,16 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>-0.1982078962428595</v>
+        <v>-0.1671059165715422</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>-0.1790825800064507</v>
+        <v>-0.2795257651224999</v>
       </c>
       <c r="G18" s="26" t="n">
-        <v>-0.2339041200402665</v>
+        <v>-0.05012861031373073</v>
       </c>
       <c r="H18" s="26" t="n">
-        <v>-0.1680410891024359</v>
+        <v>-0.404089626442284</v>
       </c>
       <c r="I18" s="25" t="inlineStr">
         <is>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="J18" s="26" t="n">
-        <v>0.02578066762240372</v>
+        <v>0.02702550967221838</v>
       </c>
       <c r="K18" s="26" t="n">
-        <v>0.009589578526037035</v>
+        <v>0.003331492037754846</v>
       </c>
     </row>
     <row r="19">
@@ -2649,16 +2649,16 @@
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>-0.2043478592582371</v>
+        <v>-0.1790909333662554</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>-0.09226193573559605</v>
+        <v>-0.1085883878620703</v>
       </c>
       <c r="G19" s="26" t="n">
-        <v>-0.185943077860043</v>
+        <v>-0.212041910740578</v>
       </c>
       <c r="H19" s="26" t="n">
-        <v>-0.2646692436810894</v>
+        <v>-0.2868573601012601</v>
       </c>
       <c r="I19" s="25" t="inlineStr">
         <is>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.03541162207403946</v>
+        <v>0.0354363586145526</v>
       </c>
       <c r="K19" s="26" t="n">
-        <v>0.1001577768561146</v>
+        <v>0.09055510579676895</v>
       </c>
     </row>
     <row r="20">
@@ -2692,16 +2692,16 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.1564356301020394</v>
+        <v>-0.1343893306989765</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.2067038510861499</v>
+        <v>-0.203198478283903</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-0.2789696619621984</v>
+        <v>-0.2731823008629398</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>-0.4715708320331669</v>
+        <v>-0.4629907698314769</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.02716394562150875</v>
+        <v>0.02715151895424818</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.05973090857545427</v>
+        <v>0.1001576921543033</v>
       </c>
     </row>
   </sheetData>
@@ -2737,7 +2737,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-22</t>
+          <t>Rapor Tarihi: 2026-10-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2745,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-26 07:09</t>
+          <t>Son Güncelleme: 2026-10-27 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, GARAN.IS, TCELL.IS</t>
+          <t>BIMAS.IS, SAHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TUPRS.IS, EREGL.IS, PGSUS.IS</t>
+          <t>THYAO.IS, TUPRS.IS, YKBNK.IS, PGSUS.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, YKBNK.IS, ARCLK.IS, AKBNK.IS, ASELS.IS, TOASO.IS, PETKM.IS, SISE.IS</t>
+          <t>TCELL.IS, ARCLK.IS, FROTO.IS, AKBNK.IS, ASELS.IS, EREGL.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.55 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2856,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-22</t>
+          <t>Rapor Tarihi: 2026-10-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2864,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-26 07:09</t>
+          <t>Son Güncelleme: 2026-10-27 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-22</t>
+          <t>Rapor Tarihi: 2026-10-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3115,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-26 07:09</t>
+          <t>Son Güncelleme: 2026-10-27 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11117</v>
+        <v>11152</v>
       </c>
     </row>
     <row r="5">
@@ -3149,7 +3149,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13619.53901855469</v>
+        <v>13615.15501953125</v>
       </c>
     </row>
     <row r="6">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>79.14</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3210,7 +3210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3226,7 +3226,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-22</t>
+          <t>Rapor Tarihi: 2026-10-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-26 07:09</t>
+          <t>Son Güncelleme: 2026-10-27 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,19 +3308,19 @@
         <v>197</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>196.1000061035156</v>
+        <v>197.5</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>-0.00456849693646888</v>
+        <v>0.002538071065989911</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>-13277.62703984696</v>
+        <v>7376.509491737932</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>35794156.72793375</v>
+        <v>35325334.95592974</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1812317286467454</v>
+        <v>-0.1887769994162288</v>
       </c>
     </row>
     <row r="5">
@@ -3338,19 +3338,19 @@
         <v>96.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>87.55000305175781</v>
+        <v>87</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>-0.09274608236520399</v>
+        <v>-0.0984455958549223</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>-8144.448949737256</v>
+        <v>-8644.948760312167</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>35794156.72793375</v>
+        <v>35325334.95592974</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1812317286467454</v>
+        <v>-0.1887769994162288</v>
       </c>
     </row>
     <row r="6">
@@ -3368,19 +3368,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>66.55000305175781</v>
+        <v>65.05000305175781</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.1401808560752207</v>
+        <v>-0.159560700654403</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-627601.611911966</v>
+        <v>-714366.8239176022</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>35794156.72793375</v>
+        <v>35325334.95592974</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1812317286467454</v>
+        <v>-0.1887769994162288</v>
       </c>
     </row>
     <row r="7">
@@ -3398,19 +3398,19 @@
         <v>134.6000061035156</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>128.5</v>
+        <v>126.5</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.04531950837226817</v>
+        <v>-0.06017834870888661</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-815594.0330395401</v>
+        <v>-1083001.64516291</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>35794156.72793375</v>
+        <v>35325334.95592974</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1812317286467454</v>
+        <v>-0.1887769994162288</v>
       </c>
     </row>
     <row r="8">
@@ -3428,23 +3428,53 @@
         <v>93.30000305175781</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>93.30000305175781</v>
+        <v>90.09999847412109</v>
       </c>
       <c r="E8" s="30" t="n">
+        <v>-0.03429801150018752</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>-134802.5845960039</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>35325334.95592974</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>-0.1887769994162288</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>373</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>373</v>
+      </c>
+      <c r="E9" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F9" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="29" t="n">
-        <v>35794156.72793375</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>-0.1812317286467454</v>
+      <c r="G9" s="29" t="n">
+        <v>35325334.95592974</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>-0.1887769994162288</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H8"/>
+  <autoFilter ref="A3:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -205,16 +205,16 @@
     <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-23</t>
+          <t>Rapor Tarihi: 2026-10-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-27 06:55</t>
+          <t>Son Güncelleme: 2026-10-28 07:37</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.85/100</t>
+          <t>Güven Puanı: 81.44/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, SAHOL.IS, GARAN.IS</t>
+          <t>AL: KCHOL.IS, SAHOL.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS</t>
+          <t>AZALT: BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, TUPRS.IS, YKBNK.IS, PGSUS.IS, TOASO.IS</t>
+          <t>ÇIK: THYAO.IS, ARCLK.IS, PGSUS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2197461737204993</v>
+        <v>0.2220640695396727</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21974.61737204992</v>
+        <v>22206.40695396727</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.01902885545086863</v>
+        <v>0.02326807908232298</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>418.1518175608848</v>
+        <v>516.7004331391574</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>380.097763083174</v>
+        <v>205.2675829094467</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>354.35</v>
+        <v>190.3478151612869</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805771090173728</v>
+        <v>0.4552760314583463</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1920657311350166</v>
+        <v>0.1976092813375661</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19206.57311350166</v>
+        <v>19760.92813375661</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.02241108024750615</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>430.4400513262798</v>
+        <v>442.8637461708214</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>88.94976398153304</v>
+        <v>89.46096952165679</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>79.62481212946793</v>
+        <v>79.42864161656404</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2643680426533155</v>
+        <v>0.2429540888286033</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,29 +1056,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.188188095144484</v>
+        <v>0.1803266491227612</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18818.8095144484</v>
+        <v>18032.66491227612</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.03311743610603668</v>
+        <v>0.01474470385264226</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>623.23072168642</v>
+        <v>265.8863038054445</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>130.6893556674137</v>
+        <v>369.8744445542881</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>120.175</v>
+        <v>333.3146090052186</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6623487221207349</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.1723385336161885</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000.00000000001</v>
+        <v>40000</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-23</t>
+          <t>Rapor Tarihi: 2026-10-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-27 06:55</t>
+          <t>Son Güncelleme: 2026-10-28 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 9</t>
+          <t>Toplam önerilen/satılacak satır: 7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -1367,28 +1367,28 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>373</v>
+        <v>200.6000061035156</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.03393167283302251</v>
+        <v>-0.05110763026068027</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.01902885545086863</v>
+        <v>0.02326807908232298</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0770489383118369</v>
+        <v>0.06904391931949128</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>360.3434860332826</v>
+        <v>190.3478151612869</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>380.097763083174</v>
+        <v>205.2675829094467</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>401.7392539903151</v>
+        <v>214.4502167404162</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>354.35</v>
+        <v>190.3478151612869</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1396,16 +1396,16 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>80.84999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
@@ -1424,45 +1424,45 @@
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>197.5</v>
+        <v>374.5</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.03024662719688587</v>
+        <v>-0.02055785179873293</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.0185279533884517</v>
+        <v>0.006068867739039252</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.07297597558230184</v>
+        <v>0.06844627048378671</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>191.526291128615</v>
+        <v>366.8010845013745</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>201.1592707942192</v>
+        <v>376.7727909682702</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>211.9127551775046</v>
+        <v>400.1331282961781</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>187.625</v>
+        <v>355.775</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>80.84999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
+          <t>trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O9" s="17" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1481,28 +1481,28 @@
         </is>
       </c>
       <c r="D10" s="15" t="n">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="E10" s="16" t="n">
-        <v>-0.08477227437393192</v>
+        <v>-0.0922440958106967</v>
       </c>
       <c r="F10" s="16" t="n">
         <v>0.02241108024750615</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.1293435773389155</v>
+        <v>0.1358529777746051</v>
       </c>
       <c r="H10" s="15" t="n">
-        <v>79.62481212946793</v>
+        <v>79.42864161656404</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>88.94976398153304</v>
+        <v>89.46096952165679</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>98.25289122848565</v>
+        <v>99.38713555527795</v>
       </c>
       <c r="K10" s="15" t="n">
-        <v>79.62481212946793</v>
+        <v>79.42864161656404</v>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
@@ -1510,140 +1510,140 @@
         </is>
       </c>
       <c r="M10" s="14" t="n">
-        <v>80.84999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="N10" s="14" t="inlineStr">
         <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>364.5</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.08555662824357047</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.01474470385264226</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.1262861172039955</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>333.3146090052186</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>369.8744445542881</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>410.5312897208564</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>333.3146090052186</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>258.25</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.06212429397630792</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>-0.03419979012555929</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.1114961067070557</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>242.2064010806185</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>249.4179042000743</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>287.0438695570971</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>242.2064010806185</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="14" t="inlineStr">
+      <c r="O12" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>258</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.06212429397630792</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-0.01403517810195221</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.09487838702996432</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>241.9719321541126</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>254.3789240496963</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>282.4786238537308</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>241.9719321541126</v>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>80.84999999999999</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>126.5</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.04467357917477277</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.03311743610603668</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.06601726062551605</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>120.8487922343912</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>130.6893556674137</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>134.8511834691278</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>120.175</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>80.84999999999999</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>360.75</v>
+        <v>69.19999694824219</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0431169977013468</v>
+        <v>-0.056962015212765</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.004933116819337835</v>
+        <v>-0.01768223248605655</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1114568577760859</v>
+        <v>0.1080537552156289</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>345.1955430792391</v>
+        <v>65.25822566935312</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>358.9703781074239</v>
+        <v>67.97638651416896</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>400.958061442723</v>
+        <v>76.67731647940981</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>341.2443971716378</v>
+        <v>65.25822566935312</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,26 +1681,26 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>80.84999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1709,28 +1709,28 @@
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>34.68000030517578</v>
+        <v>124.5999984741211</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.06608877053775497</v>
+        <v>-0.0461145394060134</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.008974380762775569</v>
+        <v>-0.001190292976959884</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.06945754637772672</v>
+        <v>0.09426842423778847</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>32.38804172275775</v>
+        <v>118.854126934497</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>34.36876877758396</v>
+        <v>124.4516879710081</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>37.08878803475211</v>
+        <v>136.3458439903073</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>32.38804172275775</v>
+        <v>118.369998550415</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1738,135 +1738,21 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>80.84999999999999</v>
+        <v>81.44</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>3A momentum destekli</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>124.6999969482422</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>-0.04456290737821772</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>-0.0171127424349814</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>0.1009389671361502</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>119.1430025341736</v>
-      </c>
-      <c r="I15" s="21" t="n">
-        <v>122.5660380188239</v>
-      </c>
-      <c r="J15" s="21" t="n">
-        <v>137.2870858420789</v>
-      </c>
-      <c r="K15" s="21" t="n">
-        <v>118.4649971008301</v>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="20" t="n">
-        <v>80.84999999999999</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="20" t="inlineStr">
-        <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="n">
-        <v>222.6000061035156</v>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>-0.1062914431538463</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-0.03410138248847927</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>0.07484769327601914</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>198.9395302087179</v>
-      </c>
-      <c r="I16" s="21" t="n">
-        <v>215.0090381534418</v>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>239.2611030835916</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>198.9395302087179</v>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="20" t="n">
-        <v>80.84999999999999</v>
-      </c>
-      <c r="N16" s="20" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O16" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O16"/>
+  <autoFilter ref="A7:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1884,9 +1770,9 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
@@ -1896,7 +1782,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-23</t>
+          <t>Rapor Tarihi: 2026-10-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1913,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-27 06:55</t>
+          <t>Son Güncelleme: 2026-10-28 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1990,7 +1876,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -2004,16 +1890,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.1176818450620934</v>
+        <v>-0.07344108035327657</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>-0.03656871943623985</v>
+        <v>0.03615702365348672</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.002554111013026716</v>
+        <v>-0.02098578780407923</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.05037733115526066</v>
+        <v>-0.223970211621691</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2021,10 +1907,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.02035878617018519</v>
+        <v>0.02186326630272022</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.01902885545086863</v>
+        <v>0.02326807908232298</v>
       </c>
     </row>
     <row r="5">
@@ -2033,7 +1919,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -2047,27 +1933,27 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.08564814814814814</v>
+        <v>-0.1183048852266039</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.01282051282051277</v>
+        <v>-0.02518612759594419</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>-0.04126213592233008</v>
+        <v>-0.007266306719331483</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>-0.2364708677628609</v>
+        <v>-0.04243247649541682</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.02180173796942599</v>
+        <v>0.02034442169324062</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.0185279533884517</v>
+        <v>0.006068867739039252</v>
       </c>
     </row>
     <row r="6">
@@ -2090,16 +1976,16 @@
         </is>
       </c>
       <c r="E6" s="16" t="n">
-        <v>-0.01360540804719501</v>
+        <v>-0.008498583569405138</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>-0.004006851519577137</v>
+        <v>0.03183958550796562</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>-0.1386138613861386</v>
+        <v>-0.1152679610717285</v>
       </c>
       <c r="H6" s="16" t="n">
-        <v>-0.02821976319684982</v>
+        <v>-0.01362207214885769</v>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
@@ -2107,182 +1993,182 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.02197669201469671</v>
+        <v>0.02166223991392735</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.02241108024750615</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-0.08612842015057842</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.2461187428989944</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.4107675306286076</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>-0.365653137405727</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.02701394809716362</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0.01474470385264226</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="22" t="n">
-        <v>-0.1057192374350087</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>-0.1912225705329154</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>-0.2110091743119266</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>-0.3281327394380832</v>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="E8" s="22" t="n">
+        <v>-0.1117798796216681</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>-0.1755786113328013</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>-0.2017001545595054</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>-0.3123972010415752</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="22" t="n">
-        <v>0.0186328144170732</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>-0.01403517810195221</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="J8" s="22" t="n">
+        <v>0.01854239239919497</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>-0.03419979012555929</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.02241108217365351</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>-0.007064376099682246</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>-0.1078984677184613</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>-0.2894898094878173</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>-0.007704160065398868</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>0.01979414045600225</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>-0.07604010981950182</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>-0.2772226004304805</v>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
-        <v>0.02267286636230853</v>
-      </c>
-      <c r="K8" s="16" t="n">
+      <c r="J9" s="24" t="n">
+        <v>0.02275709436275557</v>
+      </c>
+      <c r="K9" s="24" t="n">
         <v>0.03311743610603668</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="n">
-        <v>-0.1059898772608041</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>0.2511573494641302</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>0.4485785836372789</v>
-      </c>
-      <c r="H9" s="22" t="n">
-        <v>-0.3634116498425045</v>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J9" s="22" t="n">
-        <v>0.02703479255490248</v>
-      </c>
-      <c r="K9" s="22" t="n">
-        <v>-0.004933116819337835</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-0.02857144078334428</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0.05925468928686484</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>-0.1001556958654978</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>-0.242107976289875</v>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>0.001676952916100483</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>0.1256281401014656</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>-0.05535051529081336</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>-0.2120446919955054</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="22" t="n">
-        <v>0.02666939154754869</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>-0.008974380762775569</v>
+      <c r="J10" s="24" t="n">
+        <v>0.02671484245025517</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0.001239185781908958</v>
       </c>
     </row>
     <row r="11">
@@ -2305,16 +2191,16 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.09401708155895883</v>
+        <v>-0.09554773100502068</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.1140609520374385</v>
+        <v>-0.1084812606949777</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.2185603114539773</v>
+        <v>-0.2077125088973385</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.3717989745927658</v>
+        <v>-0.3599951288434333</v>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
@@ -2322,10 +2208,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.01980351377872516</v>
+        <v>0.01981305047211024</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.0124594158070348</v>
+        <v>0.01245965067974986</v>
       </c>
     </row>
     <row r="12">
@@ -2334,7 +2220,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -2348,16 +2234,16 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.1746674263408187</v>
+        <v>-0.1152344498938541</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.2682051438551682</v>
+        <v>-0.1070959486109639</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.388078907308417</v>
+        <v>-0.3357771757458945</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.07666647602496834</v>
+        <v>-0.1751950737976733</v>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
@@ -2365,10 +2251,10 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.01827231709776036</v>
+        <v>0.01970051802150657</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.03186277085667322</v>
+        <v>0.04170632890377113</v>
       </c>
     </row>
     <row r="13">
@@ -2377,12 +2263,12 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -2391,16 +2277,16 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.159560700654403</v>
+        <v>-0.08321581662766775</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.1611863250560719</v>
+        <v>0.02685625250283019</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.3714975550554801</v>
+        <v>-0.1798107255520505</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.2080231407259926</v>
+        <v>-0.1226821205781607</v>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
@@ -2408,10 +2294,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.01890476153677626</v>
+        <v>0.02416562439549304</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.1028056918712398</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2420,7 +2306,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -2430,117 +2316,117 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.1934732577282295</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-0.2963904624111323</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-0.3993055661335406</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>-0.05704328377160717</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.01846404040827601</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>-0.01768223248605655</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>-0.150647572827955</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>-0.1888021255015482</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>-0.3449001026638941</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>-0.32269698177479</v>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.01874422215090515</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>-0.001190292976959884</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.1033262971563255</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.03723411039524671</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>-0.2154798950573239</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>-0.1452316616202742</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="E16" s="28" t="n">
+        <v>-0.1000671591672263</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>-0.05500705218617774</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>-0.1551071878940732</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>0.1220999086223082</v>
+      </c>
+      <c r="I16" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="26" t="n">
-        <v>0.02442795134935168</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.005555545834667552</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="28" t="n">
-        <v>-0.1441317806441681</v>
-      </c>
-      <c r="F15" s="28" t="n">
-        <v>-0.2191609309256486</v>
-      </c>
-      <c r="G15" s="28" t="n">
-        <v>-0.34437434832254</v>
-      </c>
-      <c r="H15" s="28" t="n">
-        <v>-0.3332219595887419</v>
-      </c>
-      <c r="I15" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="28" t="n">
-        <v>0.01925403988606643</v>
-      </c>
-      <c r="K15" s="28" t="n">
-        <v>-0.0171127424349814</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>-0.0808973487423521</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.05586592178770955</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.1475409836065574</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>0.1006635605110808</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.03244688310541337</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.05366844959199168</v>
+      <c r="J16" s="28" t="n">
+        <v>0.03244288122275066</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <v>0.07234293133639436</v>
       </c>
     </row>
     <row r="17">
@@ -2559,20 +2445,20 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>PORTFOY_DISI</t>
         </is>
       </c>
       <c r="E17" s="28" t="n">
-        <v>-0.2035777956940407</v>
+        <v>-0.2437930929249731</v>
       </c>
       <c r="F17" s="28" t="n">
-        <v>-0.1576158709422304</v>
+        <v>-0.1930082684387937</v>
       </c>
       <c r="G17" s="28" t="n">
-        <v>-0.2297577643476968</v>
+        <v>-0.2515358257619187</v>
       </c>
       <c r="H17" s="28" t="n">
-        <v>-0.1429318307529792</v>
+        <v>-0.1358873443104501</v>
       </c>
       <c r="I17" s="27" t="inlineStr">
         <is>
@@ -2580,138 +2466,138 @@
         </is>
       </c>
       <c r="J17" s="28" t="n">
-        <v>0.0255416360235006</v>
+        <v>0.02528056940281808</v>
       </c>
       <c r="K17" s="28" t="n">
-        <v>-0.03410138248847927</v>
+        <v>0.03223836752309794</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.1671059165715422</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.2795257651224999</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-0.05012861031373073</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>-0.404089626442284</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="E18" s="28" t="n">
+        <v>-0.182299967200074</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.2849860815696472</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>-0.04050287181479761</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.37945340397831</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="26" t="n">
-        <v>0.02702550967221838</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.003331492037754846</v>
+      <c r="J18" s="28" t="n">
+        <v>0.02709134193250664</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>0.03393715942874287</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>-0.1233435256258888</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>-0.1778202342154821</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>-0.2648292821479244</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>-0.4579790490816344</v>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>0.0272010997580755</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>0.05958450099639157</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C19" s="25" t="inlineStr">
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="25" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E19" s="26" t="n">
-        <v>-0.1790909333662554</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>-0.1085883878620703</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>-0.212041910740578</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>-0.2868573601012601</v>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
+      <c r="E20" s="28" t="n">
+        <v>-0.1585945031949901</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>-0.1117795170077172</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>-0.2295652472454569</v>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>-0.2908586839394848</v>
+      </c>
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="26" t="n">
-        <v>0.0354363586145526</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>0.09055510579676895</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.1343893306989765</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.203198478283903</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.2731823008629398</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>-0.4629907698314769</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.02715151895424818</v>
-      </c>
-      <c r="K20" s="26" t="n">
+      <c r="J20" s="28" t="n">
+        <v>0.03546173317960027</v>
+      </c>
+      <c r="K20" s="28" t="n">
         <v>0.1001576921543033</v>
       </c>
     </row>
@@ -2737,7 +2623,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-23</t>
+          <t>Rapor Tarihi: 2026-10-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2745,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-27 06:55</t>
+          <t>Son Güncelleme: 2026-10-28 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2770,7 +2656,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, SAHOL.IS, GARAN.IS</t>
+          <t>KCHOL.IS, SAHOL.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2668,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2680,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TUPRS.IS, YKBNK.IS, PGSUS.IS, TOASO.IS</t>
+          <t>THYAO.IS, ARCLK.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2692,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, ARCLK.IS, FROTO.IS, AKBNK.IS, ASELS.IS, EREGL.IS, PETKM.IS, SISE.IS</t>
+          <t>GARAN.IS, YKBNK.IS, TCELL.IS, FROTO.IS, AKBNK.IS, ASELS.IS, TOASO.IS, EREGL.IS, SISE.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2704,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.47 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2742,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-23</t>
+          <t>Rapor Tarihi: 2026-10-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2864,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-27 06:55</t>
+          <t>Son Güncelleme: 2026-10-28 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2925,7 +2811,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2847,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2859,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3069,7 +2955,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3107,7 +2993,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-23</t>
+          <t>Rapor Tarihi: 2026-10-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3115,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-27 06:55</t>
+          <t>Son Güncelleme: 2026-10-28 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3139,7 +3025,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11152</v>
+        <v>11151</v>
       </c>
     </row>
     <row r="5">
@@ -3149,7 +3035,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13615.15501953125</v>
+        <v>13610.47001953125</v>
       </c>
     </row>
     <row r="6">
@@ -3183,7 +3069,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.84999999999999</v>
+        <v>81.44</v>
       </c>
     </row>
     <row r="9">
@@ -3226,7 +3112,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-23</t>
+          <t>Rapor Tarihi: 2026-10-26</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3240,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-27 06:55</t>
+          <t>Son Güncelleme: 2026-10-28 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3308,19 +3194,19 @@
         <v>197</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>197.5</v>
+        <v>200.6000061035156</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>0.002538071065989911</v>
+        <v>0.01827414265743976</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>7376.509491737932</v>
+        <v>53110.95838579722</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>35325334.95592974</v>
+        <v>35891038.39263295</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1887769994162288</v>
+        <v>-0.1862230005837712</v>
       </c>
     </row>
     <row r="5">
@@ -3338,19 +3224,19 @@
         <v>96.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>87</v>
+        <v>87.5</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>-0.0984455958549223</v>
+        <v>-0.09326424870466321</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>-8644.948760312167</v>
+        <v>-8189.951457137839</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>35325334.95592974</v>
+        <v>35891038.39263295</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1887769994162288</v>
+        <v>-0.1862230005837712</v>
       </c>
     </row>
     <row r="6">
@@ -3368,19 +3254,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>65.05000305175781</v>
+        <v>67.94999694824219</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.159560700654403</v>
+        <v>-0.1220930799914401</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-714366.8239176022</v>
+        <v>-546621.1004219232</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>35325334.95592974</v>
+        <v>35891038.39263295</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1887769994162288</v>
+        <v>-0.1862230005837712</v>
       </c>
     </row>
     <row r="7">
@@ -3398,19 +3284,19 @@
         <v>134.6000061035156</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>126.5</v>
+        <v>128.8000030517578</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.06017834870888661</v>
+        <v>-0.0430906596489844</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-1083001.64516291</v>
+        <v>-775482.4831894003</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>35325334.95592974</v>
+        <v>35891038.39263295</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1887769994162288</v>
+        <v>-0.1862230005837712</v>
       </c>
     </row>
     <row r="8">
@@ -3428,19 +3314,19 @@
         <v>93.30000305175781</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>90.09999847412109</v>
+        <v>90.40000152587891</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.03429801150018752</v>
+        <v>-0.03108254481267425</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-134802.5845960039</v>
+        <v>-122164.7318109595</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>35325334.95592974</v>
+        <v>35891038.39263295</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1887769994162288</v>
+        <v>-0.1862230005837712</v>
       </c>
     </row>
     <row r="9">
@@ -3458,19 +3344,19 @@
         <v>373</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>373</v>
+        <v>374.5</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>0</v>
+        <v>0.004021447721179516</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>0</v>
+        <v>31611.25225173775</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>35325334.95592974</v>
+        <v>35891038.39263295</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.1887769994162288</v>
+        <v>-0.1862230005837712</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -205,16 +205,16 @@
     <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-26</t>
+          <t>Rapor Tarihi: 2026-10-27</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-28 07:37</t>
+          <t>Son Güncelleme: 2026-10-29 07:44</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 81.44/100</t>
+          <t>Güven Puanı: 79.00/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, SAHOL.IS, TUPRS.IS</t>
+          <t>AL: SAHOL.IS, BIMAS.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: BIMAS.IS</t>
+          <t>AZALT: KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, ARCLK.IS, PGSUS.IS</t>
+          <t>ÇIK: THYAO.IS, ARCLK.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2220640695396727</v>
+        <v>0.2099328723914615</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22206.40695396727</v>
+        <v>20993.28723914615</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.02326807908232298</v>
+        <v>0.02304138516881959</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>516.7004331391574</v>
+        <v>483.7144172368317</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>205.2675829094467</v>
+        <v>87.98155912451848</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>190.3478151612869</v>
+        <v>80.10846476919471</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.4552760314583463</v>
+        <v>0.3363400280044888</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1976092813375661</v>
+        <v>0.1970601495616218</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19760.92813375661</v>
+        <v>19706.01495616218</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.02241108024750615</v>
+        <v>0.02199444625658509</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>442.8637461708214</v>
+        <v>433.4228868847711</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>89.46096952165679</v>
+        <v>370.9839839911404</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>79.42864161656404</v>
+        <v>344.85</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2429540888286033</v>
+        <v>0.439888925131702</v>
       </c>
       <c r="K21" s="10" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,29 +1056,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1803266491227612</v>
+        <v>0.1930069780469167</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18032.66491227612</v>
+        <v>19300.69780469167</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.01474470385264226</v>
+        <v>0.03311743610603668</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>265.8863038054445</v>
+        <v>639.1896263487988</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>369.8744445542881</v>
+        <v>131.5158527691227</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>333.3146090052186</v>
+        <v>120.9350028991699</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1723385336161885</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.6623487221207348</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1137,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-26</t>
+          <t>Rapor Tarihi: 2026-10-27</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-28 07:37</t>
+          <t>Son Güncelleme: 2026-10-29 07:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 7</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1358,292 +1358,292 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>86</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.06850622361401493</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.02304138516881959</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.1928571285433855</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>80.10846476919471</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>87.98155912451848</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>102.5857130547312</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>80.10846476919471</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>363</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <v>-0.01299463779415044</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>0.02199444625658509</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.08903152803477732</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>358.2829464807234</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>370.9839839911404</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>395.3184446766242</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>344.85</v>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>198.6999969482422</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.01864805498711886</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.01244258503774698</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.08540096890009941</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>194.994628479211</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>201.1723385572708</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>215.6691692080689</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>188.7649971008301</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.0431169977013468</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.01953818031979515</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.1268435859485835</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>345.9132053309631</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>368.563052185606</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>407.3539563204129</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>342.2303559433233</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>200.6000061035156</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.05110763026068027</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.02326807908232298</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.06904391931949128</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>190.3478151612869</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>205.2675829094467</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>214.4502167404162</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>190.3478151612869</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="D12" s="15" t="n">
+        <v>127.3000030517578</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.04467357917477277</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.03311743610603668</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.0761713768849927</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>121.6130562864763</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>131.5158527691227</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>136.996619561674</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>120.9350028991699</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
-        <v>81.44</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>374.5</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.02055785179873293</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.006068867739039252</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.06844627048378671</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>366.8010845013745</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>376.7727909682702</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>400.1331282961781</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>355.775</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>81.44</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.0922440958106967</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.02241108024750615</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.1358529777746051</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>79.42864161656404</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>89.46096952165679</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>99.38713555527795</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>79.42864161656404</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>81.44</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="M12" s="14" t="n">
+        <v>79</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>3A momentum destekli; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>364.5</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.08555662824357047</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.01474470385264226</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.1262861172039955</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>333.3146090052186</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>369.8744445542881</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>410.5312897208564</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>333.3146090052186</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M11" s="14" t="n">
-        <v>81.44</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>258.25</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.06212429397630792</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>-0.03419979012555929</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.1114961067070557</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>242.2064010806185</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>249.4179042000743</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>287.0438695570971</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>242.2064010806185</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="n">
-        <v>81.44</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>69.19999694824219</v>
+        <v>253</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.056962015212765</v>
+        <v>-0.06286186931348225</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.01768223248605655</v>
+        <v>-0.03419979012555929</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1080537552156289</v>
+        <v>0.05123038157605908</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>65.25822566935312</v>
+        <v>237.095947063689</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>67.97638651416896</v>
+        <v>244.3474530982335</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>76.67731647940981</v>
+        <v>265.961286538743</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>65.25822566935312</v>
+        <v>237.095947063689</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>81.44</v>
+        <v>79</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1709,28 +1709,28 @@
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>124.5999984741211</v>
+        <v>70.30000305175781</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0461145394060134</v>
+        <v>-0.09687043196316578</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.001190292976959884</v>
+        <v>-0.01768223248605655</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.09426842423778847</v>
+        <v>0.1002401581517093</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>118.854126934497</v>
+        <v>63.49001138912216</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>124.4516879710081</v>
+        <v>69.05694205402614</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>136.3458439903073</v>
+        <v>77.34688647573167</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>118.369998550415</v>
+        <v>63.49001138912216</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>81.44</v>
+        <v>79</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
@@ -1747,12 +1747,69 @@
       </c>
       <c r="O14" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>-0.1106174533515494</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-0.02162067956675134</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>0.02483255537268864</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>205.8920595491163</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>226.4948126802971</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>237.2487365687774</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>205.8920595491163</v>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="n">
+        <v>79</v>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O14"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1770,10 +1827,10 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
@@ -1782,7 +1839,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-26</t>
+          <t>Rapor Tarihi: 2026-10-27</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1799,7 +1856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-28 07:37</t>
+          <t>Son Güncelleme: 2026-10-29 07:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1876,213 +1933,213 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>-0.01035674925288566</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.04495743391303741</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>-0.1295546827569666</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-0.009533664074505954</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.02143933243343265</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.02304138516881959</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>-0.1488862837045721</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>-0.04648561241305083</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>-0.03395237846948962</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>-0.0181571866938105</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J5" s="16" t="n">
+        <v>0.02067658574961047</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>0.02199444625658509</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>-0.07149534136335423</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.03759789529108182</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.04009663310027933</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.2311021316262657</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>0.0218521322878793</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.01244258503774698</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>-0.07601232094647481</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.2777017825173125</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.3679482967382901</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>-0.3689779497340696</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.02665234309360539</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.01953818031979515</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>-0.07344108035327657</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.03615702365348672</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>-0.02098578780407923</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>-0.223970211621691</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="n">
-        <v>0.02186326630272022</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.02326807908232298</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.1183048852266039</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>-0.02518612759594419</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>-0.007266306719331483</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.04243247649541682</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>0.02034442169324062</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.006068867739039252</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>-0.008498583569405138</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.03183958550796562</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>-0.1152679610717285</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>-0.01362207214885769</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="E8" s="16" t="n">
+        <v>-0.01622867808175077</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0341186403712237</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>-0.07753620976987097</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>-0.2778467215849998</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>0.02166223991392735</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.02241108024750615</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.08612842015057842</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.2461187428989944</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.4107675306286076</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>-0.365653137405727</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="n">
-        <v>0.02701394809716362</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.01474470385264226</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>-0.1117798796216681</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>-0.1755786113328013</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>-0.2017001545595054</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>-0.3123972010415752</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>0.01854239239919497</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>-0.03419979012555929</v>
+      <c r="J8" s="16" t="n">
+        <v>0.02257038633453662</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.03311743610603668</v>
       </c>
     </row>
     <row r="9">
@@ -2091,7 +2148,7 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
@@ -2105,16 +2162,16 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.007704160065398868</v>
+        <v>-0.07371632041161336</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.01979414045600225</v>
+        <v>-0.1024630692204819</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.07604010981950182</v>
+        <v>-0.2029746628014628</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.2772226004304805</v>
+        <v>-0.3684219388939627</v>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
@@ -2122,53 +2179,53 @@
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.02275709436275557</v>
+        <v>0.01984567873436102</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.03311743610603668</v>
+        <v>0.01397516763500084</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>0.001676952916100483</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0.1256281401014656</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.05535051529081336</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>-0.2120446919955054</v>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>-0.1184668989547039</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-0.1792376317923763</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>-0.2215384615384616</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>-0.2993281067708407</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="24" t="n">
-        <v>0.02671484245025517</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0.001239185781908958</v>
+      <c r="J10" s="22" t="n">
+        <v>0.01860012209932643</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>-0.03419979012555929</v>
       </c>
     </row>
     <row r="11">
@@ -2177,7 +2234,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -2191,16 +2248,16 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.09554773100502068</v>
+        <v>-0.00394142420732535</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.1084812606949777</v>
+        <v>0.1412903570359754</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.2077125088973385</v>
+        <v>-0.06004246435122784</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.3599951288434333</v>
+        <v>-0.1989940832269231</v>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
@@ -2208,10 +2265,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.01981305047211024</v>
+        <v>0.02653474755659792</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.01245965067974986</v>
+        <v>0.001239185781908958</v>
       </c>
     </row>
     <row r="12">
@@ -2234,16 +2291,16 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.1152344498938541</v>
+        <v>-0.06737819383569332</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.1070959486109639</v>
+        <v>-0.08865704945140973</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.3357771757458945</v>
+        <v>-0.3311004638671875</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.1751950737976733</v>
+        <v>-0.1631692804167127</v>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
@@ -2251,10 +2308,10 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.01970051802150657</v>
+        <v>0.02003392730514667</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.04170632890377113</v>
+        <v>0.04170598245372625</v>
       </c>
     </row>
     <row r="13">
@@ -2263,7 +2320,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -2277,16 +2334,16 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.08321581662766775</v>
+        <v>-0.1503131449745331</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.02685625250283019</v>
+        <v>-0.1788836517823179</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.1798107255520505</v>
+        <v>-0.3543099178575273</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.1226821205781607</v>
+        <v>-0.3231680173851843</v>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
@@ -2294,10 +2351,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.02416562439549304</v>
+        <v>0.01850916004983935</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0</v>
+        <v>0.03403195746534782</v>
       </c>
     </row>
     <row r="14">
@@ -2306,127 +2363,127 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.08273888086466186</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>0.04383124422918661</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-0.1745827754522326</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>-0.1194612763952489</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.02395376261192243</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="C15" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D15" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.1934732577282295</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.2963904624111323</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>-0.3993055661335406</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>-0.05704328377160717</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="E15" s="28" t="n">
+        <v>-0.1900921592152623</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>-0.274509783851934</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>-0.4001706068063835</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>-0.04553052396428847</v>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="26" t="n">
-        <v>0.01846404040827601</v>
-      </c>
-      <c r="K14" s="26" t="n">
+      <c r="J15" s="28" t="n">
+        <v>0.01861675069194984</v>
+      </c>
+      <c r="K15" s="28" t="n">
         <v>-0.01768223248605655</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>-0.150647572827955</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>-0.1888021255015482</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>-0.3449001026638941</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>-0.32269698177479</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.07215793056501019</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>0.009629629629629655</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.1307397959183674</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>0.1302418663692446</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="26" t="n">
-        <v>0.01874422215090515</v>
-      </c>
-      <c r="K15" s="26" t="n">
-        <v>-0.001190292976959884</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="27" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>-0.1000671591672263</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <v>-0.05500705218617774</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>-0.1551071878940732</v>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>0.1220999086223082</v>
-      </c>
-      <c r="I16" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="28" t="n">
-        <v>0.03244288122275066</v>
-      </c>
-      <c r="K16" s="28" t="n">
-        <v>0.07234293133639436</v>
+      <c r="J16" s="26" t="n">
+        <v>0.03193616042664452</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0.05108908326348927</v>
       </c>
     </row>
     <row r="17">
@@ -2445,160 +2502,160 @@
       </c>
       <c r="D17" s="27" t="inlineStr">
         <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="28" t="n">
+        <v>-0.1695067264573991</v>
+      </c>
+      <c r="F17" s="28" t="n">
+        <v>-0.1113243761996161</v>
+      </c>
+      <c r="G17" s="28" t="n">
+        <v>-0.2165820642978004</v>
+      </c>
+      <c r="H17" s="28" t="n">
+        <v>-0.1037027422627315</v>
+      </c>
+      <c r="I17" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="28" t="n">
+        <v>0.02585775790409443</v>
+      </c>
+      <c r="K17" s="28" t="n">
+        <v>-0.02162067956675134</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="28" t="n">
-        <v>-0.2437930929249731</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <v>-0.1930082684387937</v>
-      </c>
-      <c r="G17" s="28" t="n">
-        <v>-0.2515358257619187</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>-0.1358873443104501</v>
-      </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="E18" s="26" t="n">
+        <v>-0.1606190109735651</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.2580189162193545</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>-0.03370415263327786</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>-0.3639455368437207</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="28" t="n">
-        <v>0.02528056940281808</v>
-      </c>
-      <c r="K17" s="28" t="n">
-        <v>0.03223836752309794</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
+      <c r="J18" s="26" t="n">
+        <v>0.02721375600951897</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.003331452010692737</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="28" t="n">
-        <v>-0.182299967200074</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>-0.2849860815696472</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>-0.04050287181479761</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>-0.37945340397831</v>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
+      <c r="E19" s="26" t="n">
+        <v>-0.1297030069444484</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>-0.07522358169166066</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>-0.2409326407802012</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>-0.3142685712497453</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="28" t="n">
-        <v>0.02709134193250664</v>
-      </c>
-      <c r="K18" s="28" t="n">
-        <v>0.03393715942874287</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
+      <c r="J19" s="26" t="n">
+        <v>0.03498496006918287</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0.09055514814767462</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C19" s="27" t="inlineStr">
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E19" s="28" t="n">
-        <v>-0.1233435256258888</v>
-      </c>
-      <c r="F19" s="28" t="n">
-        <v>-0.1778202342154821</v>
-      </c>
-      <c r="G19" s="28" t="n">
-        <v>-0.2648292821479244</v>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>-0.4579790490816344</v>
-      </c>
-      <c r="I19" s="27" t="inlineStr">
+      <c r="E20" s="26" t="n">
+        <v>-0.1203752636270813</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-0.1833575665959493</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-0.2857399737652133</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>-0.4643590764054489</v>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="28" t="n">
-        <v>0.0272010997580755</v>
-      </c>
-      <c r="K19" s="28" t="n">
-        <v>0.05958450099639157</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="27" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="n">
-        <v>-0.1585945031949901</v>
-      </c>
-      <c r="F20" s="28" t="n">
-        <v>-0.1117795170077172</v>
-      </c>
-      <c r="G20" s="28" t="n">
-        <v>-0.2295652472454569</v>
-      </c>
-      <c r="H20" s="28" t="n">
-        <v>-0.2908586839394848</v>
-      </c>
-      <c r="I20" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="28" t="n">
-        <v>0.03546173317960027</v>
-      </c>
-      <c r="K20" s="28" t="n">
-        <v>0.1001576921543033</v>
+      <c r="J20" s="26" t="n">
+        <v>0.0272503216390134</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>0.1001577768561146</v>
       </c>
     </row>
   </sheetData>
@@ -2623,7 +2680,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-26</t>
+          <t>Rapor Tarihi: 2026-10-27</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2631,7 +2688,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-28 07:37</t>
+          <t>Son Güncelleme: 2026-10-29 07:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2656,7 +2713,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, SAHOL.IS, TUPRS.IS</t>
+          <t>SAHOL.IS, BIMAS.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2725,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2737,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ARCLK.IS, PGSUS.IS</t>
+          <t>THYAO.IS, ARCLK.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2749,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS, YKBNK.IS, TCELL.IS, FROTO.IS, AKBNK.IS, ASELS.IS, TOASO.IS, EREGL.IS, SISE.IS, PETKM.IS</t>
+          <t>TCELL.IS, YKBNK.IS, FROTO.IS, PGSUS.IS, AKBNK.IS, ASELS.IS, EREGL.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2761,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.47 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.20 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2799,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-26</t>
+          <t>Rapor Tarihi: 2026-10-27</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2750,7 +2807,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-28 07:37</t>
+          <t>Son Güncelleme: 2026-10-29 07:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2811,7 +2868,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2904,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2916,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2955,7 +3012,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2993,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-26</t>
+          <t>Rapor Tarihi: 2026-10-27</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3001,7 +3058,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-28 07:37</t>
+          <t>Son Güncelleme: 2026-10-29 07:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3025,7 +3082,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11151</v>
+        <v>11165.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3035,7 +3092,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13610.47001953125</v>
+        <v>13605.29202148437</v>
       </c>
     </row>
     <row r="6">
@@ -3069,7 +3126,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>81.44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9">
@@ -3112,7 +3169,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-26</t>
+          <t>Rapor Tarihi: 2026-10-27</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3126,7 +3183,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-28 07:37</t>
+          <t>Son Güncelleme: 2026-10-29 07:44</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3194,19 +3251,19 @@
         <v>197</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>200.6000061035156</v>
+        <v>198.6999969482422</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>0.01827414265743976</v>
+        <v>0.008629426133209162</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>53110.95838579722</v>
+        <v>25080.08724926924</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>35891038.39263295</v>
+        <v>35561016.82159796</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1862230005837712</v>
+        <v>-0.1862959719789843</v>
       </c>
     </row>
     <row r="5">
@@ -3224,19 +3281,19 @@
         <v>96.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>87.5</v>
+        <v>86</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>-0.09326424870466321</v>
+        <v>-0.1088082901554405</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>-8189.951457137839</v>
+        <v>-9554.943366660824</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>35891038.39263295</v>
+        <v>35561016.82159796</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1862230005837712</v>
+        <v>-0.1862959719789843</v>
       </c>
     </row>
     <row r="6">
@@ -3254,19 +3311,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>67.94999694824219</v>
+        <v>69.90000152587891</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.1220930799914401</v>
+        <v>-0.09689922289591113</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-546621.1004219232</v>
+        <v>-433826.0600281823</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>35891038.39263295</v>
+        <v>35561016.82159796</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1862230005837712</v>
+        <v>-0.1862959719789843</v>
       </c>
     </row>
     <row r="7">
@@ -3284,19 +3341,19 @@
         <v>134.6000061035156</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>128.8000030517578</v>
+        <v>127.3000030517578</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.0430906596489844</v>
+        <v>-0.05423478990144814</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-775482.4831894003</v>
+        <v>-976038.1922819279</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>35891038.39263295</v>
+        <v>35561016.82159796</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1862230005837712</v>
+        <v>-0.1862959719789843</v>
       </c>
     </row>
     <row r="8">
@@ -3314,19 +3371,19 @@
         <v>93.30000305175781</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>90.40000152587891</v>
+        <v>91.09999847412109</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.03108254481267425</v>
+        <v>-0.02357989823876294</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-122164.7318109595</v>
+        <v>-92676.83717111778</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>35891038.39263295</v>
+        <v>35561016.82159796</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1862230005837712</v>
+        <v>-0.1862959719789843</v>
       </c>
     </row>
     <row r="9">
@@ -3344,19 +3401,19 @@
         <v>373</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>374.5</v>
+        <v>363</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>0.004021447721179516</v>
+        <v>-0.02680965147453085</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>31611.25225173775</v>
+        <v>-210741.681678256</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>35891038.39263295</v>
+        <v>35561016.82159796</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.1862230005837712</v>
+        <v>-0.1862959719789843</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,15 +188,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,16 +205,16 @@
     <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-27</t>
+          <t>Rapor Tarihi: 2026-10-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-29 07:44</t>
+          <t>Son Güncelleme: 2026-10-30 07:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 79.00/100</t>
+          <t>Güven Puanı: 79.18/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: SAHOL.IS, BIMAS.IS, GARAN.IS</t>
+          <t>AL: TUPRS.IS, GARAN.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS, TUPRS.IS</t>
+          <t>AZALT: BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, ARCLK.IS, TOASO.IS</t>
+          <t>ÇIK: THYAO.IS, PGSUS.IS, AKBNK.IS, ARCLK.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2099328723914615</v>
+        <v>0.2150769131151307</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20993.28723914615</v>
+        <v>21507.69131151307</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.02304138516881959</v>
+        <v>0.05844149786751873</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>483.7144172368317</v>
+        <v>1256.941695917042</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>87.98155912451848</v>
+        <v>375.7467317429691</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>80.10846476919471</v>
+        <v>336.0711478281098</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3363400280044888</v>
+        <v>1.096037496334751</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,29 +1015,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1970601495616218</v>
+        <v>0.1960104173232019</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19706.01495616218</v>
+        <v>19601.04173232019</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.02199444625658509</v>
+        <v>0.03311743610603668</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>433.4228868847711</v>
+        <v>649.1362471818724</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>370.9839839911404</v>
+        <v>130.8959760018107</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>344.85</v>
+        <v>120.0852874054473</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.439888925131702</v>
-      </c>
-      <c r="K21" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.6343406352798925</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,29 +1056,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1930069780469167</v>
+        <v>0.1889126695616674</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>19300.69780469167</v>
+        <v>18891.26695616674</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.03311743610603668</v>
+        <v>0.02241116988474068</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>639.1896263487988</v>
+        <v>423.3753930926406</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>131.5158527691227</v>
+        <v>85.11572989290467</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>120.9350028991699</v>
+        <v>76.81473124867266</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6623487221207348</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.2899226069649136</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000</v>
+        <v>40000.00000000001</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-27</t>
+          <t>Rapor Tarihi: 2026-10-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-29 07:44</t>
+          <t>Son Güncelleme: 2026-10-30 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1358,166 +1358,166 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.01299453751914625</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.02199403077497974</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.08916911887571016</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>360.0102424398914</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>372.7723227251739</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>397.2744361099153</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>346.5125</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>86</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.06850622361401493</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.02304138516881959</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.1928571285433855</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>80.10846476919471</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>87.98155912451848</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>102.5857130547312</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>80.10846476919471</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M8" s="14" t="n">
-        <v>79</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="D9" s="18" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0773005255414696</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.02241116988474068</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.1086499313597238</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>76.81473124867266</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>85.11572989290467</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>92.295106785697</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>76.81473124867266</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>199.8000030517578</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.01299527773417419</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.01757102788880816</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.0942064905399887</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>197.2035465208114</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>203.3106944775642</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>218.6224601491429</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>189.8100028991699</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>3A momentum destekli; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>363</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.01299463779415044</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.02199444625658509</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.08903152803477732</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>358.2829464807234</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>370.9839839911404</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>395.3184446766242</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>344.85</v>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M9" s="14" t="n">
-        <v>79</v>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>198.6999969482422</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.01864805498711886</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.01244258503774698</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.08540096890009941</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>194.994628479211</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>201.1723385572708</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>215.6691692080689</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>188.7649971008301</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>79</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
@@ -1534,40 +1534,40 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>361.5</v>
+        <v>355</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0431169977013468</v>
+        <v>-0.03252680765408428</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.01953818031979515</v>
+        <v>0.05844149786751873</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1268435859485835</v>
+        <v>0.1756285683893573</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>345.9132053309631</v>
+        <v>343.4529832828001</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>368.563052185606</v>
+        <v>375.7467317429691</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>407.3539563204129</v>
+        <v>417.3481417782218</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>342.2303559433233</v>
+        <v>336.0711478281098</v>
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M11" s="17" t="n">
-        <v>79</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="N11" s="17" t="inlineStr">
         <is>
@@ -1581,65 +1581,65 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D12" s="15" t="n">
-        <v>127.3000030517578</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.04467357917477277</v>
-      </c>
-      <c r="F12" s="16" t="n">
+      <c r="D12" s="18" t="n">
+        <v>126.6999969482422</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.05220765352896592</v>
+      </c>
+      <c r="F12" s="19" t="n">
         <v>0.03311743610603668</v>
       </c>
-      <c r="G12" s="16" t="n">
-        <v>0.0761713768849927</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>121.6130562864763</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>131.5158527691227</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>136.996619561674</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>120.9350028991699</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="G12" s="19" t="n">
+        <v>0.05777779972896546</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>120.0852874054473</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>130.8959760018107</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>134.0204439975783</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>120.0852874054473</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n">
-        <v>79</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
+      <c r="M12" s="17" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
         <is>
           <t>3A momentum destekli; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>253</v>
+        <v>252.5</v>
       </c>
       <c r="E13" s="22" t="n">
         <v>-0.06286186931348225</v>
@@ -1661,19 +1661,19 @@
         <v>-0.03419979012555929</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.05123038157605908</v>
+        <v>0.07045124277808107</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>237.095947063689</v>
+        <v>236.6273779983457</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>244.3474530982335</v>
+        <v>243.8645529932963</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>265.961286538743</v>
+        <v>270.2889388014655</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>237.095947063689</v>
+        <v>236.6273779983457</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>79</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1696,11 +1696,11 @@
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1709,28 +1709,28 @@
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>70.30000305175781</v>
+        <v>121.5</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.09687043196316578</v>
+        <v>-0.04285714285714282</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.01768223248605655</v>
+        <v>-0.0171127424349814</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.1002401581517093</v>
+        <v>0.06744663811106866</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>63.49001138912216</v>
+        <v>116.2928571428571</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>69.05694205402614</v>
+        <v>119.4208017941498</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>77.34688647573167</v>
+        <v>129.6947665304949</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>63.49001138912216</v>
+        <v>115.425</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>79</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
@@ -1747,69 +1747,183 @@
       </c>
       <c r="O14" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>-0.06619350494083276</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-0.02538799556850624</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>0.07228325784374789</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>58.82980918872754</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>61.40055627918411</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>67.55384524415611</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>58.82980918872754</v>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>-0.08891331537250863</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.01693890855618208</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>0.1049996640028169</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>64.68715460855189</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>69.79733749251108</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>78.4549761442</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>64.68715460855189</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D15" s="21" t="n">
-        <v>231.5</v>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>-0.1106174533515494</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>-0.02162067956675134</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>0.02483255537268864</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>205.8920595491163</v>
-      </c>
-      <c r="I15" s="21" t="n">
-        <v>226.4948126802971</v>
-      </c>
-      <c r="J15" s="21" t="n">
-        <v>237.2487365687774</v>
-      </c>
-      <c r="K15" s="21" t="n">
-        <v>205.8920595491163</v>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
+      <c r="D17" s="21" t="n">
+        <v>230</v>
+      </c>
+      <c r="E17" s="22" t="n">
+        <v>-0.1062914431538463</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>-0.03410138248847927</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>0.07484769327601914</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>205.5529680746153</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>222.1566820276498</v>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>247.2149694534844</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>205.5529680746153</v>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M15" s="20" t="n">
-        <v>79</v>
-      </c>
-      <c r="N15" s="20" t="inlineStr">
+      <c r="M17" s="20" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O15" s="20" t="inlineStr">
+      <c r="O17" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1828,7 +1942,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1839,7 +1953,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-27</t>
+          <t>Rapor Tarihi: 2026-10-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1856,7 +1970,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-29 07:44</t>
+          <t>Son Güncelleme: 2026-10-30 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1933,127 +2047,127 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>-0.1351511558980438</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>-0.05968845275641999</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>-0.01962034318498251</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-0.01146671579028524</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.02053819830186686</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.02199403077497974</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
+        <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>-0.01035674925288566</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.04495743391303741</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>-0.1295546827569666</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>-0.009533664074505954</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E5" s="19" t="n">
+        <v>-0.04089865123208569</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>-0.01479289940828399</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>-0.1518084696305406</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.002756734096740487</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.02143933243343265</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.02304138516881959</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="J5" s="19" t="n">
+        <v>0.02157502358556948</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.02241116988474068</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="n">
-        <v>-0.1488862837045721</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>-0.04648561241305083</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>-0.03395237846948962</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>-0.0181571866938105</v>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>-0.0667912314063358</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.01472833542492658</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>-0.02536583877191312</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>-0.2493550391745714</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J5" s="16" t="n">
-        <v>0.02067658574961047</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>0.02199444625658509</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>-0.07149534136335423</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.03759789529108182</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>-0.04009663310027933</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.2311021316262657</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>0.0218521322878793</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.01244258503774698</v>
+      <c r="J6" s="16" t="n">
+        <v>0.02157901039614461</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.01757102788880816</v>
       </c>
     </row>
     <row r="7">
@@ -2067,165 +2181,165 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>-0.05711255634561085</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.2239174313625476</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.3188380986285155</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>-0.3832471065512508</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.02666035517167634</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.05844149786751873</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.07601232094647481</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.2777017825173125</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.3679482967382901</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>-0.3689779497340696</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.02665234309360539</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.01953818031979515</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>-0.01859031016117108</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.02674226403207314</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>-0.07315289117223778</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>-0.2802591855740584</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0.02257989782760708</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0.03311743610603668</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.01622867808175077</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0341186403712237</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>-0.07753620976987097</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>-0.2778467215849998</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>-0.1337907375643225</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>-0.195859872611465</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>-0.2121684867394695</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-0.3116801448379308</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
-        <v>0.02257038633453662</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.03311743610603668</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="J9" s="22" t="n">
+        <v>0.01839391757492226</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>-0.03419979012555929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
-        <v>-0.07371632041161336</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>-0.1024630692204819</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>-0.2029746628014628</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>-0.3684219388939627</v>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="E10" s="24" t="n">
+        <v>-0.06989253321222011</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>-0.1360799217667964</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>-0.3255360820916915</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>-0.1647905602779468</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="24" t="n">
-        <v>0.01984567873436102</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>0.01397516763500084</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-0.1184668989547039</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>-0.1792376317923763</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>-0.2215384615384616</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>-0.2993281067708407</v>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>0.01860012209932643</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>-0.03419979012555929</v>
+      <c r="J10" s="24" t="n">
+        <v>0.01919087639488939</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0.04170591714306782</v>
       </c>
     </row>
     <row r="11">
@@ -2234,7 +2348,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -2248,16 +2362,16 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.00394142420732535</v>
+        <v>-0.07226461551268293</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>0.1412903570359754</v>
+        <v>-0.08804397889997184</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.06004246435122784</v>
+        <v>-0.2182675581585939</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.1989940832269231</v>
+        <v>-0.3952413885114084</v>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
@@ -2265,10 +2379,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.02653474755659792</v>
+        <v>0.0197687922477363</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.001239185781908958</v>
+        <v>0.003406581210156023</v>
       </c>
     </row>
     <row r="12">
@@ -2277,7 +2391,7 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -2291,16 +2405,16 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.06737819383569332</v>
+        <v>-0.0422222349378798</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.08865704945140973</v>
+        <v>0.0525030924550618</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.3311004638671875</v>
+        <v>-0.08297869836436733</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>-0.1631692804167127</v>
+        <v>-0.205826913405601</v>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
@@ -2308,53 +2422,53 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.02003392730514667</v>
+        <v>0.02583200132392652</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.04170598245372625</v>
+        <v>0.001239185781908958</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="n">
+      <c r="A13" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="n">
-        <v>-0.1503131449745331</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>-0.1788836517823179</v>
-      </c>
-      <c r="G13" s="24" t="n">
-        <v>-0.3543099178575273</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>-0.3231680173851843</v>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.1467696263503868</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.2058823529411765</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>-0.3467741935483871</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>-0.3419441366263984</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="24" t="n">
-        <v>0.01850916004983935</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>0.03403195746534782</v>
+      <c r="J13" s="22" t="n">
+        <v>0.01805472742949437</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>-0.0171127424349814</v>
       </c>
     </row>
     <row r="14">
@@ -2373,20 +2487,20 @@
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>PORTFOY_DISI</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.08273888086466186</v>
+        <v>-0.09871246602654704</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>0.04383124422918661</v>
+        <v>-0.006309172180628875</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.1745827754522326</v>
+        <v>-0.1891891573436509</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>-0.1194612763952489</v>
+        <v>-0.1322981719335814</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -2394,10 +2508,10 @@
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.02395376261192243</v>
+        <v>0.02382245399754359</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0</v>
+        <v>-0.02538799556850624</v>
       </c>
     </row>
     <row r="15">
@@ -2406,7 +2520,7 @@
       </c>
       <c r="B15" s="27" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C15" s="27" t="inlineStr">
@@ -2416,20 +2530,20 @@
       </c>
       <c r="D15" s="27" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>PORTFOY_DISI</t>
         </is>
       </c>
       <c r="E15" s="28" t="n">
-        <v>-0.1900921592152623</v>
+        <v>0.05908419497784334</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>-0.274509783851934</v>
+        <v>0.04747991234477711</v>
       </c>
       <c r="G15" s="28" t="n">
-        <v>-0.4001706068063835</v>
+        <v>-0.136144578313253</v>
       </c>
       <c r="H15" s="28" t="n">
-        <v>-0.04553052396428847</v>
+        <v>0.112913915237747</v>
       </c>
       <c r="I15" s="27" t="inlineStr">
         <is>
@@ -2437,10 +2551,10 @@
         </is>
       </c>
       <c r="J15" s="28" t="n">
-        <v>0.01861675069194984</v>
+        <v>0.03254720262450492</v>
       </c>
       <c r="K15" s="28" t="n">
-        <v>-0.01768223248605655</v>
+        <v>0.04060870280653839</v>
       </c>
     </row>
     <row r="16">
@@ -2449,7 +2563,7 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
@@ -2459,203 +2573,203 @@
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.1557669287967012</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.2699228791773779</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.3905579399141631</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>-0.07026724823866148</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>0.01868065274299167</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>-0.01693890855618208</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.1696750902527075</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-0.1559633027522935</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-0.2255892255892256</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>-0.09589767213610012</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.02513467276230041</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>-0.03410138248847927</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="26" t="n">
-        <v>-0.07215793056501019</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>0.009629629629629655</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.1307397959183674</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>0.1302418663692446</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="E18" s="28" t="n">
+        <v>-0.1507072704335108</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.2661025237082444</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>-0.05819946692026423</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.3679316391550315</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="26" t="n">
-        <v>0.03193616042664452</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.05108908326348927</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="27" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="27" t="inlineStr">
+      <c r="J18" s="28" t="n">
+        <v>0.02719901791902606</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>0.03223836752309794</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="n">
-        <v>-0.1695067264573991</v>
-      </c>
-      <c r="F17" s="28" t="n">
-        <v>-0.1113243761996161</v>
-      </c>
-      <c r="G17" s="28" t="n">
-        <v>-0.2165820642978004</v>
-      </c>
-      <c r="H17" s="28" t="n">
-        <v>-0.1037027422627315</v>
-      </c>
-      <c r="I17" s="27" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="28" t="n">
+        <v>-0.09979426341366926</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>-0.08472807364679757</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>-0.2628475076360229</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>-0.3312051448972866</v>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="28" t="n">
-        <v>0.02585775790409443</v>
-      </c>
-      <c r="K17" s="28" t="n">
-        <v>-0.02162067956675134</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
+      <c r="J19" s="28" t="n">
+        <v>0.03497853363382911</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>0.08095244598942708</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="27" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
+      <c r="D20" s="27" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.1606190109735651</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.2580189162193545</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-0.03370415263327786</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>-0.3639455368437207</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="E20" s="28" t="n">
+        <v>-0.1130298157207841</v>
+      </c>
+      <c r="F20" s="28" t="n">
+        <v>-0.1878294163230103</v>
+      </c>
+      <c r="G20" s="28" t="n">
+        <v>-0.2724450585077607</v>
+      </c>
+      <c r="H20" s="28" t="n">
+        <v>-0.4739271478831377</v>
+      </c>
+      <c r="I20" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="26" t="n">
-        <v>0.02721375600951897</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.003331452010692737</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>-0.1297030069444484</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>-0.07522358169166066</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>-0.2409326407802012</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>-0.3142685712497453</v>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.03498496006918287</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>0.09055514814767462</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.1203752636270813</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.1833575665959493</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.2857399737652133</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>-0.4643590764054489</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0272503216390134</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>0.1001577768561146</v>
+      <c r="J20" s="28" t="n">
+        <v>0.02721823312977668</v>
+      </c>
+      <c r="K20" s="28" t="n">
+        <v>0.05690249294878802</v>
       </c>
     </row>
   </sheetData>
@@ -2680,7 +2794,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-27</t>
+          <t>Rapor Tarihi: 2026-10-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2688,7 +2802,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-29 07:44</t>
+          <t>Son Güncelleme: 2026-10-30 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2713,7 +2827,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, BIMAS.IS, GARAN.IS</t>
+          <t>SAHOL.IS, TUPRS.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2839,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TUPRS.IS</t>
+          <t>BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2851,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ARCLK.IS, TOASO.IS</t>
+          <t>THYAO.IS, PGSUS.IS, AKBNK.IS, ARCLK.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2863,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, YKBNK.IS, FROTO.IS, PGSUS.IS, AKBNK.IS, ASELS.IS, EREGL.IS, PETKM.IS, SISE.IS</t>
+          <t>FROTO.IS, TCELL.IS, YKBNK.IS, ASELS.IS, EREGL.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2875,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.20 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.24 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2913,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-27</t>
+          <t>Rapor Tarihi: 2026-10-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2807,7 +2921,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-29 07:44</t>
+          <t>Son Güncelleme: 2026-10-30 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2868,7 +2982,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3126,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3164,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-27</t>
+          <t>Rapor Tarihi: 2026-10-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3058,7 +3172,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-29 07:44</t>
+          <t>Son Güncelleme: 2026-10-30 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3126,7 +3240,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>79</v>
+        <v>79.18000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -3169,7 +3283,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-27</t>
+          <t>Rapor Tarihi: 2026-10-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3183,7 +3297,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-29 07:44</t>
+          <t>Son Güncelleme: 2026-10-30 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3251,19 +3365,19 @@
         <v>197</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>198.6999969482422</v>
+        <v>199.8000030517578</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>0.008629426133209162</v>
+        <v>0.01421321346069959</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>25080.08724926924</v>
+        <v>41308.4981763754</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>35561016.82159796</v>
+        <v>35493015.16082414</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1862959719789843</v>
+        <v>-0.1852451553834646</v>
       </c>
     </row>
     <row r="5">
@@ -3281,19 +3395,19 @@
         <v>96.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>86</v>
+        <v>83.25</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>-0.1088082901554405</v>
+        <v>-0.1373056994818653</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>-9554.943366660824</v>
+        <v>-12057.42853411961</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>35561016.82159796</v>
+        <v>35493015.16082414</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1862959719789843</v>
+        <v>-0.1852451553834646</v>
       </c>
     </row>
     <row r="6">
@@ -3311,19 +3425,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>69.90000152587891</v>
+        <v>69.19999694824219</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.09689922289591113</v>
+        <v>-0.1059432095087882</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-433826.0600281823</v>
+        <v>-474316.7570838928</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>35561016.82159796</v>
+        <v>35493015.16082414</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1862959719789843</v>
+        <v>-0.1852451553834646</v>
       </c>
     </row>
     <row r="7">
@@ -3341,19 +3455,19 @@
         <v>134.6000061035156</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>127.3000030517578</v>
+        <v>126.6999969482422</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.05423478990144814</v>
+        <v>-0.0586924873480158</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-976038.1922819279</v>
+        <v>-1056261.291982207</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>35561016.82159796</v>
+        <v>35493015.16082414</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1862959719789843</v>
+        <v>-0.1852451553834646</v>
       </c>
     </row>
     <row r="8">
@@ -3371,19 +3485,19 @@
         <v>93.30000305175781</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>91.09999847412109</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.02357989823876294</v>
+        <v>-0.02304395986660579</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-92676.83717111778</v>
+        <v>-90570.42124229483</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>35561016.82159796</v>
+        <v>35493015.16082414</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1862959719789843</v>
+        <v>-0.1852451553834646</v>
       </c>
     </row>
     <row r="9">
@@ -3401,19 +3515,19 @@
         <v>373</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>363</v>
+        <v>364.75</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>-0.02680965147453085</v>
+        <v>-0.02211796246648789</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>-210741.681678256</v>
+        <v>-173861.8873845609</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>35561016.82159796</v>
+        <v>35493015.16082414</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.1862959719789843</v>
+        <v>-0.1852451553834646</v>
       </c>
     </row>
   </sheetData>

--- a/reports/latest_investor_report.xlsx
+++ b/reports/latest_investor_report.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2150769131151307</v>
+        <v>0.2150769987984023</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21507.69131151307</v>
+        <v>21507.69987984023</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.05844149786751873</v>
+        <v>0.05844167403239653</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1256.941695917042</v>
+        <v>1256.945985564237</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>375.7467317429691</v>
+        <v>375.7467942815007</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>336.0711478281098</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.096037496334751</v>
+        <v>1.09604080020817</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1960104173232019</v>
+        <v>0.1960103712894062</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19601.04173232019</v>
+        <v>19601.03712894061</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.03311743610603668</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>649.1362471818724</v>
+        <v>649.1360947297434</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>130.8959760018107</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>120.0852874054473</v>
+        <v>120.0852816272273</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6343406352798925</v>
+        <v>0.6343400811578253</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1889126695616674</v>
+        <v>0.1889126299121916</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18891.26695616674</v>
+        <v>18891.26299121916</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.02241116988474068</v>
+        <v>0.02241116791989972</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>423.3753930926406</v>
+        <v>423.3752671151997</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>85.11572989290467</v>
+        <v>85.11572972933165</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>76.81473124867266</v>
+        <v>76.81472520436542</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2899226069649136</v>
+        <v>0.2899223092380265</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000.00000000001</v>
+        <v>39999.99999999999</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1370,22 +1370,22 @@
         <v>364.75</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.01299453751914625</v>
+        <v>-0.01299463649111321</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.02199403077497974</v>
+        <v>0.02199409951792641</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.08916911887571016</v>
+        <v>0.08916908802962803</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>360.0102424398914</v>
+        <v>360.0102063398664</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>372.7723227251739</v>
+        <v>372.7723477991636</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>397.2744361099153</v>
+        <v>397.2744248588069</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>346.5125</v>
@@ -1427,25 +1427,25 @@
         <v>83.25</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.0773005255414696</v>
+        <v>-0.07730059814576073</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.02241116988474068</v>
+        <v>0.02241116791989972</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.1086499313597238</v>
+        <v>0.1086497453521593</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>76.81473124867266</v>
+        <v>76.81472520436542</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>85.11572989290467</v>
+        <v>85.11572972933165</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>92.295106785697</v>
+        <v>92.29509130056726</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>76.81473124867266</v>
+        <v>76.81472520436542</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
         <v>0.01757102788880816</v>
       </c>
       <c r="G10" s="16" t="n">
-        <v>0.0942064905399887</v>
+        <v>0.09420646554764889</v>
       </c>
       <c r="H10" s="15" t="n">
         <v>197.2035465208114</v>
@@ -1499,7 +1499,7 @@
         <v>203.3106944775642</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>218.6224601491429</v>
+        <v>218.6224551556734</v>
       </c>
       <c r="K10" s="15" t="n">
         <v>189.8100028991699</v>
@@ -1541,22 +1541,22 @@
         <v>355</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.03252680765408428</v>
+        <v>-0.03252668807429737</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>0.05844149786751873</v>
+        <v>0.05844167403239653</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1756285683893573</v>
+        <v>0.1756284535162542</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>343.4529832828001</v>
+        <v>343.4530257336244</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>375.7467317429691</v>
+        <v>375.7467942815007</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>417.3481417782218</v>
+        <v>417.3481009982702</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>336.0711478281098</v>
@@ -1598,7 +1598,7 @@
         <v>126.6999969482422</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.05220765352896592</v>
+        <v>-0.05220769913449161</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>0.03311743610603668</v>
@@ -1607,7 +1607,7 @@
         <v>0.05777779972896546</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>120.0852874054473</v>
+        <v>120.0852816272273</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>130.8959760018107</v>
@@ -1616,7 +1616,7 @@
         <v>134.0204439975783</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>120.0852874054473</v>
+        <v>120.0852816272273</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1769,25 +1769,25 @@
         <v>63</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.06619350494083276</v>
+        <v>-0.06619358886274462</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.02538799556850624</v>
+        <v>-0.02538782488734992</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.07228325784374789</v>
+        <v>0.07228317000253504</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>58.82980918872754</v>
+        <v>58.82980390164709</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>61.40055627918411</v>
+        <v>61.40056703209696</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>67.55384524415611</v>
+        <v>67.55383971015971</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>58.82980918872754</v>
+        <v>58.82980390164709</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>-0.01693890855618208</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.1049996640028169</v>
+        <v>0.1049996301466382</v>
       </c>
       <c r="H16" s="21" t="n">
         <v>64.68715460855189</v>
@@ -1841,7 +1841,7 @@
         <v>69.79733749251108</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>78.4549761442</v>
+        <v>78.45497374041132</v>
       </c>
       <c r="K16" s="21" t="n">
         <v>64.68715460855189</v>
@@ -1883,7 +1883,7 @@
         <v>230</v>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-0.1062914431538463</v>
+        <v>-0.1062914365179825</v>
       </c>
       <c r="F17" s="22" t="n">
         <v>-0.03410138248847927</v>
@@ -1892,7 +1892,7 @@
         <v>0.07484769327601914</v>
       </c>
       <c r="H17" s="21" t="n">
-        <v>205.5529680746153</v>
+        <v>205.552969600864</v>
       </c>
       <c r="I17" s="21" t="n">
         <v>222.1566820276498</v>
@@ -1901,7 +1901,7 @@
         <v>247.2149694534844</v>
       </c>
       <c r="K17" s="21" t="n">
-        <v>205.5529680746153</v>
+        <v>205.552969600864</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2078,10 +2078,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.02053819830186686</v>
+        <v>0.02053819830186682</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.02199403077497974</v>
+        <v>0.02199409951792641</v>
       </c>
     </row>
     <row r="5">
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.02157502358556948</v>
+        <v>0.02157502358556944</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.02241116988474068</v>
+        <v>0.02241116791989972</v>
       </c>
     </row>
     <row r="6">
@@ -2164,7 +2164,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.02157901039614461</v>
+        <v>0.02157901039614466</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.01757102788880816</v>
@@ -2207,10 +2207,10 @@
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.02666035517167634</v>
+        <v>0.02666035517167641</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>0.05844149786751873</v>
+        <v>0.05844167403239653</v>
       </c>
     </row>
     <row r="8">
@@ -2250,7 +2250,7 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.02257989782760708</v>
+        <v>0.02257989782760712</v>
       </c>
       <c r="K8" s="19" t="n">
         <v>0.03311743610603668</v>
@@ -2336,7 +2336,7 @@
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.01919087639488939</v>
+        <v>0.01919087639488928</v>
       </c>
       <c r="K10" s="24" t="n">
         <v>0.04170591714306782</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.0197687922477363</v>
+        <v>0.01976879224773625</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.003406581210156023</v>
+        <v>0.003406771384319551</v>
       </c>
     </row>
     <row r="12">
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.02583200132392652</v>
+        <v>0.02583200132392654</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.001239185781908958</v>
@@ -2508,10 +2508,10 @@
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.02382245399754359</v>
+        <v>0.02382245399754362</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>-0.02538799556850624</v>
+        <v>-0.02538782488734992</v>
       </c>
     </row>
     <row r="15">
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J15" s="28" t="n">
-        <v>0.03254720262450492</v>
+        <v>0.03254720262450491</v>
       </c>
       <c r="K15" s="28" t="n">
-        <v>0.04060870280653839</v>
+        <v>0.04060881671957561</v>
       </c>
     </row>
     <row r="16">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="J17" s="26" t="n">
-        <v>0.02513467276230041</v>
+        <v>0.02513467276230038</v>
       </c>
       <c r="K17" s="26" t="n">
         <v>-0.03410138248847927</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="J18" s="28" t="n">
-        <v>0.02719901791902606</v>
+        <v>0.02719901791902594</v>
       </c>
       <c r="K18" s="28" t="n">
         <v>0.03223836752309794</v>
@@ -2726,7 +2726,7 @@
         <v>0.03497853363382911</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>0.08095244598942708</v>
+        <v>0.08095237804027433</v>
       </c>
     </row>
     <row r="20">
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="J20" s="28" t="n">
-        <v>0.02721823312977668</v>
+        <v>0.02721823312977672</v>
       </c>
       <c r="K20" s="28" t="n">
-        <v>0.05690249294878802</v>
+        <v>0.05690245897421164</v>
       </c>
     </row>
   </sheetData>
@@ -2802,7 +2802,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2921,7 +2921,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3172,7 +3172,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3196,7 +3196,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11165.400390625</v>
+        <v>10759.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13605.29202148437</v>
+        <v>13597.81602050781</v>
       </c>
     </row>
     <row r="6">
@@ -3297,7 +3297,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-30 07:49</t>
+          <t>Son Güncelleme: 2026-10-31 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
